--- a/lib/davinci_dtr_test_kit/requirements/hl7.fhir.us.davinci-dtr_2.2.0_requirements.xlsx
+++ b/lib/davinci_dtr_test_kit/requirements/hl7.fhir.us.davinci-dtr_2.2.0_requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-dtr-test-kit/lib/davinci_dtr_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A095CAB-3DAA-FD41-945E-8DA720F4CF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5844B4E5-697F-8A43-B73C-CEA81DB8CF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1960" windowWidth="34560" windowHeight="20380" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
@@ -3156,9 +3156,6 @@
     <t>https://hl7.org/fhir/us/davinci-dtr/2.2.0/en/specification.html#ci-c-spec-121</t>
   </si>
   <si>
-    <t>If the launch context did not include Coverages, a QuestionnaireResponse or a Request or Encounter, the DTR app‚ÄØ**SHALL** either‚ÄØgenerate an error or‚ÄØallow the user to search to find one to use as context for the DTR session.</t>
-  </si>
-  <si>
     <t>spec-122</t>
   </si>
   <si>
@@ -3586,6 +3583,9 @@
   </si>
   <si>
     <t>If dependencies are such that a steady state cannot be reached (e.g., an item that is enabled causes a value to be set which causes a different item to be enabled, that then disables the first item...), then the Questionnaire SHALL be treated as erroneous and attempts at automatic population SHALL end, with the user being informed of that.</t>
+  </si>
+  <si>
+    <t>If the launch context did not include Coverages, a QuestionnaireResponse or a Request or Encounter, the DTR app **SHALL** either generate an error or allow the user to search to find one to use as context for the DTR session.</t>
   </si>
 </sst>
 </file>
@@ -4468,6 +4468,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W216"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4589,7 +4590,7 @@
         <v>ci-c-conf-1</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="85" x14ac:dyDescent="0.2">
@@ -4620,7 +4621,7 @@
         <v>ci-c-conf-2</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="51" x14ac:dyDescent="0.2">
@@ -4651,10 +4652,10 @@
         <v>ci-c-conf-3</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>92</v>
       </c>
@@ -4682,14 +4683,14 @@
         <v>ci-c-conf-4</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -4713,7 +4714,7 @@
         <v>ci-c-conf-5</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="85" x14ac:dyDescent="0.2">
@@ -4744,10 +4745,10 @@
         <v>ci-c-conf-6</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>101</v>
       </c>
@@ -4775,10 +4776,10 @@
         <v>ci-c-conf-7</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="102" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>104</v>
       </c>
@@ -4806,10 +4807,10 @@
         <v>ci-c-conf-8</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>108</v>
       </c>
@@ -4837,10 +4838,10 @@
         <v>ci-c-conf-9</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="170" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="170" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>111</v>
       </c>
@@ -4868,10 +4869,10 @@
         <v>ci-c-conf-10</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>115</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>ci-c-conf-11</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="153" x14ac:dyDescent="0.2">
@@ -4930,7 +4931,7 @@
         <v>ci-c-conf-12</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="102" x14ac:dyDescent="0.2">
@@ -4961,7 +4962,7 @@
         <v>ci-c-conf-13</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="136" x14ac:dyDescent="0.2">
@@ -4992,7 +4993,7 @@
         <v>ci-c-conf-14</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="51" x14ac:dyDescent="0.2">
@@ -5023,10 +5024,10 @@
         <v>ci-c-conf-15</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>131</v>
       </c>
@@ -5054,10 +5055,10 @@
         <v>ci-c-opcn-1</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>134</v>
       </c>
@@ -5085,7 +5086,7 @@
         <v>ci-c-opcn-2</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -5116,7 +5117,7 @@
         <v>ci-c-oper-1</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="136" x14ac:dyDescent="0.2">
@@ -5147,10 +5148,10 @@
         <v>ci-c-oper-2</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>144</v>
       </c>
@@ -5178,7 +5179,7 @@
         <v>ci-c-oper-3</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -5209,10 +5210,10 @@
         <v>ci-c-oper-4</v>
       </c>
       <c r="P22" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>150</v>
       </c>
@@ -5240,7 +5241,7 @@
         <v>ci-c-oper-5</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -5271,14 +5272,14 @@
         <v>ci-c-oper-6</v>
       </c>
       <c r="P24" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="11" t="s">
         <v>157</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -5302,10 +5303,10 @@
         <v>ci-c-oper-7</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>159</v>
       </c>
@@ -5333,10 +5334,10 @@
         <v>ci-c-oper-8</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>162</v>
       </c>
@@ -5364,10 +5365,10 @@
         <v>ci-c-oper-9</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>165</v>
       </c>
@@ -5395,10 +5396,10 @@
         <v>ci-c-oper-10</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>168</v>
       </c>
@@ -5426,10 +5427,10 @@
         <v>ci-c-oper-11</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>171</v>
       </c>
@@ -5457,10 +5458,10 @@
         <v>ci-c-oper-12</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>174</v>
       </c>
@@ -5488,10 +5489,10 @@
         <v>ci-c-oper-13</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>177</v>
       </c>
@@ -5519,10 +5520,10 @@
         <v>ci-c-oper-14</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>180</v>
       </c>
@@ -5550,10 +5551,10 @@
         <v>ci-c-oper-15</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>183</v>
       </c>
@@ -5581,10 +5582,10 @@
         <v>ci-c-oper-16</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>186</v>
       </c>
@@ -5612,10 +5613,10 @@
         <v>ci-c-oper-17</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>189</v>
       </c>
@@ -5643,10 +5644,10 @@
         <v>ci-c-oper-18</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>192</v>
       </c>
@@ -5674,7 +5675,7 @@
         <v>ci-c-oper-19</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="136" x14ac:dyDescent="0.2">
@@ -5705,10 +5706,10 @@
         <v>ci-c-oper-20</v>
       </c>
       <c r="P38" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>198</v>
       </c>
@@ -5736,14 +5737,14 @@
         <v>ci-c-prof-1</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C40" s="8" t="s">
@@ -5767,7 +5768,7 @@
         <v>ci-c-prof-2</v>
       </c>
       <c r="P40" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -5798,10 +5799,10 @@
         <v>ci-c-sec-1</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
         <v>207</v>
       </c>
@@ -5829,10 +5830,10 @@
         <v>ci-c-sec-2</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
         <v>210</v>
       </c>
@@ -5860,10 +5861,10 @@
         <v>ci-c-sec-3</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
         <v>213</v>
       </c>
@@ -5891,7 +5892,7 @@
         <v>ci-c-sec-4</v>
       </c>
       <c r="P44" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -5922,10 +5923,10 @@
         <v>ci-c-sec-5</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
         <v>218</v>
       </c>
@@ -5953,10 +5954,10 @@
         <v>ci-c-sec-6</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
         <v>220</v>
       </c>
@@ -5984,7 +5985,7 @@
         <v>ci-c-sec-7</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -6015,10 +6016,10 @@
         <v>ci-c-sec-8</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
         <v>225</v>
       </c>
@@ -6046,10 +6047,10 @@
         <v>ci-c-sec-9</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>228</v>
       </c>
@@ -6077,10 +6078,10 @@
         <v>ci-c-sec-10</v>
       </c>
       <c r="P50" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
         <v>231</v>
       </c>
@@ -6108,10 +6109,10 @@
         <v>ci-c-spec-1</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
         <v>234</v>
       </c>
@@ -6139,10 +6140,10 @@
         <v>ci-c-spec-2</v>
       </c>
       <c r="P52" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
         <v>237</v>
       </c>
@@ -6170,7 +6171,7 @@
         <v>ci-c-spec-3</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -6201,10 +6202,10 @@
         <v>ci-c-spec-4</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
         <v>243</v>
       </c>
@@ -6232,10 +6233,10 @@
         <v>ci-c-spec-5</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
         <v>246</v>
       </c>
@@ -6263,7 +6264,7 @@
         <v>ci-c-spec-6</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -6294,10 +6295,10 @@
         <v>ci-c-spec-7</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
         <v>252</v>
       </c>
@@ -6325,10 +6326,10 @@
         <v>ci-c-spec-8</v>
       </c>
       <c r="P58" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
         <v>255</v>
       </c>
@@ -6356,10 +6357,10 @@
         <v>ci-c-spec-9</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
         <v>259</v>
       </c>
@@ -6387,7 +6388,7 @@
         <v>ci-c-spec-10</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -6418,10 +6419,10 @@
         <v>ci-c-spec-11</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
         <v>265</v>
       </c>
@@ -6449,10 +6450,10 @@
         <v>ci-c-spec-12</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
         <v>269</v>
       </c>
@@ -6480,14 +6481,14 @@
         <v>ci-c-spec-13</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="7" t="s">
         <v>273</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -6511,10 +6512,10 @@
         <v>ci-c-spec-14</v>
       </c>
       <c r="P64" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
         <v>275</v>
       </c>
@@ -6542,7 +6543,7 @@
         <v>ci-c-spec-15</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -6573,10 +6574,10 @@
         <v>ci-c-spec-16</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
         <v>281</v>
       </c>
@@ -6604,10 +6605,10 @@
         <v>ci-c-spec-17</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
         <v>284</v>
       </c>
@@ -6635,7 +6636,7 @@
         <v>ci-c-spec-18</v>
       </c>
       <c r="P68" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -6666,7 +6667,7 @@
         <v>ci-c-spec-19</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="119" x14ac:dyDescent="0.2">
@@ -6697,10 +6698,10 @@
         <v>ci-c-spec-20</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
         <v>293</v>
       </c>
@@ -6728,10 +6729,10 @@
         <v>ci-c-spec-21</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
         <v>296</v>
       </c>
@@ -6759,10 +6760,10 @@
         <v>ci-c-spec-22</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
         <v>299</v>
       </c>
@@ -6790,10 +6791,10 @@
         <v>ci-c-spec-23</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
         <v>302</v>
       </c>
@@ -6821,14 +6822,14 @@
         <v>ci-c-spec-24</v>
       </c>
       <c r="P74" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="11" t="s">
         <v>306</v>
       </c>
       <c r="C75" s="8" t="s">
@@ -6852,10 +6853,10 @@
         <v>ci-c-spec-25</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
         <v>308</v>
       </c>
@@ -6883,10 +6884,10 @@
         <v>ci-c-spec-26</v>
       </c>
       <c r="P76" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
         <v>311</v>
       </c>
@@ -6914,10 +6915,10 @@
         <v>ci-c-spec-27</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>314</v>
       </c>
@@ -6945,10 +6946,10 @@
         <v>ci-c-spec-28</v>
       </c>
       <c r="P78" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
         <v>317</v>
       </c>
@@ -6976,10 +6977,10 @@
         <v>ci-c-spec-29</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="187" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="187" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
         <v>320</v>
       </c>
@@ -7007,10 +7008,10 @@
         <v>ci-c-spec-30</v>
       </c>
       <c r="P80" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
         <v>323</v>
       </c>
@@ -7038,10 +7039,10 @@
         <v>ci-c-spec-31</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
         <v>326</v>
       </c>
@@ -7069,10 +7070,10 @@
         <v>ci-c-spec-32</v>
       </c>
       <c r="P82" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
         <v>329</v>
       </c>
@@ -7100,10 +7101,10 @@
         <v>ci-c-spec-33</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
         <v>332</v>
       </c>
@@ -7131,7 +7132,7 @@
         <v>ci-c-spec-34</v>
       </c>
       <c r="P84" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="119" x14ac:dyDescent="0.2">
@@ -7162,10 +7163,10 @@
         <v>ci-c-spec-35</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
         <v>338</v>
       </c>
@@ -7193,10 +7194,10 @@
         <v>ci-c-spec-36</v>
       </c>
       <c r="P86" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
         <v>341</v>
       </c>
@@ -7224,10 +7225,10 @@
         <v>ci-c-spec-37</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
         <v>344</v>
       </c>
@@ -7255,10 +7256,10 @@
         <v>ci-c-spec-38</v>
       </c>
       <c r="P88" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
         <v>347</v>
       </c>
@@ -7286,10 +7287,10 @@
         <v>ci-c-spec-39</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
         <v>350</v>
       </c>
@@ -7317,10 +7318,10 @@
         <v>ci-c-spec-40</v>
       </c>
       <c r="P90" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
         <v>353</v>
       </c>
@@ -7348,10 +7349,10 @@
         <v>ci-c-spec-41</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
         <v>356</v>
       </c>
@@ -7379,10 +7380,10 @@
         <v>ci-c-spec-42</v>
       </c>
       <c r="P92" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
         <v>359</v>
       </c>
@@ -7410,7 +7411,7 @@
         <v>ci-c-spec-43</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -7441,10 +7442,10 @@
         <v>ci-c-spec-44</v>
       </c>
       <c r="P94" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7" t="s">
         <v>365</v>
       </c>
@@ -7472,7 +7473,7 @@
         <v>ci-c-spec-45</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="119" x14ac:dyDescent="0.2">
@@ -7503,7 +7504,7 @@
         <v>ci-c-spec-46</v>
       </c>
       <c r="P96" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="153" x14ac:dyDescent="0.2">
@@ -7534,10 +7535,10 @@
         <v>ci-c-spec-47</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
         <v>373</v>
       </c>
@@ -7565,7 +7566,7 @@
         <v>ci-c-spec-48</v>
       </c>
       <c r="P98" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -7596,10 +7597,10 @@
         <v>ci-c-spec-49</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
         <v>379</v>
       </c>
@@ -7627,10 +7628,10 @@
         <v>ci-c-spec-50</v>
       </c>
       <c r="P100" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
         <v>382</v>
       </c>
@@ -7658,10 +7659,10 @@
         <v>ci-c-spec-51</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
         <v>384</v>
       </c>
@@ -7689,10 +7690,10 @@
         <v>ci-c-spec-52</v>
       </c>
       <c r="P102" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
         <v>387</v>
       </c>
@@ -7720,10 +7721,10 @@
         <v>ci-c-spec-53</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
         <v>390</v>
       </c>
@@ -7751,10 +7752,10 @@
         <v>ci-c-spec-54</v>
       </c>
       <c r="P104" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
         <v>392</v>
       </c>
@@ -7782,10 +7783,10 @@
         <v>ci-c-spec-55</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
         <v>395</v>
       </c>
@@ -7813,10 +7814,10 @@
         <v>ci-c-spec-56</v>
       </c>
       <c r="P106" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
         <v>397</v>
       </c>
@@ -7844,10 +7845,10 @@
         <v>ci-c-spec-57</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
         <v>400</v>
       </c>
@@ -7875,7 +7876,7 @@
         <v>ci-c-spec-58</v>
       </c>
       <c r="P108" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -7906,7 +7907,7 @@
         <v>ci-c-spec-59</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="110" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -7937,10 +7938,10 @@
         <v>ci-c-spec-60</v>
       </c>
       <c r="P110" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
         <v>409</v>
       </c>
@@ -7968,7 +7969,7 @@
         <v>ci-c-spec-61</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="238" x14ac:dyDescent="0.2">
@@ -7999,10 +8000,10 @@
         <v>ci-c-spec-62</v>
       </c>
       <c r="P112" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
         <v>415</v>
       </c>
@@ -8030,7 +8031,7 @@
         <v>ci-c-spec-63</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -8061,7 +8062,7 @@
         <v>ci-c-spec-64</v>
       </c>
       <c r="P114" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="136" x14ac:dyDescent="0.2">
@@ -8092,7 +8093,7 @@
         <v>ci-c-spec-65</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -8123,7 +8124,7 @@
         <v>ci-c-spec-66</v>
       </c>
       <c r="P116" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="119" x14ac:dyDescent="0.2">
@@ -8134,7 +8135,7 @@
         <v>428</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>26</v>
@@ -8154,7 +8155,7 @@
         <v>ci-c-spec-67</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -8185,10 +8186,10 @@
         <v>ci-c-spec-68</v>
       </c>
       <c r="P118" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
         <v>432</v>
       </c>
@@ -8216,7 +8217,7 @@
         <v>ci-c-spec-69</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -8247,10 +8248,10 @@
         <v>ci-c-spec-70</v>
       </c>
       <c r="P120" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
         <v>438</v>
       </c>
@@ -8278,7 +8279,7 @@
         <v>ci-c-spec-71</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -8309,7 +8310,7 @@
         <v>ci-c-spec-72</v>
       </c>
       <c r="P122" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -8340,7 +8341,7 @@
         <v>ci-c-spec-73</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -8371,10 +8372,10 @@
         <v>ci-c-spec-74</v>
       </c>
       <c r="P124" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
         <v>450</v>
       </c>
@@ -8402,7 +8403,7 @@
         <v>ci-c-spec-75</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -8433,10 +8434,10 @@
         <v>ci-c-spec-76</v>
       </c>
       <c r="P126" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
         <v>456</v>
       </c>
@@ -8464,7 +8465,7 @@
         <v>ci-c-spec-77</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -8495,7 +8496,7 @@
         <v>ci-c-spec-78</v>
       </c>
       <c r="P128" s="10" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -8526,10 +8527,10 @@
         <v>ci-c-spec-79</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7" t="s">
         <v>465</v>
       </c>
@@ -8557,7 +8558,7 @@
         <v>ci-c-spec-80</v>
       </c>
       <c r="P130" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="131" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -8588,7 +8589,7 @@
         <v>ci-c-spec-81</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -8619,10 +8620,10 @@
         <v>ci-c-spec-82</v>
       </c>
       <c r="P132" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="7" t="s">
         <v>474</v>
       </c>
@@ -8650,10 +8651,10 @@
         <v>ci-c-spec-83</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7" t="s">
         <v>477</v>
       </c>
@@ -8681,10 +8682,10 @@
         <v>ci-c-spec-84</v>
       </c>
       <c r="P134" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="7" t="s">
         <v>480</v>
       </c>
@@ -8712,10 +8713,10 @@
         <v>ci-c-spec-85</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="7" t="s">
         <v>483</v>
       </c>
@@ -8743,10 +8744,10 @@
         <v>ci-c-spec-86</v>
       </c>
       <c r="P136" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7" t="s">
         <v>486</v>
       </c>
@@ -8774,10 +8775,10 @@
         <v>ci-c-spec-87</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7" t="s">
         <v>489</v>
       </c>
@@ -8805,10 +8806,10 @@
         <v>ci-c-spec-88</v>
       </c>
       <c r="P138" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="7" t="s">
         <v>492</v>
       </c>
@@ -8836,10 +8837,10 @@
         <v>ci-c-spec-89</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
         <v>495</v>
       </c>
@@ -8867,10 +8868,10 @@
         <v>ci-c-spec-90</v>
       </c>
       <c r="P140" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="7" t="s">
         <v>498</v>
       </c>
@@ -8898,10 +8899,10 @@
         <v>ci-c-spec-91</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
         <v>501</v>
       </c>
@@ -8929,10 +8930,10 @@
         <v>ci-c-spec-92</v>
       </c>
       <c r="P142" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
         <v>504</v>
       </c>
@@ -8960,10 +8961,10 @@
         <v>ci-c-spec-93</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="7" t="s">
         <v>507</v>
       </c>
@@ -8991,10 +8992,10 @@
         <v>ci-c-spec-94</v>
       </c>
       <c r="P144" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="7" t="s">
         <v>510</v>
       </c>
@@ -9022,10 +9023,10 @@
         <v>ci-c-spec-95</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="7" t="s">
         <v>513</v>
       </c>
@@ -9053,10 +9054,10 @@
         <v>ci-c-spec-96</v>
       </c>
       <c r="P146" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" ht="170" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="170" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
         <v>516</v>
       </c>
@@ -9084,10 +9085,10 @@
         <v>ci-c-spec-97</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="s">
         <v>519</v>
       </c>
@@ -9115,10 +9116,10 @@
         <v>ci-c-spec-98</v>
       </c>
       <c r="P148" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7" t="s">
         <v>522</v>
       </c>
@@ -9146,10 +9147,10 @@
         <v>ci-c-spec-99</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="s">
         <v>525</v>
       </c>
@@ -9177,7 +9178,7 @@
         <v>ci-c-spec-100</v>
       </c>
       <c r="P150" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="151" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -9208,7 +9209,7 @@
         <v>ci-c-spec-101</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -9239,7 +9240,7 @@
         <v>ci-c-spec-102</v>
       </c>
       <c r="P152" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="153" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -9270,7 +9271,7 @@
         <v>ci-c-spec-103</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="154" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -9301,7 +9302,7 @@
         <v>ci-c-spec-104</v>
       </c>
       <c r="P154" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="155" spans="1:16" ht="119" x14ac:dyDescent="0.2">
@@ -9332,7 +9333,7 @@
         <v>ci-c-spec-105</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -9363,7 +9364,7 @@
         <v>ci-c-spec-106</v>
       </c>
       <c r="P156" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="157" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -9394,10 +9395,10 @@
         <v>ci-c-spec-107</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
         <v>548</v>
       </c>
@@ -9425,7 +9426,7 @@
         <v>ci-c-spec-108</v>
       </c>
       <c r="P158" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="159" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -9456,10 +9457,10 @@
         <v>ci-c-spec-109</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="7" t="s">
         <v>554</v>
       </c>
@@ -9487,7 +9488,7 @@
         <v>ci-c-spec-110</v>
       </c>
       <c r="P160" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="136" x14ac:dyDescent="0.2">
@@ -9518,7 +9519,7 @@
         <v>ci-c-spec-111</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="162" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -9549,10 +9550,10 @@
         <v>ci-c-spec-112</v>
       </c>
       <c r="P162" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="s">
         <v>563</v>
       </c>
@@ -9580,10 +9581,10 @@
         <v>ci-c-spec-113</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="s">
         <v>566</v>
       </c>
@@ -9611,10 +9612,10 @@
         <v>ci-c-spec-114</v>
       </c>
       <c r="P164" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="s">
         <v>569</v>
       </c>
@@ -9642,7 +9643,7 @@
         <v>ci-c-spec-115</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="166" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -9673,7 +9674,7 @@
         <v>ci-c-spec-116</v>
       </c>
       <c r="P166" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -9704,10 +9705,10 @@
         <v>ci-c-spec-117</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="s">
         <v>578</v>
       </c>
@@ -9735,7 +9736,7 @@
         <v>ci-c-spec-118</v>
       </c>
       <c r="P168" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="169" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -9766,10 +9767,10 @@
         <v>ci-c-spec-119</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="s">
         <v>583</v>
       </c>
@@ -9797,7 +9798,7 @@
         <v>ci-c-spec-120</v>
       </c>
       <c r="P170" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -9808,7 +9809,7 @@
         <v>587</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>588</v>
+        <v>731</v>
       </c>
       <c r="D171" s="7" t="s">
         <v>26</v>
@@ -9828,18 +9829,18 @@
         <v>ci-c-spec-121</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="B172" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="B172" s="7" t="s">
+      <c r="C172" s="8" t="s">
         <v>590</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>591</v>
       </c>
       <c r="D172" s="7" t="s">
         <v>26</v>
@@ -9859,18 +9860,18 @@
         <v>ci-c-spec-122</v>
       </c>
       <c r="P172" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="173" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A173" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B173" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="B173" s="7" t="s">
+      <c r="C173" s="8" t="s">
         <v>593</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>594</v>
       </c>
       <c r="D173" s="7" t="s">
         <v>26</v>
@@ -9890,18 +9891,18 @@
         <v>ci-c-spec-123</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="B174" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="C174" s="8" t="s">
         <v>596</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>597</v>
       </c>
       <c r="D174" s="7" t="s">
         <v>29</v>
@@ -9921,18 +9922,18 @@
         <v>ci-c-spec-124</v>
       </c>
       <c r="P174" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="175" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="B175" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="C175" s="8" t="s">
         <v>599</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>600</v>
       </c>
       <c r="D175" s="7" t="s">
         <v>31</v>
@@ -9952,18 +9953,18 @@
         <v>ci-c-spec-125</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="176" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="B176" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="C176" s="8" t="s">
         <v>602</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>603</v>
       </c>
       <c r="D176" s="7" t="s">
         <v>26</v>
@@ -9983,18 +9984,18 @@
         <v>ci-c-spec-126</v>
       </c>
       <c r="P176" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="B177" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="C177" s="8" t="s">
         <v>605</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>606</v>
       </c>
       <c r="D177" s="7" t="s">
         <v>30</v>
@@ -10014,18 +10015,18 @@
         <v>ci-c-spec-127</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="B178" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="C178" s="8" t="s">
         <v>608</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>609</v>
       </c>
       <c r="D178" s="7" t="s">
         <v>26</v>
@@ -10045,18 +10046,18 @@
         <v>ci-c-spec-128</v>
       </c>
       <c r="P178" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B179" s="7" t="s">
         <v>610</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="C179" s="8" t="s">
         <v>611</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>612</v>
       </c>
       <c r="D179" s="7" t="s">
         <v>30</v>
@@ -10076,18 +10077,18 @@
         <v>ci-c-spec-129</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="B180" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="C180" s="8" t="s">
         <v>614</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>615</v>
       </c>
       <c r="D180" s="7" t="s">
         <v>26</v>
@@ -10107,18 +10108,18 @@
         <v>ci-c-spec-130</v>
       </c>
       <c r="P180" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="B181" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="B181" s="7" t="s">
+      <c r="C181" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>618</v>
       </c>
       <c r="D181" s="7" t="s">
         <v>30</v>
@@ -10138,18 +10139,18 @@
         <v>ci-c-spec-131</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="182" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A182" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="B182" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="C182" s="8" t="s">
         <v>620</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>621</v>
       </c>
       <c r="D182" s="7" t="s">
         <v>26</v>
@@ -10169,18 +10170,18 @@
         <v>ci-c-spec-132</v>
       </c>
       <c r="P182" s="10" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="B183" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="B183" s="7" t="s">
+      <c r="C183" s="8" t="s">
         <v>623</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>624</v>
       </c>
       <c r="D183" s="7" t="s">
         <v>29</v>
@@ -10200,18 +10201,18 @@
         <v>ci-c-spec-133</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="B184" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="C184" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="C184" s="8" t="s">
-        <v>627</v>
       </c>
       <c r="D184" s="7" t="s">
         <v>29</v>
@@ -10231,18 +10232,18 @@
         <v>ci-c-spec-134</v>
       </c>
       <c r="P184" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="185" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A185" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="B185" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="B185" s="7" t="s">
+      <c r="C185" s="8" t="s">
         <v>629</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>630</v>
       </c>
       <c r="D185" s="7" t="s">
         <v>26</v>
@@ -10262,15 +10263,15 @@
         <v>ci-c-spec-135</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="186" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A186" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="B186" s="7" t="s">
         <v>631</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>632</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>39</v>
@@ -10293,18 +10294,18 @@
         <v>ci-c-spec-136</v>
       </c>
       <c r="P186" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="B187" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="B187" s="7" t="s">
+      <c r="C187" s="8" t="s">
         <v>634</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>635</v>
       </c>
       <c r="D187" s="7" t="s">
         <v>26</v>
@@ -10324,18 +10325,18 @@
         <v>ci-c-spec-137</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="B188" s="7" t="s">
         <v>636</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="C188" s="8" t="s">
         <v>637</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>638</v>
       </c>
       <c r="D188" s="7" t="s">
         <v>26</v>
@@ -10355,18 +10356,18 @@
         <v>ci-c-spec-138</v>
       </c>
       <c r="P188" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="B189" s="7" t="s">
         <v>639</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="C189" s="8" t="s">
         <v>640</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>641</v>
       </c>
       <c r="D189" s="7" t="s">
         <v>26</v>
@@ -10386,18 +10387,18 @@
         <v>ci-c-spec-139</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="B190" s="7" t="s">
         <v>642</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="C190" s="8" t="s">
         <v>643</v>
-      </c>
-      <c r="C190" s="8" t="s">
-        <v>644</v>
       </c>
       <c r="D190" s="7" t="s">
         <v>26</v>
@@ -10417,18 +10418,18 @@
         <v>ci-c-spec-140</v>
       </c>
       <c r="P190" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="B191" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="C191" s="8" t="s">
         <v>646</v>
-      </c>
-      <c r="C191" s="8" t="s">
-        <v>647</v>
       </c>
       <c r="D191" s="7" t="s">
         <v>26</v>
@@ -10448,15 +10449,15 @@
         <v>ci-c-spec-141</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="192" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A192" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="B192" s="7" t="s">
         <v>648</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>649</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>40</v>
@@ -10479,15 +10480,15 @@
         <v>ci-c-spec-142</v>
       </c>
       <c r="P192" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="193" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A193" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="B193" s="7" t="s">
         <v>650</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>651</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>41</v>
@@ -10510,21 +10511,21 @@
         <v>ci-c-spec-143</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="B194" s="7" t="s">
         <v>652</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="C194" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="C194" s="8" t="s">
+      <c r="D194" s="7" t="s">
         <v>654</v>
-      </c>
-      <c r="D194" s="7" t="s">
-        <v>655</v>
       </c>
       <c r="E194" s="8" t="s">
         <v>91</v>
@@ -10541,18 +10542,18 @@
         <v>ci-c-spec-144</v>
       </c>
       <c r="P194" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="195" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A195" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B195" s="7" t="s">
         <v>656</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="C195" s="8" t="s">
         <v>657</v>
-      </c>
-      <c r="C195" s="8" t="s">
-        <v>658</v>
       </c>
       <c r="D195" s="7" t="s">
         <v>31</v>
@@ -10572,18 +10573,18 @@
         <v>ci-c-spec-145</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="196" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A196" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="B196" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="C196" s="8" t="s">
         <v>660</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>661</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>31</v>
@@ -10603,18 +10604,18 @@
         <v>ci-c-spec-146</v>
       </c>
       <c r="P196" s="10" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="B197" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="C197" s="8" t="s">
         <v>663</v>
-      </c>
-      <c r="C197" s="8" t="s">
-        <v>664</v>
       </c>
       <c r="D197" s="7" t="s">
         <v>26</v>
@@ -10634,18 +10635,18 @@
         <v>ci-c-spec-147</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="B198" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="C198" s="8" t="s">
         <v>666</v>
-      </c>
-      <c r="C198" s="8" t="s">
-        <v>667</v>
       </c>
       <c r="D198" s="7" t="s">
         <v>30</v>
@@ -10665,18 +10666,18 @@
         <v>ci-c-spec-148</v>
       </c>
       <c r="P198" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="B199" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="C199" s="8" t="s">
         <v>669</v>
-      </c>
-      <c r="C199" s="8" t="s">
-        <v>670</v>
       </c>
       <c r="D199" s="7" t="s">
         <v>30</v>
@@ -10696,18 +10697,18 @@
         <v>ci-c-spec-149</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A200" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="B200" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="C200" s="8" t="s">
         <v>672</v>
-      </c>
-      <c r="C200" s="8" t="s">
-        <v>673</v>
       </c>
       <c r="D200" s="7" t="s">
         <v>26</v>
@@ -10727,18 +10728,18 @@
         <v>ci-c-spec-150</v>
       </c>
       <c r="P200" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="201" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A201" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="B201" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="C201" s="8" t="s">
         <v>675</v>
-      </c>
-      <c r="C201" s="8" t="s">
-        <v>676</v>
       </c>
       <c r="D201" s="7" t="s">
         <v>26</v>
@@ -10758,18 +10759,18 @@
         <v>ci-c-spec-151</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="202" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A202" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="B202" s="7" t="s">
         <v>677</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="C202" s="8" t="s">
         <v>678</v>
-      </c>
-      <c r="C202" s="8" t="s">
-        <v>679</v>
       </c>
       <c r="D202" s="7" t="s">
         <v>26</v>
@@ -10789,18 +10790,18 @@
         <v>ci-c-spec-152</v>
       </c>
       <c r="P202" s="10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="203" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="B203" s="7" t="s">
         <v>680</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="C203" s="8" t="s">
         <v>681</v>
-      </c>
-      <c r="C203" s="8" t="s">
-        <v>682</v>
       </c>
       <c r="D203" s="7" t="s">
         <v>26</v>
@@ -10820,18 +10821,18 @@
         <v>ci-c-spec-153</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="204" spans="1:16" ht="204" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="B204" s="7" t="s">
         <v>683</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="C204" s="8" t="s">
         <v>684</v>
-      </c>
-      <c r="C204" s="8" t="s">
-        <v>685</v>
       </c>
       <c r="D204" s="7" t="s">
         <v>26</v>
@@ -10851,18 +10852,18 @@
         <v>ci-c-spec-154</v>
       </c>
       <c r="P204" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="B205" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="C205" s="8" t="s">
         <v>687</v>
-      </c>
-      <c r="C205" s="8" t="s">
-        <v>688</v>
       </c>
       <c r="D205" s="7" t="s">
         <v>26</v>
@@ -10882,18 +10883,18 @@
         <v>ci-c-spec-155</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="206" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A206" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="B206" s="7" t="s">
         <v>689</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="C206" s="8" t="s">
         <v>690</v>
-      </c>
-      <c r="C206" s="8" t="s">
-        <v>691</v>
       </c>
       <c r="D206" s="7" t="s">
         <v>26</v>
@@ -10913,18 +10914,18 @@
         <v>ci-c-spec-156</v>
       </c>
       <c r="P206" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="207" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="B207" s="7" t="s">
         <v>692</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="C207" s="8" t="s">
         <v>693</v>
-      </c>
-      <c r="C207" s="8" t="s">
-        <v>694</v>
       </c>
       <c r="D207" s="7" t="s">
         <v>26</v>
@@ -10944,18 +10945,18 @@
         <v>ci-c-spec-157</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A208" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="B208" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="C208" s="8" t="s">
         <v>696</v>
-      </c>
-      <c r="C208" s="8" t="s">
-        <v>697</v>
       </c>
       <c r="D208" s="7" t="s">
         <v>26</v>
@@ -10975,18 +10976,18 @@
         <v>ci-c-spec-158</v>
       </c>
       <c r="P208" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" ht="221" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" ht="221" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="B209" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="C209" s="8" t="s">
         <v>699</v>
-      </c>
-      <c r="C209" s="8" t="s">
-        <v>700</v>
       </c>
       <c r="D209" s="7" t="s">
         <v>26</v>
@@ -11006,18 +11007,18 @@
         <v>ci-c-spec-159</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="B210" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="C210" s="8" t="s">
         <v>702</v>
-      </c>
-      <c r="C210" s="8" t="s">
-        <v>703</v>
       </c>
       <c r="D210" s="7" t="s">
         <v>26</v>
@@ -11037,18 +11038,18 @@
         <v>ci-c-spec-160</v>
       </c>
       <c r="P210" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="B211" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="C211" s="8" t="s">
         <v>705</v>
-      </c>
-      <c r="C211" s="8" t="s">
-        <v>706</v>
       </c>
       <c r="D211" s="7" t="s">
         <v>30</v>
@@ -11068,18 +11069,18 @@
         <v>ci-c-spec-161</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="B212" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="C212" s="8" t="s">
         <v>708</v>
-      </c>
-      <c r="C212" s="8" t="s">
-        <v>709</v>
       </c>
       <c r="D212" s="7" t="s">
         <v>29</v>
@@ -11099,21 +11100,21 @@
         <v>ci-c-spec-162</v>
       </c>
       <c r="P212" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="B213" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="C213" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="C213" s="8" t="s">
+      <c r="D213" s="7" t="s">
         <v>712</v>
-      </c>
-      <c r="D213" s="7" t="s">
-        <v>713</v>
       </c>
       <c r="E213" s="8" t="s">
         <v>91</v>
@@ -11130,18 +11131,18 @@
         <v>ci-c-spec-163</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="B214" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="C214" s="8" t="s">
         <v>715</v>
-      </c>
-      <c r="C214" s="8" t="s">
-        <v>716</v>
       </c>
       <c r="D214" s="7" t="s">
         <v>29</v>
@@ -11161,18 +11162,18 @@
         <v>ci-c-spec-164</v>
       </c>
       <c r="P214" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="B215" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="C215" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="C215" s="8" t="s">
-        <v>719</v>
       </c>
       <c r="D215" s="7" t="s">
         <v>31</v>
@@ -11192,18 +11193,18 @@
         <v>ci-c-spec-165</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="B216" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="C216" s="8" t="s">
         <v>721</v>
-      </c>
-      <c r="C216" s="8" t="s">
-        <v>722</v>
       </c>
       <c r="D216" s="7" t="s">
         <v>30</v>
@@ -11223,15 +11224,32 @@
         <v>ci-c-spec-166</v>
       </c>
       <c r="P216" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE216" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
+  <autoFilter ref="A1:AE216" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="SHALL"/>
+        <filter val="SHALL / MAY"/>
+        <filter val="SHALL / SHOULD"/>
+        <filter val="SHALL NOT"/>
+        <filter val="SHALL NOT / MAY"/>
+        <filter val="SHALL NOT / SHALL"/>
+        <filter val="SHALL NOT / SHOULD"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="DTR Client"/>
+        <filter val="DTR Client, DTR Server"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" location="ci-c-conf-5" xr:uid="{54FDFC2F-0C71-9847-9311-57A99C2A2FC8}"/>
-    <hyperlink ref="B40" r:id="rId2" location="ci-c-prof-2" xr:uid="{7290C952-57E1-8842-B595-0231F7C148ED}"/>
-    <hyperlink ref="B64" r:id="rId3" location="ci-c-spec-14" xr:uid="{00DAE728-E8A3-4041-ABBD-1CA449CC91CF}"/>
+    <hyperlink ref="B25" r:id="rId1" location="ci-c-oper-7" xr:uid="{4023679D-7765-2B42-A707-2B63CD4C2439}"/>
+    <hyperlink ref="B75" r:id="rId2" location="ci-c-spec-25" xr:uid="{C6E51CB5-4ECD-3246-931F-4ABAFB05C0AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/lib/davinci_dtr_test_kit/requirements/hl7.fhir.us.davinci-dtr_2.2.0_requirements.xlsx
+++ b/lib/davinci_dtr_test_kit/requirements/hl7.fhir.us.davinci-dtr_2.2.0_requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-dtr-test-kit/lib/davinci_dtr_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5844B4E5-697F-8A43-B73C-CEA81DB8CF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41385D38-F18D-A448-81DF-4EFCFF584FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1960" windowWidth="34560" windowHeight="20380" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20380" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="9" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Column Data" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$AE$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$AF$217</definedName>
     <definedName name="EXPLODE" localSheetId="0">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="EXPLODE">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="FIND_DUPLICATES" localSheetId="0">_xlfn.LAMBDA(_xlpm.test_word,_xlpm.test_key,_xlpm.words,_xlpm.keys,_xlpm.threshold, _xlfn.LET(_xlpm.duplist,_xlfn._xlws.FILTER(_xlpm.keys,_xlfn.BYROW(_xlpm.words, _xlfn.LAMBDA(_xlpm.word, Info!HAMDIST(INDEX(_xlpm.word,1,1), _xlpm.test_word)&lt;_xlpm.threshold))),_xlfn.SINGLE(_xlfn._xlws.FILTER(_xlpm.duplist,_xlpm.duplist&lt;&gt;_xlpm.test_key,""))))</definedName>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="764">
   <si>
     <r>
       <rPr>
@@ -1812,15 +1812,9 @@
     <t>This operation **SHALL** be supported by payers and DTR applications.</t>
   </si>
   <si>
-    <t>oper-2</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-dtr/2.2.0/en/OperationDefinition-log-questionnaire-errors.html#ci-c-oper-2</t>
   </si>
   <si>
-    <t>The input OperationOutcome resource **SHOULD** include information on the DTR application identity and version, date-time with time-zone offset, as well as the provider endpoint during which the error occurred, and it **SHALL NOT** contain information about the response or information retrieved from FHIR APIs that could potentially include PHI.</t>
-  </si>
-  <si>
     <t>SHALL NOT / SHOULD</t>
   </si>
   <si>
@@ -3586,6 +3580,108 @@
   </si>
   <si>
     <t>If the launch context did not include Coverages, a QuestionnaireResponse or a Request or Encounter, the DTR app **SHALL** either generate an error or allow the user to search to find one to use as context for the DTR session.</t>
+  </si>
+  <si>
+    <t>Test Implementation Ticket</t>
+  </si>
+  <si>
+    <t>Mechanical - wait for invocations</t>
+  </si>
+  <si>
+    <t>Limitation - initial tests will focus on requirements within DTR itself</t>
+  </si>
+  <si>
+    <t>Attestation - Inferno can't check display</t>
+  </si>
+  <si>
+    <t>Not Applicable - responsibility of the organization, not the software</t>
+  </si>
+  <si>
+    <t>oper-2-A</t>
+  </si>
+  <si>
+    <t>oper-2-B</t>
+  </si>
+  <si>
+    <t>The input OperationOutcome resource **SHOULD** include information on the DTR application identity and version, date-time with time-zone offset, as well as the provider endpoint during which the error occurred</t>
+  </si>
+  <si>
+    <t>The input OperationOutcome resource … **SHALL NOT** contain information about the response or information retrieved from FHIR APIs that could potentially include PHI.</t>
+  </si>
+  <si>
+    <t>Attestation - Inferno cannot determine what is PHI</t>
+  </si>
+  <si>
+    <t>Mechanical - request verification</t>
+  </si>
+  <si>
+    <t>Mechanical - set up a resume scenario and verify the inputs</t>
+  </si>
+  <si>
+    <t>NA - SMART App, not Full HER</t>
+  </si>
+  <si>
+    <t>Attestation - security details too complex to check completely</t>
+  </si>
+  <si>
+    <t>Attestation - Inferno cannot know what the policy is and when/what was restricted</t>
+  </si>
+  <si>
+    <t>Mechanical - require systems to register with Inferno's simulation</t>
+  </si>
+  <si>
+    <t>TODO - check full requirement</t>
+  </si>
+  <si>
+    <t>Attestation - no outward sign of licensing</t>
+  </si>
+  <si>
+    <t>Attestation - no outward sign to verify</t>
+  </si>
+  <si>
+    <t>Mechanical - scenarios for both static and adaptive</t>
+  </si>
+  <si>
+    <t>Mechanical - observe all Questionnaire must support elements</t>
+  </si>
+  <si>
+    <t>Mechanical - observe these additional items as well, with a slightly different attestation</t>
+  </si>
+  <si>
+    <t>Attestation - set up the scenario but can't check the display</t>
+  </si>
+  <si>
+    <t>Mechanical - Set up a scenario for this where value sets passed early and confirm they can still be used later in the adaptive questionnaire</t>
+  </si>
+  <si>
+    <t>Attestation - no API and can't check display</t>
+  </si>
+  <si>
+    <t>Attestation - can't check the display</t>
+  </si>
+  <si>
+    <t>Requirement categories (technical exchange, visual, other)</t>
+  </si>
+  <si>
+    <t>Technical Exchange</t>
+  </si>
+  <si>
+    <t>cateogry rationale</t>
+  </si>
+  <si>
+    <t>Visual</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t>Content Meaning</t>
+  </si>
+  <si>
+    <t>Element Coverage (multiple - come back)</t>
+  </si>
+  <si>
+    <t>clients need to be able to complete forms</t>
   </si>
 </sst>
 </file>
@@ -3944,7 +4040,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4026,6 +4122,10 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4044,7 +4144,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4416,14 +4515,14 @@
       <c r="C3" s="29"/>
     </row>
     <row r="4" spans="1:3" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="37" t="s">
         <v>76</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:3" ht="258" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="34"/>
       <c r="C5" s="29"/>
     </row>
@@ -4435,17 +4534,17 @@
       <c r="C6" s="24"/>
     </row>
     <row r="7" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="40"/>
     </row>
     <row r="8" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37"/>
-      <c r="B8" s="39"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="41"/>
     </row>
     <row r="9" spans="1:3" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="33"/>
     </row>
     <row r="10" spans="1:3" ht="292" x14ac:dyDescent="0.2">
@@ -4468,8 +4567,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:W216"/>
+  <dimension ref="A1:X224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="7"/>
@@ -4489,17 +4587,18 @@
     <col min="15" max="15" width="20" style="10" customWidth="1"/>
     <col min="16" max="16" width="28.5" style="10" customWidth="1"/>
     <col min="17" max="17" width="10.83203125" style="13"/>
-    <col min="18" max="18" width="10.83203125" style="10"/>
-    <col min="19" max="19" width="10.5" style="10" customWidth="1"/>
-    <col min="20" max="20" width="42.5" style="13" customWidth="1"/>
-    <col min="21" max="21" width="21.83203125" style="6" customWidth="1"/>
-    <col min="22" max="22" width="19.1640625" style="6" customWidth="1"/>
-    <col min="23" max="23" width="10.83203125" style="6"/>
-    <col min="24" max="24" width="14.83203125" style="6" customWidth="1"/>
-    <col min="25" max="16384" width="10.83203125" style="6"/>
+    <col min="18" max="18" width="39.1640625" style="13" customWidth="1"/>
+    <col min="19" max="19" width="15.83203125" style="10" customWidth="1"/>
+    <col min="20" max="20" width="10.5" style="10" customWidth="1"/>
+    <col min="21" max="21" width="42.5" style="13" customWidth="1"/>
+    <col min="22" max="22" width="21.83203125" style="6" customWidth="1"/>
+    <col min="23" max="23" width="19.1640625" style="6" customWidth="1"/>
+    <col min="24" max="24" width="10.83203125" style="6"/>
+    <col min="25" max="25" width="14.83203125" style="6" customWidth="1"/>
+    <col min="26" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="5" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4551,18 +4650,27 @@
       <c r="Q1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="14" t="s">
+        <v>730</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="U1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="W1" s="6"/>
-    </row>
-    <row r="2" spans="1:23" ht="85" x14ac:dyDescent="0.2">
+      <c r="V1" s="36" t="s">
+        <v>756</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="X1" s="6"/>
+    </row>
+    <row r="2" spans="1:24" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>81</v>
       </c>
@@ -4590,10 +4698,16 @@
         <v>ci-c-conf-1</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>731</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>85</v>
       </c>
@@ -4621,10 +4735,16 @@
         <v>ci-c-conf-2</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>88</v>
       </c>
@@ -4652,10 +4772,16 @@
         <v>ci-c-conf-3</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>92</v>
       </c>
@@ -4683,10 +4809,10 @@
         <v>ci-c-conf-4</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="34" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>95</v>
       </c>
@@ -4714,10 +4840,16 @@
         <v>ci-c-conf-5</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="85" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>98</v>
       </c>
@@ -4745,10 +4877,16 @@
         <v>ci-c-conf-6</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>101</v>
       </c>
@@ -4776,10 +4914,10 @@
         <v>ci-c-conf-7</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="102" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>104</v>
       </c>
@@ -4807,10 +4945,13 @@
         <v>ci-c-conf-8</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>108</v>
       </c>
@@ -4838,10 +4979,13 @@
         <v>ci-c-conf-9</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="170" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="170" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>111</v>
       </c>
@@ -4869,10 +5013,13 @@
         <v>ci-c-conf-10</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>115</v>
       </c>
@@ -4900,10 +5047,10 @@
         <v>ci-c-conf-11</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="153" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>118</v>
       </c>
@@ -4931,10 +5078,19 @@
         <v>ci-c-conf-12</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="W13" s="6" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>121</v>
       </c>
@@ -4962,10 +5118,16 @@
         <v>ci-c-conf-13</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R14" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="136" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>124</v>
       </c>
@@ -4993,10 +5155,16 @@
         <v>ci-c-conf-14</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>734</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>128</v>
       </c>
@@ -5024,10 +5192,16 @@
         <v>ci-c-conf-15</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>734</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>131</v>
       </c>
@@ -5055,10 +5229,10 @@
         <v>ci-c-opcn-1</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>134</v>
       </c>
@@ -5086,10 +5260,10 @@
         <v>ci-c-opcn-2</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>137</v>
       </c>
@@ -5117,21 +5291,27 @@
         <v>ci-c-oper-1</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>731</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>141</v>
-      </c>
       <c r="C20" s="8" t="s">
-        <v>142</v>
+        <v>737</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>91</v>
@@ -5148,21 +5328,21 @@
         <v>ci-c-oper-2</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>144</v>
+        <v>736</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>146</v>
+        <v>738</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>91</v>
@@ -5176,24 +5356,30 @@
       </c>
       <c r="N21" s="9" t="str" cm="1">
         <f t="array" ref="N21">SECTION_NAME(B21)</f>
-        <v>ci-c-oper-3</v>
+        <v>ci-c-oper-2</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>739</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>91</v>
@@ -5203,31 +5389,31 @@
       </c>
       <c r="M22" s="9" t="str" cm="1">
         <f t="array" ref="M22">PAGE_NAME(B22)</f>
-        <v>OperationDefinition-DTR-ValueSet-expand</v>
+        <v>OperationDefinition-log-questionnaire-errors</v>
       </c>
       <c r="N22" s="9" t="str" cm="1">
         <f t="array" ref="N22">SECTION_NAME(B22)</f>
-        <v>ci-c-oper-4</v>
+        <v>ci-c-oper-3</v>
       </c>
       <c r="P22" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G23" s="8" t="b">
         <v>0</v>
@@ -5238,61 +5424,67 @@
       </c>
       <c r="N23" s="9" t="str" cm="1">
         <f t="array" ref="N23">SECTION_NAME(B23)</f>
-        <v>ci-c-oper-5</v>
+        <v>ci-c-oper-4</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>731</v>
+      </c>
+      <c r="V23" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G24" s="8" t="b">
         <v>0</v>
       </c>
       <c r="M24" s="9" t="str" cm="1">
         <f t="array" ref="M24">PAGE_NAME(B24)</f>
-        <v>OperationDefinition-questionnaire-package</v>
+        <v>OperationDefinition-DTR-ValueSet-expand</v>
       </c>
       <c r="N24" s="9" t="str" cm="1">
         <f t="array" ref="N24">SECTION_NAME(B24)</f>
-        <v>ci-c-oper-6</v>
+        <v>ci-c-oper-5</v>
       </c>
       <c r="P24" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>157</v>
+        <v>151</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G25" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="9" t="str" cm="1">
         <f t="array" ref="M25">PAGE_NAME(B25)</f>
@@ -5300,21 +5492,27 @@
       </c>
       <c r="N25" s="9" t="str" cm="1">
         <f t="array" ref="N25">SECTION_NAME(B25)</f>
-        <v>ci-c-oper-7</v>
+        <v>ci-c-oper-6</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R25" s="13" t="s">
+        <v>740</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>26</v>
@@ -5331,21 +5529,21 @@
       </c>
       <c r="N26" s="9" t="str" cm="1">
         <f t="array" ref="N26">SECTION_NAME(B26)</f>
-        <v>ci-c-oper-8</v>
+        <v>ci-c-oper-7</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>26</v>
@@ -5362,21 +5560,21 @@
       </c>
       <c r="N27" s="9" t="str" cm="1">
         <f t="array" ref="N27">SECTION_NAME(B27)</f>
-        <v>ci-c-oper-9</v>
+        <v>ci-c-oper-8</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>26</v>
@@ -5393,24 +5591,24 @@
       </c>
       <c r="N28" s="9" t="str" cm="1">
         <f t="array" ref="N28">SECTION_NAME(B28)</f>
-        <v>ci-c-oper-10</v>
+        <v>ci-c-oper-9</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>107</v>
@@ -5424,30 +5622,30 @@
       </c>
       <c r="N29" s="9" t="str" cm="1">
         <f t="array" ref="N29">SECTION_NAME(B29)</f>
-        <v>ci-c-oper-11</v>
+        <v>ci-c-oper-10</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G30" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="9" t="str" cm="1">
         <f t="array" ref="M30">PAGE_NAME(B30)</f>
@@ -5455,21 +5653,21 @@
       </c>
       <c r="N30" s="9" t="str" cm="1">
         <f t="array" ref="N30">SECTION_NAME(B30)</f>
-        <v>ci-c-oper-12</v>
+        <v>ci-c-oper-11</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>26</v>
@@ -5486,21 +5684,21 @@
       </c>
       <c r="N31" s="9" t="str" cm="1">
         <f t="array" ref="N31">SECTION_NAME(B31)</f>
-        <v>ci-c-oper-13</v>
+        <v>ci-c-oper-12</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>26</v>
@@ -5517,21 +5715,21 @@
       </c>
       <c r="N32" s="9" t="str" cm="1">
         <f t="array" ref="N32">SECTION_NAME(B32)</f>
-        <v>ci-c-oper-14</v>
+        <v>ci-c-oper-13</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>26</v>
@@ -5548,21 +5746,21 @@
       </c>
       <c r="N33" s="9" t="str" cm="1">
         <f t="array" ref="N33">SECTION_NAME(B33)</f>
-        <v>ci-c-oper-15</v>
+        <v>ci-c-oper-14</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>26</v>
@@ -5579,24 +5777,24 @@
       </c>
       <c r="N34" s="9" t="str" cm="1">
         <f t="array" ref="N34">SECTION_NAME(B34)</f>
-        <v>ci-c-oper-16</v>
+        <v>ci-c-oper-15</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>107</v>
@@ -5610,24 +5808,24 @@
       </c>
       <c r="N35" s="9" t="str" cm="1">
         <f t="array" ref="N35">SECTION_NAME(B35)</f>
-        <v>ci-c-oper-17</v>
+        <v>ci-c-oper-16</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>107</v>
@@ -5641,24 +5839,24 @@
       </c>
       <c r="N36" s="9" t="str" cm="1">
         <f t="array" ref="N36">SECTION_NAME(B36)</f>
-        <v>ci-c-oper-18</v>
+        <v>ci-c-oper-17</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>107</v>
@@ -5672,30 +5870,30 @@
       </c>
       <c r="N37" s="9" t="str" cm="1">
         <f t="array" ref="N37">SECTION_NAME(B37)</f>
-        <v>ci-c-oper-19</v>
+        <v>ci-c-oper-18</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G38" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="9" t="str" cm="1">
         <f t="array" ref="M38">PAGE_NAME(B38)</f>
@@ -5703,117 +5901,129 @@
       </c>
       <c r="N38" s="9" t="str" cm="1">
         <f t="array" ref="N38">SECTION_NAME(B38)</f>
-        <v>ci-c-oper-20</v>
+        <v>ci-c-oper-19</v>
       </c>
       <c r="P38" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G39" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="9" t="str" cm="1">
         <f t="array" ref="M39">PAGE_NAME(B39)</f>
-        <v>StructureDefinition-dtr-qpackage-input-parameters</v>
+        <v>OperationDefinition-questionnaire-package</v>
       </c>
       <c r="N39" s="9" t="str" cm="1">
         <f t="array" ref="N39">SECTION_NAME(B39)</f>
-        <v>ci-c-prof-1</v>
+        <v>ci-c-oper-20</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>741</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G40" s="8" t="b">
         <v>0</v>
       </c>
       <c r="M40" s="9" t="str" cm="1">
         <f t="array" ref="M40">PAGE_NAME(B40)</f>
-        <v>StructureDefinition-dtr-supported-Payers</v>
+        <v>StructureDefinition-dtr-qpackage-input-parameters</v>
       </c>
       <c r="N40" s="9" t="str" cm="1">
         <f t="array" ref="N40">SECTION_NAME(B40)</f>
-        <v>ci-c-prof-2</v>
+        <v>ci-c-prof-1</v>
       </c>
       <c r="P40" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G41" s="8" t="b">
         <v>0</v>
       </c>
       <c r="M41" s="9" t="str" cm="1">
         <f t="array" ref="M41">PAGE_NAME(B41)</f>
-        <v>security</v>
+        <v>StructureDefinition-dtr-supported-Payers</v>
       </c>
       <c r="N41" s="9" t="str" cm="1">
         <f t="array" ref="N41">SECTION_NAME(B41)</f>
-        <v>ci-c-sec-1</v>
+        <v>ci-c-prof-2</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R41" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="V41" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>84</v>
@@ -5827,27 +6037,30 @@
       </c>
       <c r="N42" s="9" t="str" cm="1">
         <f t="array" ref="N42">SECTION_NAME(B42)</f>
-        <v>ci-c-sec-2</v>
+        <v>ci-c-sec-1</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R42" s="13" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G43" s="8" t="b">
         <v>0</v>
@@ -5858,24 +6071,24 @@
       </c>
       <c r="N43" s="9" t="str" cm="1">
         <f t="array" ref="N43">SECTION_NAME(B43)</f>
-        <v>ci-c-sec-3</v>
+        <v>ci-c-sec-2</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>107</v>
@@ -5889,27 +6102,27 @@
       </c>
       <c r="N44" s="9" t="str" cm="1">
         <f t="array" ref="N44">SECTION_NAME(B44)</f>
-        <v>ci-c-sec-4</v>
+        <v>ci-c-sec-3</v>
       </c>
       <c r="P44" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>217</v>
+        <v>42</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G45" s="8" t="b">
         <v>0</v>
@@ -5920,24 +6133,24 @@
       </c>
       <c r="N45" s="9" t="str" cm="1">
         <f t="array" ref="N45">SECTION_NAME(B45)</f>
-        <v>ci-c-sec-5</v>
+        <v>ci-c-sec-4</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>91</v>
@@ -5951,21 +6164,24 @@
       </c>
       <c r="N46" s="9" t="str" cm="1">
         <f t="array" ref="N46">SECTION_NAME(B46)</f>
-        <v>ci-c-sec-6</v>
+        <v>ci-c-sec-5</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R46" s="13" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>29</v>
@@ -5982,24 +6198,24 @@
       </c>
       <c r="N47" s="9" t="str" cm="1">
         <f t="array" ref="N47">SECTION_NAME(B47)</f>
-        <v>ci-c-sec-7</v>
+        <v>ci-c-sec-6</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>91</v>
@@ -6013,27 +6229,27 @@
       </c>
       <c r="N48" s="9" t="str" cm="1">
         <f t="array" ref="N48">SECTION_NAME(B48)</f>
-        <v>ci-c-sec-8</v>
+        <v>ci-c-sec-7</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G49" s="8" t="b">
         <v>0</v>
@@ -6044,30 +6260,30 @@
       </c>
       <c r="N49" s="9" t="str" cm="1">
         <f t="array" ref="N49">SECTION_NAME(B49)</f>
-        <v>ci-c-sec-9</v>
+        <v>ci-c-sec-8</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G50" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="9" t="str" cm="1">
         <f t="array" ref="M50">PAGE_NAME(B50)</f>
@@ -6075,58 +6291,58 @@
       </c>
       <c r="N50" s="9" t="str" cm="1">
         <f t="array" ref="N50">SECTION_NAME(B50)</f>
-        <v>ci-c-sec-10</v>
+        <v>ci-c-sec-9</v>
       </c>
       <c r="P50" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G51" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="9" t="str" cm="1">
         <f t="array" ref="M51">PAGE_NAME(B51)</f>
-        <v>specification</v>
+        <v>security</v>
       </c>
       <c r="N51" s="9" t="str" cm="1">
         <f t="array" ref="N51">SECTION_NAME(B51)</f>
-        <v>ci-c-spec-1</v>
+        <v>ci-c-sec-10</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G52" s="8" t="b">
         <v>0</v>
@@ -6137,21 +6353,21 @@
       </c>
       <c r="N52" s="9" t="str" cm="1">
         <f t="array" ref="N52">SECTION_NAME(B52)</f>
-        <v>ci-c-spec-2</v>
+        <v>ci-c-spec-1</v>
       </c>
       <c r="P52" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>30</v>
@@ -6160,7 +6376,7 @@
         <v>91</v>
       </c>
       <c r="G53" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="9" t="str" cm="1">
         <f t="array" ref="M53">PAGE_NAME(B53)</f>
@@ -6168,30 +6384,30 @@
       </c>
       <c r="N53" s="9" t="str" cm="1">
         <f t="array" ref="N53">SECTION_NAME(B53)</f>
-        <v>ci-c-spec-3</v>
+        <v>ci-c-spec-2</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G54" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="9" t="str" cm="1">
         <f t="array" ref="M54">PAGE_NAME(B54)</f>
@@ -6199,27 +6415,27 @@
       </c>
       <c r="N54" s="9" t="str" cm="1">
         <f t="array" ref="N54">SECTION_NAME(B54)</f>
-        <v>ci-c-spec-4</v>
+        <v>ci-c-spec-3</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G55" s="8" t="b">
         <v>0</v>
@@ -6230,24 +6446,27 @@
       </c>
       <c r="N55" s="9" t="str" cm="1">
         <f t="array" ref="N55">SECTION_NAME(B55)</f>
-        <v>ci-c-spec-5</v>
+        <v>ci-c-spec-4</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+      <c r="R55" s="13" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>107</v>
@@ -6261,27 +6480,27 @@
       </c>
       <c r="N56" s="9" t="str" cm="1">
         <f t="array" ref="N56">SECTION_NAME(B56)</f>
-        <v>ci-c-spec-6</v>
+        <v>ci-c-spec-5</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G57" s="8" t="b">
         <v>0</v>
@@ -6292,24 +6511,24 @@
       </c>
       <c r="N57" s="9" t="str" cm="1">
         <f t="array" ref="N57">SECTION_NAME(B57)</f>
-        <v>ci-c-spec-7</v>
+        <v>ci-c-spec-6</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>84</v>
@@ -6323,24 +6542,27 @@
       </c>
       <c r="N58" s="9" t="str" cm="1">
         <f t="array" ref="N58">SECTION_NAME(B58)</f>
-        <v>ci-c-spec-8</v>
+        <v>ci-c-spec-7</v>
       </c>
       <c r="P58" s="10" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+      <c r="R58" s="13" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>258</v>
+        <v>29</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>84</v>
@@ -6354,27 +6576,27 @@
       </c>
       <c r="N59" s="9" t="str" cm="1">
         <f t="array" ref="N59">SECTION_NAME(B59)</f>
-        <v>ci-c-spec-9</v>
+        <v>ci-c-spec-8</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>30</v>
+        <v>256</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G60" s="8" t="b">
         <v>0</v>
@@ -6385,27 +6607,27 @@
       </c>
       <c r="N60" s="9" t="str" cm="1">
         <f t="array" ref="N60">SECTION_NAME(B60)</f>
-        <v>ci-c-spec-10</v>
+        <v>ci-c-spec-9</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G61" s="8" t="b">
         <v>0</v>
@@ -6416,27 +6638,27 @@
       </c>
       <c r="N61" s="9" t="str" cm="1">
         <f t="array" ref="N61">SECTION_NAME(B61)</f>
-        <v>ci-c-spec-11</v>
+        <v>ci-c-spec-10</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>268</v>
+        <v>26</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G62" s="8" t="b">
         <v>0</v>
@@ -6447,24 +6669,27 @@
       </c>
       <c r="N62" s="9" t="str" cm="1">
         <f t="array" ref="N62">SECTION_NAME(B62)</f>
-        <v>ci-c-spec-12</v>
+        <v>ci-c-spec-11</v>
       </c>
       <c r="P62" s="10" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+      <c r="R62" s="13" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>107</v>
@@ -6478,27 +6703,27 @@
       </c>
       <c r="N63" s="9" t="str" cm="1">
         <f t="array" ref="N63">SECTION_NAME(B63)</f>
-        <v>ci-c-spec-13</v>
+        <v>ci-c-spec-12</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G64" s="8" t="b">
         <v>0</v>
@@ -6509,27 +6734,27 @@
       </c>
       <c r="N64" s="9" t="str" cm="1">
         <f t="array" ref="N64">SECTION_NAME(B64)</f>
-        <v>ci-c-spec-14</v>
+        <v>ci-c-spec-13</v>
       </c>
       <c r="P64" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G65" s="8" t="b">
         <v>0</v>
@@ -6540,27 +6765,30 @@
       </c>
       <c r="N65" s="9" t="str" cm="1">
         <f t="array" ref="N65">SECTION_NAME(B65)</f>
-        <v>ci-c-spec-15</v>
+        <v>ci-c-spec-14</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R65" s="13" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G66" s="8" t="b">
         <v>0</v>
@@ -6571,27 +6799,27 @@
       </c>
       <c r="N66" s="9" t="str" cm="1">
         <f t="array" ref="N66">SECTION_NAME(B66)</f>
-        <v>ci-c-spec-16</v>
+        <v>ci-c-spec-15</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G67" s="8" t="b">
         <v>0</v>
@@ -6602,21 +6830,24 @@
       </c>
       <c r="N67" s="9" t="str" cm="1">
         <f t="array" ref="N67">SECTION_NAME(B67)</f>
-        <v>ci-c-spec-17</v>
+        <v>ci-c-spec-16</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R67" s="13" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>26</v>
@@ -6625,7 +6856,7 @@
         <v>107</v>
       </c>
       <c r="G68" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="9" t="str" cm="1">
         <f t="array" ref="M68">PAGE_NAME(B68)</f>
@@ -6633,30 +6864,30 @@
       </c>
       <c r="N68" s="9" t="str" cm="1">
         <f t="array" ref="N68">SECTION_NAME(B68)</f>
-        <v>ci-c-spec-18</v>
+        <v>ci-c-spec-17</v>
       </c>
       <c r="P68" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G69" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="9" t="str" cm="1">
         <f t="array" ref="M69">PAGE_NAME(B69)</f>
@@ -6664,24 +6895,24 @@
       </c>
       <c r="N69" s="9" t="str" cm="1">
         <f t="array" ref="N69">SECTION_NAME(B69)</f>
-        <v>ci-c-spec-19</v>
+        <v>ci-c-spec-18</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>91</v>
@@ -6695,27 +6926,30 @@
       </c>
       <c r="N70" s="9" t="str" cm="1">
         <f t="array" ref="N70">SECTION_NAME(B70)</f>
-        <v>ci-c-spec-20</v>
+        <v>ci-c-spec-19</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R70" s="13" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G71" s="8" t="b">
         <v>0</v>
@@ -6726,30 +6960,33 @@
       </c>
       <c r="N71" s="9" t="str" cm="1">
         <f t="array" ref="N71">SECTION_NAME(B71)</f>
-        <v>ci-c-spec-21</v>
+        <v>ci-c-spec-20</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R71" s="13" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G72" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="9" t="str" cm="1">
         <f t="array" ref="M72">PAGE_NAME(B72)</f>
@@ -6757,21 +6994,21 @@
       </c>
       <c r="N72" s="9" t="str" cm="1">
         <f t="array" ref="N72">SECTION_NAME(B72)</f>
-        <v>ci-c-spec-22</v>
+        <v>ci-c-spec-21</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>26</v>
@@ -6788,21 +7025,21 @@
       </c>
       <c r="N73" s="9" t="str" cm="1">
         <f t="array" ref="N73">SECTION_NAME(B73)</f>
-        <v>ci-c-spec-23</v>
+        <v>ci-c-spec-22</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>26</v>
@@ -6819,21 +7056,21 @@
       </c>
       <c r="N74" s="9" t="str" cm="1">
         <f t="array" ref="N74">SECTION_NAME(B74)</f>
-        <v>ci-c-spec-24</v>
+        <v>ci-c-spec-23</v>
       </c>
       <c r="P74" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>26</v>
@@ -6842,7 +7079,7 @@
         <v>107</v>
       </c>
       <c r="G75" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="9" t="str" cm="1">
         <f t="array" ref="M75">PAGE_NAME(B75)</f>
@@ -6850,24 +7087,24 @@
       </c>
       <c r="N75" s="9" t="str" cm="1">
         <f t="array" ref="N75">SECTION_NAME(B75)</f>
-        <v>ci-c-spec-25</v>
+        <v>ci-c-spec-24</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>304</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>107</v>
@@ -6881,21 +7118,21 @@
       </c>
       <c r="N76" s="9" t="str" cm="1">
         <f t="array" ref="N76">SECTION_NAME(B76)</f>
-        <v>ci-c-spec-26</v>
+        <v>ci-c-spec-25</v>
       </c>
       <c r="P76" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>30</v>
@@ -6912,21 +7149,21 @@
       </c>
       <c r="N77" s="9" t="str" cm="1">
         <f t="array" ref="N77">SECTION_NAME(B77)</f>
-        <v>ci-c-spec-27</v>
+        <v>ci-c-spec-26</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>30</v>
@@ -6943,21 +7180,21 @@
       </c>
       <c r="N78" s="9" t="str" cm="1">
         <f t="array" ref="N78">SECTION_NAME(B78)</f>
-        <v>ci-c-spec-28</v>
+        <v>ci-c-spec-27</v>
       </c>
       <c r="P78" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>30</v>
@@ -6974,21 +7211,21 @@
       </c>
       <c r="N79" s="9" t="str" cm="1">
         <f t="array" ref="N79">SECTION_NAME(B79)</f>
-        <v>ci-c-spec-29</v>
+        <v>ci-c-spec-28</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="187" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>30</v>
@@ -7005,21 +7242,21 @@
       </c>
       <c r="N80" s="9" t="str" cm="1">
         <f t="array" ref="N80">SECTION_NAME(B80)</f>
-        <v>ci-c-spec-30</v>
+        <v>ci-c-spec-29</v>
       </c>
       <c r="P80" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="187" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>30</v>
@@ -7036,30 +7273,30 @@
       </c>
       <c r="N81" s="9" t="str" cm="1">
         <f t="array" ref="N81">SECTION_NAME(B81)</f>
-        <v>ci-c-spec-31</v>
+        <v>ci-c-spec-30</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G82" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="9" t="str" cm="1">
         <f t="array" ref="M82">PAGE_NAME(B82)</f>
@@ -7067,24 +7304,24 @@
       </c>
       <c r="N82" s="9" t="str" cm="1">
         <f t="array" ref="N82">SECTION_NAME(B82)</f>
-        <v>ci-c-spec-32</v>
+        <v>ci-c-spec-31</v>
       </c>
       <c r="P82" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>107</v>
@@ -7098,24 +7335,24 @@
       </c>
       <c r="N83" s="9" t="str" cm="1">
         <f t="array" ref="N83">SECTION_NAME(B83)</f>
-        <v>ci-c-spec-33</v>
+        <v>ci-c-spec-32</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>107</v>
@@ -7129,27 +7366,27 @@
       </c>
       <c r="N84" s="9" t="str" cm="1">
         <f t="array" ref="N84">SECTION_NAME(B84)</f>
-        <v>ci-c-spec-34</v>
+        <v>ci-c-spec-33</v>
       </c>
       <c r="P84" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A85" s="7" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G85" s="8" t="b">
         <v>1</v>
@@ -7160,27 +7397,27 @@
       </c>
       <c r="N85" s="9" t="str" cm="1">
         <f t="array" ref="N85">SECTION_NAME(B85)</f>
-        <v>ci-c-spec-35</v>
+        <v>ci-c-spec-34</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G86" s="8" t="b">
         <v>1</v>
@@ -7191,27 +7428,30 @@
       </c>
       <c r="N86" s="9" t="str" cm="1">
         <f t="array" ref="N86">SECTION_NAME(B86)</f>
-        <v>ci-c-spec-36</v>
+        <v>ci-c-spec-35</v>
       </c>
       <c r="P86" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R86" s="13" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G87" s="8" t="b">
         <v>1</v>
@@ -7222,30 +7462,30 @@
       </c>
       <c r="N87" s="9" t="str" cm="1">
         <f t="array" ref="N87">SECTION_NAME(B87)</f>
-        <v>ci-c-spec-37</v>
+        <v>ci-c-spec-36</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G88" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="9" t="str" cm="1">
         <f t="array" ref="M88">PAGE_NAME(B88)</f>
@@ -7253,21 +7493,21 @@
       </c>
       <c r="N88" s="9" t="str" cm="1">
         <f t="array" ref="N88">SECTION_NAME(B88)</f>
-        <v>ci-c-spec-38</v>
+        <v>ci-c-spec-37</v>
       </c>
       <c r="P88" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>26</v>
@@ -7276,7 +7516,7 @@
         <v>107</v>
       </c>
       <c r="G89" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="9" t="str" cm="1">
         <f t="array" ref="M89">PAGE_NAME(B89)</f>
@@ -7284,30 +7524,30 @@
       </c>
       <c r="N89" s="9" t="str" cm="1">
         <f t="array" ref="N89">SECTION_NAME(B89)</f>
-        <v>ci-c-spec-39</v>
+        <v>ci-c-spec-38</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G90" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="9" t="str" cm="1">
         <f t="array" ref="M90">PAGE_NAME(B90)</f>
@@ -7315,30 +7555,30 @@
       </c>
       <c r="N90" s="9" t="str" cm="1">
         <f t="array" ref="N90">SECTION_NAME(B90)</f>
-        <v>ci-c-spec-40</v>
+        <v>ci-c-spec-39</v>
       </c>
       <c r="P90" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G91" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="9" t="str" cm="1">
         <f t="array" ref="M91">PAGE_NAME(B91)</f>
@@ -7346,30 +7586,30 @@
       </c>
       <c r="N91" s="9" t="str" cm="1">
         <f t="array" ref="N91">SECTION_NAME(B91)</f>
-        <v>ci-c-spec-41</v>
+        <v>ci-c-spec-40</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G92" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="9" t="str" cm="1">
         <f t="array" ref="M92">PAGE_NAME(B92)</f>
@@ -7377,24 +7617,24 @@
       </c>
       <c r="N92" s="9" t="str" cm="1">
         <f t="array" ref="N92">SECTION_NAME(B92)</f>
-        <v>ci-c-spec-42</v>
+        <v>ci-c-spec-41</v>
       </c>
       <c r="P92" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>107</v>
@@ -7408,30 +7648,30 @@
       </c>
       <c r="N93" s="9" t="str" cm="1">
         <f t="array" ref="N93">SECTION_NAME(B93)</f>
-        <v>ci-c-spec-43</v>
+        <v>ci-c-spec-42</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G94" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="9" t="str" cm="1">
         <f t="array" ref="M94">PAGE_NAME(B94)</f>
@@ -7439,27 +7679,27 @@
       </c>
       <c r="N94" s="9" t="str" cm="1">
         <f t="array" ref="N94">SECTION_NAME(B94)</f>
-        <v>ci-c-spec-44</v>
+        <v>ci-c-spec-43</v>
       </c>
       <c r="P94" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A95" s="7" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G95" s="8" t="b">
         <v>1</v>
@@ -7470,27 +7710,30 @@
       </c>
       <c r="N95" s="9" t="str" cm="1">
         <f t="array" ref="N95">SECTION_NAME(B95)</f>
-        <v>ci-c-spec-45</v>
+        <v>ci-c-spec-44</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R95" s="13" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A96" s="7" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>369</v>
+        <v>32</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G96" s="8" t="b">
         <v>1</v>
@@ -7501,21 +7744,21 @@
       </c>
       <c r="N96" s="9" t="str" cm="1">
         <f t="array" ref="N96">SECTION_NAME(B96)</f>
-        <v>ci-c-spec-46</v>
+        <v>ci-c-spec-45</v>
       </c>
       <c r="P96" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>26</v>
@@ -7524,7 +7767,7 @@
         <v>91</v>
       </c>
       <c r="G97" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="9" t="str" cm="1">
         <f t="array" ref="M97">PAGE_NAME(B97)</f>
@@ -7532,24 +7775,27 @@
       </c>
       <c r="N97" s="9" t="str" cm="1">
         <f t="array" ref="N97">SECTION_NAME(B97)</f>
-        <v>ci-c-spec-47</v>
+        <v>ci-c-spec-46</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R97" s="13" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>91</v>
@@ -7563,30 +7809,33 @@
       </c>
       <c r="N98" s="9" t="str" cm="1">
         <f t="array" ref="N98">SECTION_NAME(B98)</f>
-        <v>ci-c-spec-48</v>
+        <v>ci-c-spec-47</v>
       </c>
       <c r="P98" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R98" s="13" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A99" s="7" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G99" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" s="9" t="str" cm="1">
         <f t="array" ref="M99">PAGE_NAME(B99)</f>
@@ -7594,30 +7843,30 @@
       </c>
       <c r="N99" s="9" t="str" cm="1">
         <f t="array" ref="N99">SECTION_NAME(B99)</f>
-        <v>ci-c-spec-49</v>
+        <v>ci-c-spec-48</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G100" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="9" t="str" cm="1">
         <f t="array" ref="M100">PAGE_NAME(B100)</f>
@@ -7625,30 +7874,33 @@
       </c>
       <c r="N100" s="9" t="str" cm="1">
         <f t="array" ref="N100">SECTION_NAME(B100)</f>
-        <v>ci-c-spec-50</v>
+        <v>ci-c-spec-49</v>
       </c>
       <c r="P100" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R100" s="13" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>35</v>
+        <v>379</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G101" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" s="9" t="str" cm="1">
         <f t="array" ref="M101">PAGE_NAME(B101)</f>
@@ -7656,30 +7908,30 @@
       </c>
       <c r="N101" s="9" t="str" cm="1">
         <f t="array" ref="N101">SECTION_NAME(B101)</f>
-        <v>ci-c-spec-51</v>
+        <v>ci-c-spec-50</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>386</v>
+        <v>35</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E102" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G102" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="9" t="str" cm="1">
         <f t="array" ref="M102">PAGE_NAME(B102)</f>
@@ -7687,24 +7939,24 @@
       </c>
       <c r="N102" s="9" t="str" cm="1">
         <f t="array" ref="N102">SECTION_NAME(B102)</f>
-        <v>ci-c-spec-52</v>
+        <v>ci-c-spec-51</v>
       </c>
       <c r="P102" s="10" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E103" s="8" t="s">
         <v>107</v>
@@ -7718,24 +7970,24 @@
       </c>
       <c r="N103" s="9" t="str" cm="1">
         <f t="array" ref="N103">SECTION_NAME(B103)</f>
-        <v>ci-c-spec-53</v>
+        <v>ci-c-spec-52</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>33</v>
+        <v>387</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E104" s="8" t="s">
         <v>107</v>
@@ -7749,24 +8001,24 @@
       </c>
       <c r="N104" s="9" t="str" cm="1">
         <f t="array" ref="N104">SECTION_NAME(B104)</f>
-        <v>ci-c-spec-54</v>
+        <v>ci-c-spec-53</v>
       </c>
       <c r="P104" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>394</v>
+        <v>33</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>107</v>
@@ -7780,21 +8032,21 @@
       </c>
       <c r="N105" s="9" t="str" cm="1">
         <f t="array" ref="N105">SECTION_NAME(B105)</f>
-        <v>ci-c-spec-55</v>
+        <v>ci-c-spec-54</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>34</v>
+        <v>392</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>29</v>
@@ -7811,27 +8063,27 @@
       </c>
       <c r="N106" s="9" t="str" cm="1">
         <f t="array" ref="N106">SECTION_NAME(B106)</f>
-        <v>ci-c-spec-56</v>
+        <v>ci-c-spec-55</v>
       </c>
       <c r="P106" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>399</v>
+        <v>34</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G107" s="8" t="b">
         <v>0</v>
@@ -7842,27 +8094,27 @@
       </c>
       <c r="N107" s="9" t="str" cm="1">
         <f t="array" ref="N107">SECTION_NAME(B107)</f>
-        <v>ci-c-spec-57</v>
+        <v>ci-c-spec-56</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G108" s="8" t="b">
         <v>0</v>
@@ -7873,27 +8125,27 @@
       </c>
       <c r="N108" s="9" t="str" cm="1">
         <f t="array" ref="N108">SECTION_NAME(B108)</f>
-        <v>ci-c-spec-58</v>
+        <v>ci-c-spec-57</v>
       </c>
       <c r="P108" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G109" s="8" t="b">
         <v>0</v>
@@ -7904,21 +8156,21 @@
       </c>
       <c r="N109" s="9" t="str" cm="1">
         <f t="array" ref="N109">SECTION_NAME(B109)</f>
-        <v>ci-c-spec-59</v>
+        <v>ci-c-spec-58</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A110" s="7" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>26</v>
@@ -7935,27 +8187,27 @@
       </c>
       <c r="N110" s="9" t="str" cm="1">
         <f t="array" ref="N110">SECTION_NAME(B110)</f>
-        <v>ci-c-spec-60</v>
+        <v>ci-c-spec-59</v>
       </c>
       <c r="P110" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G111" s="8" t="b">
         <v>0</v>
@@ -7966,27 +8218,27 @@
       </c>
       <c r="N111" s="9" t="str" cm="1">
         <f t="array" ref="N111">SECTION_NAME(B111)</f>
-        <v>ci-c-spec-61</v>
+        <v>ci-c-spec-60</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="238" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A112" s="7" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G112" s="8" t="b">
         <v>0</v>
@@ -7997,24 +8249,24 @@
       </c>
       <c r="N112" s="9" t="str" cm="1">
         <f t="array" ref="N112">SECTION_NAME(B112)</f>
-        <v>ci-c-spec-62</v>
+        <v>ci-c-spec-61</v>
       </c>
       <c r="P112" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="238" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E113" s="8" t="s">
         <v>91</v>
@@ -8028,24 +8280,24 @@
       </c>
       <c r="N113" s="9" t="str" cm="1">
         <f t="array" ref="N113">SECTION_NAME(B113)</f>
-        <v>ci-c-spec-63</v>
+        <v>ci-c-spec-62</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>91</v>
@@ -8059,21 +8311,21 @@
       </c>
       <c r="N114" s="9" t="str" cm="1">
         <f t="array" ref="N114">SECTION_NAME(B114)</f>
-        <v>ci-c-spec-64</v>
+        <v>ci-c-spec-63</v>
       </c>
       <c r="P114" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>26</v>
@@ -8082,7 +8334,7 @@
         <v>91</v>
       </c>
       <c r="G115" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" s="9" t="str" cm="1">
         <f t="array" ref="M115">PAGE_NAME(B115)</f>
@@ -8090,21 +8342,21 @@
       </c>
       <c r="N115" s="9" t="str" cm="1">
         <f t="array" ref="N115">SECTION_NAME(B115)</f>
-        <v>ci-c-spec-65</v>
+        <v>ci-c-spec-64</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>26</v>
@@ -8113,7 +8365,7 @@
         <v>91</v>
       </c>
       <c r="G116" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="9" t="str" cm="1">
         <f t="array" ref="M116">PAGE_NAME(B116)</f>
@@ -8121,21 +8373,21 @@
       </c>
       <c r="N116" s="9" t="str" cm="1">
         <f t="array" ref="N116">SECTION_NAME(B116)</f>
-        <v>ci-c-spec-66</v>
+        <v>ci-c-spec-65</v>
       </c>
       <c r="P116" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A117" s="7" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>730</v>
+        <v>424</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>26</v>
@@ -8144,7 +8396,7 @@
         <v>91</v>
       </c>
       <c r="G117" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="9" t="str" cm="1">
         <f t="array" ref="M117">PAGE_NAME(B117)</f>
@@ -8152,21 +8404,21 @@
       </c>
       <c r="N117" s="9" t="str" cm="1">
         <f t="array" ref="N117">SECTION_NAME(B117)</f>
-        <v>ci-c-spec-67</v>
+        <v>ci-c-spec-66</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A118" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>431</v>
+        <v>728</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>26</v>
@@ -8183,30 +8435,30 @@
       </c>
       <c r="N118" s="9" t="str" cm="1">
         <f t="array" ref="N118">SECTION_NAME(B118)</f>
-        <v>ci-c-spec-68</v>
+        <v>ci-c-spec-67</v>
       </c>
       <c r="P118" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G119" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="9" t="str" cm="1">
         <f t="array" ref="M119">PAGE_NAME(B119)</f>
@@ -8214,24 +8466,24 @@
       </c>
       <c r="N119" s="9" t="str" cm="1">
         <f t="array" ref="N119">SECTION_NAME(B119)</f>
-        <v>ci-c-spec-69</v>
+        <v>ci-c-spec-68</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A120" s="7" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>91</v>
@@ -8245,30 +8497,30 @@
       </c>
       <c r="N120" s="9" t="str" cm="1">
         <f t="array" ref="N120">SECTION_NAME(B120)</f>
-        <v>ci-c-spec-70</v>
+        <v>ci-c-spec-69</v>
       </c>
       <c r="P120" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="102" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E121" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G121" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="9" t="str" cm="1">
         <f t="array" ref="M121">PAGE_NAME(B121)</f>
@@ -8276,24 +8528,24 @@
       </c>
       <c r="N121" s="9" t="str" cm="1">
         <f t="array" ref="N121">SECTION_NAME(B121)</f>
-        <v>ci-c-spec-71</v>
+        <v>ci-c-spec-70</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A122" s="7" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="E122" s="8" t="s">
         <v>91</v>
@@ -8307,24 +8559,24 @@
       </c>
       <c r="N122" s="9" t="str" cm="1">
         <f t="array" ref="N122">SECTION_NAME(B122)</f>
-        <v>ci-c-spec-72</v>
+        <v>ci-c-spec-71</v>
       </c>
       <c r="P122" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A123" s="7" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E123" s="8" t="s">
         <v>91</v>
@@ -8338,21 +8590,21 @@
       </c>
       <c r="N123" s="9" t="str" cm="1">
         <f t="array" ref="N123">SECTION_NAME(B123)</f>
-        <v>ci-c-spec-73</v>
+        <v>ci-c-spec-72</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>26</v>
@@ -8369,24 +8621,24 @@
       </c>
       <c r="N124" s="9" t="str" cm="1">
         <f t="array" ref="N124">SECTION_NAME(B124)</f>
-        <v>ci-c-spec-74</v>
+        <v>ci-c-spec-73</v>
       </c>
       <c r="P124" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E125" s="8" t="s">
         <v>91</v>
@@ -8400,24 +8652,24 @@
       </c>
       <c r="N125" s="9" t="str" cm="1">
         <f t="array" ref="N125">SECTION_NAME(B125)</f>
-        <v>ci-c-spec-75</v>
+        <v>ci-c-spec-74</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>91</v>
@@ -8431,24 +8683,24 @@
       </c>
       <c r="N126" s="9" t="str" cm="1">
         <f t="array" ref="N126">SECTION_NAME(B126)</f>
-        <v>ci-c-spec-76</v>
+        <v>ci-c-spec-75</v>
       </c>
       <c r="P126" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>91</v>
@@ -8462,30 +8714,30 @@
       </c>
       <c r="N127" s="9" t="str" cm="1">
         <f t="array" ref="N127">SECTION_NAME(B127)</f>
-        <v>ci-c-spec-77</v>
+        <v>ci-c-spec-76</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A128" s="7" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G128" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="9" t="str" cm="1">
         <f t="array" ref="M128">PAGE_NAME(B128)</f>
@@ -8493,21 +8745,21 @@
       </c>
       <c r="N128" s="9" t="str" cm="1">
         <f t="array" ref="N128">SECTION_NAME(B128)</f>
-        <v>ci-c-spec-78</v>
+        <v>ci-c-spec-77</v>
       </c>
       <c r="P128" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A129" s="7" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>26</v>
@@ -8516,7 +8768,7 @@
         <v>91</v>
       </c>
       <c r="G129" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" s="9" t="str" cm="1">
         <f t="array" ref="M129">PAGE_NAME(B129)</f>
@@ -8524,24 +8776,24 @@
       </c>
       <c r="N129" s="9" t="str" cm="1">
         <f t="array" ref="N129">SECTION_NAME(B129)</f>
-        <v>ci-c-spec-79</v>
+        <v>ci-c-spec-78</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A130" s="7" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E130" s="8" t="s">
         <v>91</v>
@@ -8555,24 +8807,24 @@
       </c>
       <c r="N130" s="9" t="str" cm="1">
         <f t="array" ref="N130">SECTION_NAME(B130)</f>
-        <v>ci-c-spec-80</v>
+        <v>ci-c-spec-79</v>
       </c>
       <c r="P130" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A131" s="7" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E131" s="8" t="s">
         <v>91</v>
@@ -8586,30 +8838,30 @@
       </c>
       <c r="N131" s="9" t="str" cm="1">
         <f t="array" ref="N131">SECTION_NAME(B131)</f>
-        <v>ci-c-spec-81</v>
+        <v>ci-c-spec-80</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A132" s="7" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E132" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G132" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="9" t="str" cm="1">
         <f t="array" ref="M132">PAGE_NAME(B132)</f>
@@ -8617,27 +8869,27 @@
       </c>
       <c r="N132" s="9" t="str" cm="1">
         <f t="array" ref="N132">SECTION_NAME(B132)</f>
-        <v>ci-c-spec-82</v>
+        <v>ci-c-spec-81</v>
       </c>
       <c r="P132" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A133" s="7" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G133" s="8" t="b">
         <v>0</v>
@@ -8648,27 +8900,27 @@
       </c>
       <c r="N133" s="9" t="str" cm="1">
         <f t="array" ref="N133">SECTION_NAME(B133)</f>
-        <v>ci-c-spec-83</v>
+        <v>ci-c-spec-82</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A134" s="7" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G134" s="8" t="b">
         <v>0</v>
@@ -8679,27 +8931,27 @@
       </c>
       <c r="N134" s="9" t="str" cm="1">
         <f t="array" ref="N134">SECTION_NAME(B134)</f>
-        <v>ci-c-spec-84</v>
+        <v>ci-c-spec-83</v>
       </c>
       <c r="P134" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A135" s="7" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G135" s="8" t="b">
         <v>0</v>
@@ -8710,24 +8962,24 @@
       </c>
       <c r="N135" s="9" t="str" cm="1">
         <f t="array" ref="N135">SECTION_NAME(B135)</f>
-        <v>ci-c-spec-85</v>
+        <v>ci-c-spec-84</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A136" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E136" s="8" t="s">
         <v>107</v>
@@ -8741,24 +8993,24 @@
       </c>
       <c r="N136" s="9" t="str" cm="1">
         <f t="array" ref="N136">SECTION_NAME(B136)</f>
-        <v>ci-c-spec-86</v>
+        <v>ci-c-spec-85</v>
       </c>
       <c r="P136" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A137" s="7" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E137" s="8" t="s">
         <v>107</v>
@@ -8772,24 +9024,24 @@
       </c>
       <c r="N137" s="9" t="str" cm="1">
         <f t="array" ref="N137">SECTION_NAME(B137)</f>
-        <v>ci-c-spec-87</v>
+        <v>ci-c-spec-86</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A138" s="7" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>258</v>
+        <v>26</v>
       </c>
       <c r="E138" s="8" t="s">
         <v>107</v>
@@ -8803,27 +9055,27 @@
       </c>
       <c r="N138" s="9" t="str" cm="1">
         <f t="array" ref="N138">SECTION_NAME(B138)</f>
-        <v>ci-c-spec-88</v>
+        <v>ci-c-spec-87</v>
       </c>
       <c r="P138" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A139" s="7" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>30</v>
+        <v>256</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G139" s="8" t="b">
         <v>0</v>
@@ -8834,27 +9086,27 @@
       </c>
       <c r="N139" s="9" t="str" cm="1">
         <f t="array" ref="N139">SECTION_NAME(B139)</f>
-        <v>ci-c-spec-89</v>
+        <v>ci-c-spec-88</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G140" s="8" t="b">
         <v>0</v>
@@ -8865,21 +9117,21 @@
       </c>
       <c r="N140" s="9" t="str" cm="1">
         <f t="array" ref="N140">SECTION_NAME(B140)</f>
-        <v>ci-c-spec-90</v>
+        <v>ci-c-spec-89</v>
       </c>
       <c r="P140" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A141" s="7" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>29</v>
@@ -8896,24 +9148,24 @@
       </c>
       <c r="N141" s="9" t="str" cm="1">
         <f t="array" ref="N141">SECTION_NAME(B141)</f>
-        <v>ci-c-spec-91</v>
+        <v>ci-c-spec-90</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E142" s="8" t="s">
         <v>107</v>
@@ -8927,21 +9179,21 @@
       </c>
       <c r="N142" s="9" t="str" cm="1">
         <f t="array" ref="N142">SECTION_NAME(B142)</f>
-        <v>ci-c-spec-92</v>
+        <v>ci-c-spec-91</v>
       </c>
       <c r="P142" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>26</v>
@@ -8958,21 +9210,21 @@
       </c>
       <c r="N143" s="9" t="str" cm="1">
         <f t="array" ref="N143">SECTION_NAME(B143)</f>
-        <v>ci-c-spec-93</v>
+        <v>ci-c-spec-92</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A144" s="7" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>26</v>
@@ -8989,21 +9241,21 @@
       </c>
       <c r="N144" s="9" t="str" cm="1">
         <f t="array" ref="N144">SECTION_NAME(B144)</f>
-        <v>ci-c-spec-94</v>
+        <v>ci-c-spec-93</v>
       </c>
       <c r="P144" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A145" s="7" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>26</v>
@@ -9020,21 +9272,21 @@
       </c>
       <c r="N145" s="9" t="str" cm="1">
         <f t="array" ref="N145">SECTION_NAME(B145)</f>
-        <v>ci-c-spec-95</v>
+        <v>ci-c-spec-94</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A146" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>26</v>
@@ -9051,21 +9303,21 @@
       </c>
       <c r="N146" s="9" t="str" cm="1">
         <f t="array" ref="N146">SECTION_NAME(B146)</f>
-        <v>ci-c-spec-96</v>
+        <v>ci-c-spec-95</v>
       </c>
       <c r="P146" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" ht="170" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>26</v>
@@ -9074,7 +9326,7 @@
         <v>107</v>
       </c>
       <c r="G147" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="9" t="str" cm="1">
         <f t="array" ref="M147">PAGE_NAME(B147)</f>
@@ -9082,30 +9334,30 @@
       </c>
       <c r="N147" s="9" t="str" cm="1">
         <f t="array" ref="N147">SECTION_NAME(B147)</f>
-        <v>ci-c-spec-97</v>
+        <v>ci-c-spec-96</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>268</v>
+        <v>26</v>
       </c>
       <c r="E148" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G148" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" s="9" t="str" cm="1">
         <f t="array" ref="M148">PAGE_NAME(B148)</f>
@@ -9113,24 +9365,24 @@
       </c>
       <c r="N148" s="9" t="str" cm="1">
         <f t="array" ref="N148">SECTION_NAME(B148)</f>
-        <v>ci-c-spec-98</v>
+        <v>ci-c-spec-97</v>
       </c>
       <c r="P148" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A149" s="7" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>26</v>
+        <v>266</v>
       </c>
       <c r="E149" s="8" t="s">
         <v>107</v>
@@ -9144,27 +9396,27 @@
       </c>
       <c r="N149" s="9" t="str" cm="1">
         <f t="array" ref="N149">SECTION_NAME(B149)</f>
-        <v>ci-c-spec-99</v>
+        <v>ci-c-spec-98</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G150" s="8" t="b">
         <v>0</v>
@@ -9175,30 +9427,30 @@
       </c>
       <c r="N150" s="9" t="str" cm="1">
         <f t="array" ref="N150">SECTION_NAME(B150)</f>
-        <v>ci-c-spec-100</v>
+        <v>ci-c-spec-99</v>
       </c>
       <c r="P150" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E151" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G151" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" s="9" t="str" cm="1">
         <f t="array" ref="M151">PAGE_NAME(B151)</f>
@@ -9206,21 +9458,21 @@
       </c>
       <c r="N151" s="9" t="str" cm="1">
         <f t="array" ref="N151">SECTION_NAME(B151)</f>
-        <v>ci-c-spec-101</v>
+        <v>ci-c-spec-100</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A152" s="7" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>26</v>
@@ -9229,7 +9481,7 @@
         <v>91</v>
       </c>
       <c r="G152" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="9" t="str" cm="1">
         <f t="array" ref="M152">PAGE_NAME(B152)</f>
@@ -9237,21 +9489,21 @@
       </c>
       <c r="N152" s="9" t="str" cm="1">
         <f t="array" ref="N152">SECTION_NAME(B152)</f>
-        <v>ci-c-spec-102</v>
+        <v>ci-c-spec-101</v>
       </c>
       <c r="P152" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A153" s="7" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>26</v>
@@ -9260,7 +9512,7 @@
         <v>91</v>
       </c>
       <c r="G153" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" s="9" t="str" cm="1">
         <f t="array" ref="M153">PAGE_NAME(B153)</f>
@@ -9268,21 +9520,21 @@
       </c>
       <c r="N153" s="9" t="str" cm="1">
         <f t="array" ref="N153">SECTION_NAME(B153)</f>
-        <v>ci-c-spec-103</v>
+        <v>ci-c-spec-102</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>36</v>
+        <v>534</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>26</v>
@@ -9291,7 +9543,7 @@
         <v>91</v>
       </c>
       <c r="G154" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="9" t="str" cm="1">
         <f t="array" ref="M154">PAGE_NAME(B154)</f>
@@ -9299,21 +9551,21 @@
       </c>
       <c r="N154" s="9" t="str" cm="1">
         <f t="array" ref="N154">SECTION_NAME(B154)</f>
-        <v>ci-c-spec-104</v>
+        <v>ci-c-spec-103</v>
       </c>
       <c r="P154" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A155" s="7" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>541</v>
+        <v>36</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>26</v>
@@ -9330,27 +9582,27 @@
       </c>
       <c r="N155" s="9" t="str" cm="1">
         <f t="array" ref="N155">SECTION_NAME(B155)</f>
-        <v>ci-c-spec-105</v>
+        <v>ci-c-spec-104</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G156" s="8" t="b">
         <v>0</v>
@@ -9361,27 +9613,27 @@
       </c>
       <c r="N156" s="9" t="str" cm="1">
         <f t="array" ref="N156">SECTION_NAME(B156)</f>
-        <v>ci-c-spec-106</v>
+        <v>ci-c-spec-105</v>
       </c>
       <c r="P156" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A157" s="7" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G157" s="8" t="b">
         <v>0</v>
@@ -9392,30 +9644,30 @@
       </c>
       <c r="N157" s="9" t="str" cm="1">
         <f t="array" ref="N157">SECTION_NAME(B157)</f>
-        <v>ci-c-spec-107</v>
+        <v>ci-c-spec-106</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>549</v>
+        <v>543</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>544</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E158" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G158" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="9" t="str" cm="1">
         <f t="array" ref="M158">PAGE_NAME(B158)</f>
@@ -9423,30 +9675,30 @@
       </c>
       <c r="N158" s="9" t="str" cm="1">
         <f t="array" ref="N158">SECTION_NAME(B158)</f>
-        <v>ci-c-spec-108</v>
+        <v>ci-c-spec-107</v>
       </c>
       <c r="P158" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A159" s="7" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E159" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G159" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="9" t="str" cm="1">
         <f t="array" ref="M159">PAGE_NAME(B159)</f>
@@ -9454,30 +9706,30 @@
       </c>
       <c r="N159" s="9" t="str" cm="1">
         <f t="array" ref="N159">SECTION_NAME(B159)</f>
-        <v>ci-c-spec-109</v>
+        <v>ci-c-spec-108</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A160" s="7" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G160" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="9" t="str" cm="1">
         <f t="array" ref="M160">PAGE_NAME(B160)</f>
@@ -9485,30 +9737,30 @@
       </c>
       <c r="N160" s="9" t="str" cm="1">
         <f t="array" ref="N160">SECTION_NAME(B160)</f>
-        <v>ci-c-spec-110</v>
+        <v>ci-c-spec-109</v>
       </c>
       <c r="P160" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A161" s="7" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G161" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="9" t="str" cm="1">
         <f t="array" ref="M161">PAGE_NAME(B161)</f>
@@ -9516,21 +9768,21 @@
       </c>
       <c r="N161" s="9" t="str" cm="1">
         <f t="array" ref="N161">SECTION_NAME(B161)</f>
-        <v>ci-c-spec-111</v>
+        <v>ci-c-spec-110</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>26</v>
@@ -9547,24 +9799,24 @@
       </c>
       <c r="N162" s="9" t="str" cm="1">
         <f t="array" ref="N162">SECTION_NAME(B162)</f>
-        <v>ci-c-spec-112</v>
+        <v>ci-c-spec-111</v>
       </c>
       <c r="P162" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E163" s="8" t="s">
         <v>91</v>
@@ -9578,30 +9830,30 @@
       </c>
       <c r="N163" s="9" t="str" cm="1">
         <f t="array" ref="N163">SECTION_NAME(B163)</f>
-        <v>ci-c-spec-113</v>
+        <v>ci-c-spec-112</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E164" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G164" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="9" t="str" cm="1">
         <f t="array" ref="M164">PAGE_NAME(B164)</f>
@@ -9609,30 +9861,30 @@
       </c>
       <c r="N164" s="9" t="str" cm="1">
         <f t="array" ref="N164">SECTION_NAME(B164)</f>
-        <v>ci-c-spec-114</v>
+        <v>ci-c-spec-113</v>
       </c>
       <c r="P164" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G165" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="9" t="str" cm="1">
         <f t="array" ref="M165">PAGE_NAME(B165)</f>
@@ -9640,27 +9892,27 @@
       </c>
       <c r="N165" s="9" t="str" cm="1">
         <f t="array" ref="N165">SECTION_NAME(B165)</f>
-        <v>ci-c-spec-115</v>
+        <v>ci-c-spec-114</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A166" s="7" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G166" s="8" t="b">
         <v>0</v>
@@ -9671,30 +9923,30 @@
       </c>
       <c r="N166" s="9" t="str" cm="1">
         <f t="array" ref="N166">SECTION_NAME(B166)</f>
-        <v>ci-c-spec-116</v>
+        <v>ci-c-spec-115</v>
       </c>
       <c r="P166" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D167" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G167" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" s="9" t="str" cm="1">
         <f t="array" ref="M167">PAGE_NAME(B167)</f>
@@ -9702,30 +9954,30 @@
       </c>
       <c r="N167" s="9" t="str" cm="1">
         <f t="array" ref="N167">SECTION_NAME(B167)</f>
-        <v>ci-c-spec-117</v>
+        <v>ci-c-spec-116</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>38</v>
+        <v>575</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E168" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G168" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" s="9" t="str" cm="1">
         <f t="array" ref="M168">PAGE_NAME(B168)</f>
@@ -9733,24 +9985,24 @@
       </c>
       <c r="N168" s="9" t="str" cm="1">
         <f t="array" ref="N168">SECTION_NAME(B168)</f>
-        <v>ci-c-spec-118</v>
+        <v>ci-c-spec-117</v>
       </c>
       <c r="P168" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A169" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>582</v>
+        <v>38</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E169" s="8" t="s">
         <v>91</v>
@@ -9764,27 +10016,27 @@
       </c>
       <c r="N169" s="9" t="str" cm="1">
         <f t="array" ref="N169">SECTION_NAME(B169)</f>
-        <v>ci-c-spec-119</v>
+        <v>ci-c-spec-118</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D170" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G170" s="8" t="b">
         <v>0</v>
@@ -9795,30 +10047,30 @@
       </c>
       <c r="N170" s="9" t="str" cm="1">
         <f t="array" ref="N170">SECTION_NAME(B170)</f>
-        <v>ci-c-spec-120</v>
+        <v>ci-c-spec-119</v>
       </c>
       <c r="P170" s="10" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A171" s="7" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>731</v>
+        <v>583</v>
       </c>
       <c r="D171" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G171" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" s="9" t="str" cm="1">
         <f t="array" ref="M171">PAGE_NAME(B171)</f>
@@ -9826,27 +10078,27 @@
       </c>
       <c r="N171" s="9" t="str" cm="1">
         <f t="array" ref="N171">SECTION_NAME(B171)</f>
-        <v>ci-c-spec-121</v>
+        <v>ci-c-spec-120</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>590</v>
+        <v>729</v>
       </c>
       <c r="D172" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G172" s="8" t="b">
         <v>1</v>
@@ -9857,27 +10109,27 @@
       </c>
       <c r="N172" s="9" t="str" cm="1">
         <f t="array" ref="N172">SECTION_NAME(B172)</f>
-        <v>ci-c-spec-122</v>
+        <v>ci-c-spec-121</v>
       </c>
       <c r="P172" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A173" s="7" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D173" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G173" s="8" t="b">
         <v>1</v>
@@ -9888,24 +10140,24 @@
       </c>
       <c r="N173" s="9" t="str" cm="1">
         <f t="array" ref="N173">SECTION_NAME(B173)</f>
-        <v>ci-c-spec-123</v>
+        <v>ci-c-spec-122</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A174" s="7" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E174" s="8" t="s">
         <v>91</v>
@@ -9919,30 +10171,30 @@
       </c>
       <c r="N174" s="9" t="str" cm="1">
         <f t="array" ref="N174">SECTION_NAME(B174)</f>
-        <v>ci-c-spec-124</v>
+        <v>ci-c-spec-123</v>
       </c>
       <c r="P174" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E175" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G175" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175" s="9" t="str" cm="1">
         <f t="array" ref="M175">PAGE_NAME(B175)</f>
@@ -9950,30 +10202,30 @@
       </c>
       <c r="N175" s="9" t="str" cm="1">
         <f t="array" ref="N175">SECTION_NAME(B175)</f>
-        <v>ci-c-spec-125</v>
+        <v>ci-c-spec-124</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E176" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G176" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M176" s="9" t="str" cm="1">
         <f t="array" ref="M176">PAGE_NAME(B176)</f>
@@ -9981,30 +10233,30 @@
       </c>
       <c r="N176" s="9" t="str" cm="1">
         <f t="array" ref="N176">SECTION_NAME(B176)</f>
-        <v>ci-c-spec-126</v>
+        <v>ci-c-spec-125</v>
       </c>
       <c r="P176" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="17" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A177" s="7" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E177" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G177" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" s="9" t="str" cm="1">
         <f t="array" ref="M177">PAGE_NAME(B177)</f>
@@ -10012,27 +10264,27 @@
       </c>
       <c r="N177" s="9" t="str" cm="1">
         <f t="array" ref="N177">SECTION_NAME(B177)</f>
-        <v>ci-c-spec-127</v>
+        <v>ci-c-spec-126</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="7" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G178" s="8" t="b">
         <v>0</v>
@@ -10043,30 +10295,30 @@
       </c>
       <c r="N178" s="9" t="str" cm="1">
         <f t="array" ref="N178">SECTION_NAME(B178)</f>
-        <v>ci-c-spec-128</v>
+        <v>ci-c-spec-127</v>
       </c>
       <c r="P178" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A179" s="7" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E179" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G179" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M179" s="9" t="str" cm="1">
         <f t="array" ref="M179">PAGE_NAME(B179)</f>
@@ -10074,24 +10326,24 @@
       </c>
       <c r="N179" s="9" t="str" cm="1">
         <f t="array" ref="N179">SECTION_NAME(B179)</f>
-        <v>ci-c-spec-129</v>
+        <v>ci-c-spec-128</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A180" s="7" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E180" s="8" t="s">
         <v>107</v>
@@ -10105,30 +10357,30 @@
       </c>
       <c r="N180" s="9" t="str" cm="1">
         <f t="array" ref="N180">SECTION_NAME(B180)</f>
-        <v>ci-c-spec-130</v>
+        <v>ci-c-spec-129</v>
       </c>
       <c r="P180" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A181" s="7" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G181" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" s="9" t="str" cm="1">
         <f t="array" ref="M181">PAGE_NAME(B181)</f>
@@ -10136,24 +10388,24 @@
       </c>
       <c r="N181" s="9" t="str" cm="1">
         <f t="array" ref="N181">SECTION_NAME(B181)</f>
-        <v>ci-c-spec-131</v>
+        <v>ci-c-spec-130</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A182" s="7" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E182" s="8" t="s">
         <v>91</v>
@@ -10167,27 +10419,27 @@
       </c>
       <c r="N182" s="9" t="str" cm="1">
         <f t="array" ref="N182">SECTION_NAME(B182)</f>
-        <v>ci-c-spec-132</v>
+        <v>ci-c-spec-131</v>
       </c>
       <c r="P182" s="10" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" ht="85" hidden="1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A183" s="7" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G183" s="8" t="b">
         <v>0</v>
@@ -10198,21 +10450,21 @@
       </c>
       <c r="N183" s="9" t="str" cm="1">
         <f t="array" ref="N183">SECTION_NAME(B183)</f>
-        <v>ci-c-spec-133</v>
+        <v>ci-c-spec-132</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D184" s="7" t="s">
         <v>29</v>
@@ -10229,27 +10481,27 @@
       </c>
       <c r="N184" s="9" t="str" cm="1">
         <f t="array" ref="N184">SECTION_NAME(B184)</f>
-        <v>ci-c-spec-134</v>
+        <v>ci-c-spec-133</v>
       </c>
       <c r="P184" s="10" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="185" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A185" s="7" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G185" s="8" t="b">
         <v>0</v>
@@ -10260,21 +10512,21 @@
       </c>
       <c r="N185" s="9" t="str" cm="1">
         <f t="array" ref="N185">SECTION_NAME(B185)</f>
-        <v>ci-c-spec-135</v>
+        <v>ci-c-spec-134</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A186" s="7" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>39</v>
+        <v>627</v>
       </c>
       <c r="D186" s="7" t="s">
         <v>26</v>
@@ -10291,21 +10543,21 @@
       </c>
       <c r="N186" s="9" t="str" cm="1">
         <f t="array" ref="N186">SECTION_NAME(B186)</f>
-        <v>ci-c-spec-136</v>
+        <v>ci-c-spec-135</v>
       </c>
       <c r="P186" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>634</v>
+        <v>39</v>
       </c>
       <c r="D187" s="7" t="s">
         <v>26</v>
@@ -10314,7 +10566,7 @@
         <v>91</v>
       </c>
       <c r="G187" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M187" s="9" t="str" cm="1">
         <f t="array" ref="M187">PAGE_NAME(B187)</f>
@@ -10322,21 +10574,21 @@
       </c>
       <c r="N187" s="9" t="str" cm="1">
         <f t="array" ref="N187">SECTION_NAME(B187)</f>
-        <v>ci-c-spec-137</v>
+        <v>ci-c-spec-136</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D188" s="7" t="s">
         <v>26</v>
@@ -10345,7 +10597,7 @@
         <v>91</v>
       </c>
       <c r="G188" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" s="9" t="str" cm="1">
         <f t="array" ref="M188">PAGE_NAME(B188)</f>
@@ -10353,27 +10605,27 @@
       </c>
       <c r="N188" s="9" t="str" cm="1">
         <f t="array" ref="N188">SECTION_NAME(B188)</f>
-        <v>ci-c-spec-138</v>
+        <v>ci-c-spec-137</v>
       </c>
       <c r="P188" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A189" s="7" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="D189" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G189" s="8" t="b">
         <v>0</v>
@@ -10384,21 +10636,21 @@
       </c>
       <c r="N189" s="9" t="str" cm="1">
         <f t="array" ref="N189">SECTION_NAME(B189)</f>
-        <v>ci-c-spec-139</v>
+        <v>ci-c-spec-138</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A190" s="7" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="D190" s="7" t="s">
         <v>26</v>
@@ -10415,21 +10667,21 @@
       </c>
       <c r="N190" s="9" t="str" cm="1">
         <f t="array" ref="N190">SECTION_NAME(B190)</f>
-        <v>ci-c-spec-140</v>
+        <v>ci-c-spec-139</v>
       </c>
       <c r="P190" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A191" s="7" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D191" s="7" t="s">
         <v>26</v>
@@ -10446,27 +10698,27 @@
       </c>
       <c r="N191" s="9" t="str" cm="1">
         <f t="array" ref="N191">SECTION_NAME(B191)</f>
-        <v>ci-c-spec-141</v>
+        <v>ci-c-spec-140</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A192" s="7" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>40</v>
+        <v>644</v>
       </c>
       <c r="D192" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G192" s="8" t="b">
         <v>0</v>
@@ -10477,21 +10729,21 @@
       </c>
       <c r="N192" s="9" t="str" cm="1">
         <f t="array" ref="N192">SECTION_NAME(B192)</f>
-        <v>ci-c-spec-142</v>
+        <v>ci-c-spec-141</v>
       </c>
       <c r="P192" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A193" s="7" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D193" s="7" t="s">
         <v>26</v>
@@ -10508,30 +10760,30 @@
       </c>
       <c r="N193" s="9" t="str" cm="1">
         <f t="array" ref="N193">SECTION_NAME(B193)</f>
-        <v>ci-c-spec-143</v>
+        <v>ci-c-spec-142</v>
       </c>
       <c r="P193" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="194" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>653</v>
+        <v>41</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>654</v>
+        <v>26</v>
       </c>
       <c r="E194" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G194" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M194" s="9" t="str" cm="1">
         <f t="array" ref="M194">PAGE_NAME(B194)</f>
@@ -10539,30 +10791,30 @@
       </c>
       <c r="N194" s="9" t="str" cm="1">
         <f t="array" ref="N194">SECTION_NAME(B194)</f>
-        <v>ci-c-spec-144</v>
+        <v>ci-c-spec-143</v>
       </c>
       <c r="P194" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A195" s="7" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>31</v>
+        <v>652</v>
       </c>
       <c r="E195" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G195" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" s="9" t="str" cm="1">
         <f t="array" ref="M195">PAGE_NAME(B195)</f>
@@ -10570,21 +10822,21 @@
       </c>
       <c r="N195" s="9" t="str" cm="1">
         <f t="array" ref="N195">SECTION_NAME(B195)</f>
-        <v>ci-c-spec-145</v>
+        <v>ci-c-spec-144</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A196" s="7" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>31</v>
@@ -10601,30 +10853,30 @@
       </c>
       <c r="N196" s="9" t="str" cm="1">
         <f t="array" ref="N196">SECTION_NAME(B196)</f>
-        <v>ci-c-spec-146</v>
+        <v>ci-c-spec-145</v>
       </c>
       <c r="P196" s="10" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="153" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A197" s="7" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G197" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" s="9" t="str" cm="1">
         <f t="array" ref="M197">PAGE_NAME(B197)</f>
@@ -10632,30 +10884,30 @@
       </c>
       <c r="N197" s="9" t="str" cm="1">
         <f t="array" ref="N197">SECTION_NAME(B197)</f>
-        <v>ci-c-spec-147</v>
+        <v>ci-c-spec-146</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A198" s="7" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E198" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G198" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M198" s="9" t="str" cm="1">
         <f t="array" ref="M198">PAGE_NAME(B198)</f>
@@ -10663,27 +10915,27 @@
       </c>
       <c r="N198" s="9" t="str" cm="1">
         <f t="array" ref="N198">SECTION_NAME(B198)</f>
-        <v>ci-c-spec-148</v>
+        <v>ci-c-spec-147</v>
       </c>
       <c r="P198" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A199" s="7" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="D199" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G199" s="8" t="b">
         <v>0</v>
@@ -10694,24 +10946,24 @@
       </c>
       <c r="N199" s="9" t="str" cm="1">
         <f t="array" ref="N199">SECTION_NAME(B199)</f>
-        <v>ci-c-spec-149</v>
+        <v>ci-c-spec-148</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A200" s="7" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E200" s="8" t="s">
         <v>91</v>
@@ -10725,21 +10977,21 @@
       </c>
       <c r="N200" s="9" t="str" cm="1">
         <f t="array" ref="N200">SECTION_NAME(B200)</f>
-        <v>ci-c-spec-150</v>
+        <v>ci-c-spec-149</v>
       </c>
       <c r="P200" s="10" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="201" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A201" s="7" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="D201" s="7" t="s">
         <v>26</v>
@@ -10756,21 +11008,21 @@
       </c>
       <c r="N201" s="9" t="str" cm="1">
         <f t="array" ref="N201">SECTION_NAME(B201)</f>
-        <v>ci-c-spec-151</v>
+        <v>ci-c-spec-150</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A202" s="7" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="D202" s="7" t="s">
         <v>26</v>
@@ -10779,7 +11031,7 @@
         <v>91</v>
       </c>
       <c r="G202" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M202" s="9" t="str" cm="1">
         <f t="array" ref="M202">PAGE_NAME(B202)</f>
@@ -10787,21 +11039,21 @@
       </c>
       <c r="N202" s="9" t="str" cm="1">
         <f t="array" ref="N202">SECTION_NAME(B202)</f>
-        <v>ci-c-spec-152</v>
+        <v>ci-c-spec-151</v>
       </c>
       <c r="P202" s="10" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="D203" s="7" t="s">
         <v>26</v>
@@ -10818,21 +11070,21 @@
       </c>
       <c r="N203" s="9" t="str" cm="1">
         <f t="array" ref="N203">SECTION_NAME(B203)</f>
-        <v>ci-c-spec-153</v>
+        <v>ci-c-spec-152</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="D204" s="7" t="s">
         <v>26</v>
@@ -10841,7 +11093,7 @@
         <v>91</v>
       </c>
       <c r="G204" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" s="9" t="str" cm="1">
         <f t="array" ref="M204">PAGE_NAME(B204)</f>
@@ -10849,21 +11101,21 @@
       </c>
       <c r="N204" s="9" t="str" cm="1">
         <f t="array" ref="N204">SECTION_NAME(B204)</f>
-        <v>ci-c-spec-154</v>
+        <v>ci-c-spec-153</v>
       </c>
       <c r="P204" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="204" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D205" s="7" t="s">
         <v>26</v>
@@ -10872,7 +11124,7 @@
         <v>91</v>
       </c>
       <c r="G205" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" s="9" t="str" cm="1">
         <f t="array" ref="M205">PAGE_NAME(B205)</f>
@@ -10880,21 +11132,21 @@
       </c>
       <c r="N205" s="9" t="str" cm="1">
         <f t="array" ref="N205">SECTION_NAME(B205)</f>
-        <v>ci-c-spec-155</v>
+        <v>ci-c-spec-154</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A206" s="7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="D206" s="7" t="s">
         <v>26</v>
@@ -10903,7 +11155,7 @@
         <v>91</v>
       </c>
       <c r="G206" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M206" s="9" t="str" cm="1">
         <f t="array" ref="M206">PAGE_NAME(B206)</f>
@@ -10911,21 +11163,21 @@
       </c>
       <c r="N206" s="9" t="str" cm="1">
         <f t="array" ref="N206">SECTION_NAME(B206)</f>
-        <v>ci-c-spec-156</v>
+        <v>ci-c-spec-155</v>
       </c>
       <c r="P206" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="D207" s="7" t="s">
         <v>26</v>
@@ -10942,21 +11194,21 @@
       </c>
       <c r="N207" s="9" t="str" cm="1">
         <f t="array" ref="N207">SECTION_NAME(B207)</f>
-        <v>ci-c-spec-157</v>
+        <v>ci-c-spec-156</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A208" s="7" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="D208" s="7" t="s">
         <v>26</v>
@@ -10973,30 +11225,30 @@
       </c>
       <c r="N208" s="9" t="str" cm="1">
         <f t="array" ref="N208">SECTION_NAME(B208)</f>
-        <v>ci-c-spec-158</v>
+        <v>ci-c-spec-157</v>
       </c>
       <c r="P208" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" ht="221" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="D209" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G209" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M209" s="9" t="str" cm="1">
         <f t="array" ref="M209">PAGE_NAME(B209)</f>
@@ -11004,21 +11256,21 @@
       </c>
       <c r="N209" s="9" t="str" cm="1">
         <f t="array" ref="N209">SECTION_NAME(B209)</f>
-        <v>ci-c-spec-159</v>
+        <v>ci-c-spec-158</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" ht="221" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="D210" s="7" t="s">
         <v>26</v>
@@ -11035,30 +11287,30 @@
       </c>
       <c r="N210" s="9" t="str" cm="1">
         <f t="array" ref="N210">SECTION_NAME(B210)</f>
-        <v>ci-c-spec-160</v>
+        <v>ci-c-spec-159</v>
       </c>
       <c r="P210" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E211" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G211" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" s="9" t="str" cm="1">
         <f t="array" ref="M211">PAGE_NAME(B211)</f>
@@ -11066,30 +11318,30 @@
       </c>
       <c r="N211" s="9" t="str" cm="1">
         <f t="array" ref="N211">SECTION_NAME(B211)</f>
-        <v>ci-c-spec-161</v>
+        <v>ci-c-spec-160</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G212" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M212" s="9" t="str" cm="1">
         <f t="array" ref="M212">PAGE_NAME(B212)</f>
@@ -11097,30 +11349,30 @@
       </c>
       <c r="N212" s="9" t="str" cm="1">
         <f t="array" ref="N212">SECTION_NAME(B212)</f>
-        <v>ci-c-spec-162</v>
+        <v>ci-c-spec-161</v>
       </c>
       <c r="P212" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A213" s="7" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>712</v>
+        <v>29</v>
       </c>
       <c r="E213" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G213" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213" s="9" t="str" cm="1">
         <f t="array" ref="M213">PAGE_NAME(B213)</f>
@@ -11128,27 +11380,28 @@
       </c>
       <c r="N213" s="9" t="str" cm="1">
         <f t="array" ref="N213">SECTION_NAME(B213)</f>
-        <v>ci-c-spec-163</v>
+        <v>ci-c-spec-162</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+      <c r="S213" s="13"/>
+    </row>
+    <row r="214" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A214" s="7" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>29</v>
+        <v>710</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G214" s="8" t="b">
         <v>0</v>
@@ -11159,30 +11412,31 @@
       </c>
       <c r="N214" s="9" t="str" cm="1">
         <f t="array" ref="N214">SECTION_NAME(B214)</f>
-        <v>ci-c-spec-164</v>
+        <v>ci-c-spec-163</v>
       </c>
       <c r="P214" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="S214" s="13"/>
+    </row>
+    <row r="215" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A215" s="7" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E215" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G215" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M215" s="9" t="str" cm="1">
         <f t="array" ref="M215">PAGE_NAME(B215)</f>
@@ -11190,24 +11444,25 @@
       </c>
       <c r="N215" s="9" t="str" cm="1">
         <f t="array" ref="N215">SECTION_NAME(B215)</f>
-        <v>ci-c-spec-165</v>
+        <v>ci-c-spec-164</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="68" hidden="1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="S215" s="13"/>
+    </row>
+    <row r="216" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A216" s="7" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E216" s="8" t="s">
         <v>107</v>
@@ -11221,35 +11476,72 @@
       </c>
       <c r="N216" s="9" t="str" cm="1">
         <f t="array" ref="N216">SECTION_NAME(B216)</f>
+        <v>ci-c-spec-165</v>
+      </c>
+      <c r="P216" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="S216" s="13"/>
+    </row>
+    <row r="217" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A217" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C217" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="D217" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G217" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M217" s="9" t="str" cm="1">
+        <f t="array" ref="M217">PAGE_NAME(B217)</f>
+        <v>specification</v>
+      </c>
+      <c r="N217" s="9" t="str" cm="1">
+        <f t="array" ref="N217">SECTION_NAME(B217)</f>
         <v>ci-c-spec-166</v>
       </c>
-      <c r="P216" s="10" t="s">
-        <v>722</v>
-      </c>
+      <c r="P217" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="S217" s="13"/>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S218" s="13"/>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S219" s="13"/>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S220" s="13"/>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S221" s="13"/>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S222" s="13"/>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S223" s="13"/>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S224" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE216" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="SHALL"/>
-        <filter val="SHALL / MAY"/>
-        <filter val="SHALL / SHOULD"/>
-        <filter val="SHALL NOT"/>
-        <filter val="SHALL NOT / MAY"/>
-        <filter val="SHALL NOT / SHALL"/>
-        <filter val="SHALL NOT / SHOULD"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="DTR Client"/>
-        <filter val="DTR Client, DTR Server"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AF217" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
   <hyperlinks>
-    <hyperlink ref="B25" r:id="rId1" location="ci-c-oper-7" xr:uid="{4023679D-7765-2B42-A707-2B63CD4C2439}"/>
-    <hyperlink ref="B75" r:id="rId2" location="ci-c-spec-25" xr:uid="{C6E51CB5-4ECD-3246-931F-4ABAFB05C0AF}"/>
+    <hyperlink ref="B26" r:id="rId1" location="ci-c-oper-7" xr:uid="{4023679D-7765-2B42-A707-2B63CD4C2439}"/>
+    <hyperlink ref="B76" r:id="rId2" location="ci-c-spec-25" xr:uid="{C6E51CB5-4ECD-3246-931F-4ABAFB05C0AF}"/>
+    <hyperlink ref="B158" r:id="rId3" location="ci-c-spec-107" xr:uid="{165FFDE3-4610-954A-A59A-28C882B3B7C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -11260,7 +11552,7 @@
           <x14:formula1>
             <xm:f>'Column Data'!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G1 G217:G1048576</xm:sqref>
+          <xm:sqref>G1 G218:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4866B9BF-5615-6646-965F-909D4D65F2A5}">
           <x14:formula1>
@@ -11272,7 +11564,7 @@
           <x14:formula1>
             <xm:f>'Column Data'!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K1048576 I2:I1048576</xm:sqref>
+          <xm:sqref>I2:I1048576 K2:K1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11290,14 +11582,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="40"/>
+      <c r="B1" s="42"/>
     </row>
     <row r="2" spans="1:2" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
@@ -11362,7 +11654,7 @@
       <c r="A13" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="35" t="s">
         <v>80</v>
       </c>
     </row>
@@ -11522,6 +11814,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -11775,7 +12080,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11784,20 +12089,25 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
+    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94A9A0BE-5C9D-4319-9F23-325C29977794}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11817,28 +12127,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
-    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/lib/davinci_dtr_test_kit/requirements/hl7.fhir.us.davinci-dtr_2.2.0_requirements.xlsx
+++ b/lib/davinci_dtr_test_kit/requirements/hl7.fhir.us.davinci-dtr_2.2.0_requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-dtr-test-kit/lib/davinci_dtr_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A095CAB-3DAA-FD41-945E-8DA720F4CF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41385D38-F18D-A448-81DF-4EFCFF584FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1960" windowWidth="34560" windowHeight="20380" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20380" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="9" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Column Data" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$AE$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$AF$217</definedName>
     <definedName name="EXPLODE" localSheetId="0">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="EXPLODE">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="FIND_DUPLICATES" localSheetId="0">_xlfn.LAMBDA(_xlpm.test_word,_xlpm.test_key,_xlpm.words,_xlpm.keys,_xlpm.threshold, _xlfn.LET(_xlpm.duplist,_xlfn._xlws.FILTER(_xlpm.keys,_xlfn.BYROW(_xlpm.words, _xlfn.LAMBDA(_xlpm.word, Info!HAMDIST(INDEX(_xlpm.word,1,1), _xlpm.test_word)&lt;_xlpm.threshold))),_xlfn.SINGLE(_xlfn._xlws.FILTER(_xlpm.duplist,_xlpm.duplist&lt;&gt;_xlpm.test_key,""))))</definedName>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="764">
   <si>
     <r>
       <rPr>
@@ -1812,15 +1812,9 @@
     <t>This operation **SHALL** be supported by payers and DTR applications.</t>
   </si>
   <si>
-    <t>oper-2</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-dtr/2.2.0/en/OperationDefinition-log-questionnaire-errors.html#ci-c-oper-2</t>
   </si>
   <si>
-    <t>The input OperationOutcome resource **SHOULD** include information on the DTR application identity and version, date-time with time-zone offset, as well as the provider endpoint during which the error occurred, and it **SHALL NOT** contain information about the response or information retrieved from FHIR APIs that could potentially include PHI.</t>
-  </si>
-  <si>
     <t>SHALL NOT / SHOULD</t>
   </si>
   <si>
@@ -3156,9 +3150,6 @@
     <t>https://hl7.org/fhir/us/davinci-dtr/2.2.0/en/specification.html#ci-c-spec-121</t>
   </si>
   <si>
-    <t>If the launch context did not include Coverages, a QuestionnaireResponse or a Request or Encounter, the DTR app‚ÄØ**SHALL** either‚ÄØgenerate an error or‚ÄØallow the user to search to find one to use as context for the DTR session.</t>
-  </si>
-  <si>
     <t>spec-122</t>
   </si>
   <si>
@@ -3586,6 +3577,111 @@
   </si>
   <si>
     <t>If dependencies are such that a steady state cannot be reached (e.g., an item that is enabled causes a value to be set which causes a different item to be enabled, that then disables the first item...), then the Questionnaire SHALL be treated as erroneous and attempts at automatic population SHALL end, with the user being informed of that.</t>
+  </si>
+  <si>
+    <t>If the launch context did not include Coverages, a QuestionnaireResponse or a Request or Encounter, the DTR app **SHALL** either generate an error or allow the user to search to find one to use as context for the DTR session.</t>
+  </si>
+  <si>
+    <t>Test Implementation Ticket</t>
+  </si>
+  <si>
+    <t>Mechanical - wait for invocations</t>
+  </si>
+  <si>
+    <t>Limitation - initial tests will focus on requirements within DTR itself</t>
+  </si>
+  <si>
+    <t>Attestation - Inferno can't check display</t>
+  </si>
+  <si>
+    <t>Not Applicable - responsibility of the organization, not the software</t>
+  </si>
+  <si>
+    <t>oper-2-A</t>
+  </si>
+  <si>
+    <t>oper-2-B</t>
+  </si>
+  <si>
+    <t>The input OperationOutcome resource **SHOULD** include information on the DTR application identity and version, date-time with time-zone offset, as well as the provider endpoint during which the error occurred</t>
+  </si>
+  <si>
+    <t>The input OperationOutcome resource … **SHALL NOT** contain information about the response or information retrieved from FHIR APIs that could potentially include PHI.</t>
+  </si>
+  <si>
+    <t>Attestation - Inferno cannot determine what is PHI</t>
+  </si>
+  <si>
+    <t>Mechanical - request verification</t>
+  </si>
+  <si>
+    <t>Mechanical - set up a resume scenario and verify the inputs</t>
+  </si>
+  <si>
+    <t>NA - SMART App, not Full HER</t>
+  </si>
+  <si>
+    <t>Attestation - security details too complex to check completely</t>
+  </si>
+  <si>
+    <t>Attestation - Inferno cannot know what the policy is and when/what was restricted</t>
+  </si>
+  <si>
+    <t>Mechanical - require systems to register with Inferno's simulation</t>
+  </si>
+  <si>
+    <t>TODO - check full requirement</t>
+  </si>
+  <si>
+    <t>Attestation - no outward sign of licensing</t>
+  </si>
+  <si>
+    <t>Attestation - no outward sign to verify</t>
+  </si>
+  <si>
+    <t>Mechanical - scenarios for both static and adaptive</t>
+  </si>
+  <si>
+    <t>Mechanical - observe all Questionnaire must support elements</t>
+  </si>
+  <si>
+    <t>Mechanical - observe these additional items as well, with a slightly different attestation</t>
+  </si>
+  <si>
+    <t>Attestation - set up the scenario but can't check the display</t>
+  </si>
+  <si>
+    <t>Mechanical - Set up a scenario for this where value sets passed early and confirm they can still be used later in the adaptive questionnaire</t>
+  </si>
+  <si>
+    <t>Attestation - no API and can't check display</t>
+  </si>
+  <si>
+    <t>Attestation - can't check the display</t>
+  </si>
+  <si>
+    <t>Requirement categories (technical exchange, visual, other)</t>
+  </si>
+  <si>
+    <t>Technical Exchange</t>
+  </si>
+  <si>
+    <t>cateogry rationale</t>
+  </si>
+  <si>
+    <t>Visual</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t>Content Meaning</t>
+  </si>
+  <si>
+    <t>Element Coverage (multiple - come back)</t>
+  </si>
+  <si>
+    <t>clients need to be able to complete forms</t>
   </si>
 </sst>
 </file>
@@ -3944,7 +4040,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4026,6 +4122,10 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4044,7 +4144,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4416,14 +4515,14 @@
       <c r="C3" s="29"/>
     </row>
     <row r="4" spans="1:3" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="37" t="s">
         <v>76</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:3" ht="258" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="34"/>
       <c r="C5" s="29"/>
     </row>
@@ -4435,17 +4534,17 @@
       <c r="C6" s="24"/>
     </row>
     <row r="7" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="40"/>
     </row>
     <row r="8" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37"/>
-      <c r="B8" s="39"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="41"/>
     </row>
     <row r="9" spans="1:3" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="33"/>
     </row>
     <row r="10" spans="1:3" ht="292" x14ac:dyDescent="0.2">
@@ -4468,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
-  <dimension ref="A1:W216"/>
+  <dimension ref="A1:X224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="7"/>
@@ -4488,17 +4587,18 @@
     <col min="15" max="15" width="20" style="10" customWidth="1"/>
     <col min="16" max="16" width="28.5" style="10" customWidth="1"/>
     <col min="17" max="17" width="10.83203125" style="13"/>
-    <col min="18" max="18" width="10.83203125" style="10"/>
-    <col min="19" max="19" width="10.5" style="10" customWidth="1"/>
-    <col min="20" max="20" width="42.5" style="13" customWidth="1"/>
-    <col min="21" max="21" width="21.83203125" style="6" customWidth="1"/>
-    <col min="22" max="22" width="19.1640625" style="6" customWidth="1"/>
-    <col min="23" max="23" width="10.83203125" style="6"/>
-    <col min="24" max="24" width="14.83203125" style="6" customWidth="1"/>
-    <col min="25" max="16384" width="10.83203125" style="6"/>
+    <col min="18" max="18" width="39.1640625" style="13" customWidth="1"/>
+    <col min="19" max="19" width="15.83203125" style="10" customWidth="1"/>
+    <col min="20" max="20" width="10.5" style="10" customWidth="1"/>
+    <col min="21" max="21" width="42.5" style="13" customWidth="1"/>
+    <col min="22" max="22" width="21.83203125" style="6" customWidth="1"/>
+    <col min="23" max="23" width="19.1640625" style="6" customWidth="1"/>
+    <col min="24" max="24" width="10.83203125" style="6"/>
+    <col min="25" max="25" width="14.83203125" style="6" customWidth="1"/>
+    <col min="26" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="5" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4550,18 +4650,27 @@
       <c r="Q1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="14" t="s">
+        <v>730</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="U1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="W1" s="6"/>
-    </row>
-    <row r="2" spans="1:23" ht="85" x14ac:dyDescent="0.2">
+      <c r="V1" s="36" t="s">
+        <v>756</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="X1" s="6"/>
+    </row>
+    <row r="2" spans="1:24" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>81</v>
       </c>
@@ -4589,10 +4698,16 @@
         <v>ci-c-conf-1</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>731</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>85</v>
       </c>
@@ -4620,10 +4735,16 @@
         <v>ci-c-conf-2</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>88</v>
       </c>
@@ -4651,10 +4772,16 @@
         <v>ci-c-conf-3</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>92</v>
       </c>
@@ -4682,14 +4809,14 @@
         <v>ci-c-conf-4</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="34" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -4713,10 +4840,16 @@
         <v>ci-c-conf-5</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="85" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>98</v>
       </c>
@@ -4744,10 +4877,16 @@
         <v>ci-c-conf-6</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="34" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>101</v>
       </c>
@@ -4775,10 +4914,10 @@
         <v>ci-c-conf-7</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="102" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="102" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>104</v>
       </c>
@@ -4806,10 +4945,13 @@
         <v>ci-c-conf-8</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>108</v>
       </c>
@@ -4837,10 +4979,13 @@
         <v>ci-c-conf-9</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="170" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="170" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>111</v>
       </c>
@@ -4868,10 +5013,13 @@
         <v>ci-c-conf-10</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>115</v>
       </c>
@@ -4899,10 +5047,10 @@
         <v>ci-c-conf-11</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="153" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="153" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>118</v>
       </c>
@@ -4930,10 +5078,19 @@
         <v>ci-c-conf-12</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="W13" s="6" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>121</v>
       </c>
@@ -4961,10 +5118,16 @@
         <v>ci-c-conf-13</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R14" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="136" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>124</v>
       </c>
@@ -4992,10 +5155,16 @@
         <v>ci-c-conf-14</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>734</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>128</v>
       </c>
@@ -5023,10 +5192,16 @@
         <v>ci-c-conf-15</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>734</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>131</v>
       </c>
@@ -5054,10 +5229,10 @@
         <v>ci-c-opcn-1</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>134</v>
       </c>
@@ -5085,10 +5260,10 @@
         <v>ci-c-opcn-2</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>137</v>
       </c>
@@ -5116,21 +5291,27 @@
         <v>ci-c-oper-1</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>731</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>141</v>
-      </c>
       <c r="C20" s="8" t="s">
-        <v>142</v>
+        <v>737</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>91</v>
@@ -5147,21 +5328,21 @@
         <v>ci-c-oper-2</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>144</v>
+        <v>736</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>146</v>
+        <v>738</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>91</v>
@@ -5175,24 +5356,30 @@
       </c>
       <c r="N21" s="9" t="str" cm="1">
         <f t="array" ref="N21">SECTION_NAME(B21)</f>
-        <v>ci-c-oper-3</v>
+        <v>ci-c-oper-2</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>739</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>91</v>
@@ -5202,31 +5389,31 @@
       </c>
       <c r="M22" s="9" t="str" cm="1">
         <f t="array" ref="M22">PAGE_NAME(B22)</f>
-        <v>OperationDefinition-DTR-ValueSet-expand</v>
+        <v>OperationDefinition-log-questionnaire-errors</v>
       </c>
       <c r="N22" s="9" t="str" cm="1">
         <f t="array" ref="N22">SECTION_NAME(B22)</f>
-        <v>ci-c-oper-4</v>
+        <v>ci-c-oper-3</v>
       </c>
       <c r="P22" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G23" s="8" t="b">
         <v>0</v>
@@ -5237,61 +5424,67 @@
       </c>
       <c r="N23" s="9" t="str" cm="1">
         <f t="array" ref="N23">SECTION_NAME(B23)</f>
-        <v>ci-c-oper-5</v>
+        <v>ci-c-oper-4</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>731</v>
+      </c>
+      <c r="V23" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G24" s="8" t="b">
         <v>0</v>
       </c>
       <c r="M24" s="9" t="str" cm="1">
         <f t="array" ref="M24">PAGE_NAME(B24)</f>
-        <v>OperationDefinition-questionnaire-package</v>
+        <v>OperationDefinition-DTR-ValueSet-expand</v>
       </c>
       <c r="N24" s="9" t="str" cm="1">
         <f t="array" ref="N24">SECTION_NAME(B24)</f>
-        <v>ci-c-oper-6</v>
+        <v>ci-c-oper-5</v>
       </c>
       <c r="P24" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G25" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="9" t="str" cm="1">
         <f t="array" ref="M25">PAGE_NAME(B25)</f>
@@ -5299,21 +5492,27 @@
       </c>
       <c r="N25" s="9" t="str" cm="1">
         <f t="array" ref="N25">SECTION_NAME(B25)</f>
-        <v>ci-c-oper-7</v>
+        <v>ci-c-oper-6</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R25" s="13" t="s">
+        <v>740</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>26</v>
@@ -5330,21 +5529,21 @@
       </c>
       <c r="N26" s="9" t="str" cm="1">
         <f t="array" ref="N26">SECTION_NAME(B26)</f>
-        <v>ci-c-oper-8</v>
+        <v>ci-c-oper-7</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>26</v>
@@ -5361,21 +5560,21 @@
       </c>
       <c r="N27" s="9" t="str" cm="1">
         <f t="array" ref="N27">SECTION_NAME(B27)</f>
-        <v>ci-c-oper-9</v>
+        <v>ci-c-oper-8</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>26</v>
@@ -5392,24 +5591,24 @@
       </c>
       <c r="N28" s="9" t="str" cm="1">
         <f t="array" ref="N28">SECTION_NAME(B28)</f>
-        <v>ci-c-oper-10</v>
+        <v>ci-c-oper-9</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>107</v>
@@ -5423,30 +5622,30 @@
       </c>
       <c r="N29" s="9" t="str" cm="1">
         <f t="array" ref="N29">SECTION_NAME(B29)</f>
-        <v>ci-c-oper-11</v>
+        <v>ci-c-oper-10</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G30" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="9" t="str" cm="1">
         <f t="array" ref="M30">PAGE_NAME(B30)</f>
@@ -5454,21 +5653,21 @@
       </c>
       <c r="N30" s="9" t="str" cm="1">
         <f t="array" ref="N30">SECTION_NAME(B30)</f>
-        <v>ci-c-oper-12</v>
+        <v>ci-c-oper-11</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>26</v>
@@ -5485,21 +5684,21 @@
       </c>
       <c r="N31" s="9" t="str" cm="1">
         <f t="array" ref="N31">SECTION_NAME(B31)</f>
-        <v>ci-c-oper-13</v>
+        <v>ci-c-oper-12</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>26</v>
@@ -5516,21 +5715,21 @@
       </c>
       <c r="N32" s="9" t="str" cm="1">
         <f t="array" ref="N32">SECTION_NAME(B32)</f>
-        <v>ci-c-oper-14</v>
+        <v>ci-c-oper-13</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>26</v>
@@ -5547,21 +5746,21 @@
       </c>
       <c r="N33" s="9" t="str" cm="1">
         <f t="array" ref="N33">SECTION_NAME(B33)</f>
-        <v>ci-c-oper-15</v>
+        <v>ci-c-oper-14</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>26</v>
@@ -5578,24 +5777,24 @@
       </c>
       <c r="N34" s="9" t="str" cm="1">
         <f t="array" ref="N34">SECTION_NAME(B34)</f>
-        <v>ci-c-oper-16</v>
+        <v>ci-c-oper-15</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>107</v>
@@ -5609,24 +5808,24 @@
       </c>
       <c r="N35" s="9" t="str" cm="1">
         <f t="array" ref="N35">SECTION_NAME(B35)</f>
-        <v>ci-c-oper-17</v>
+        <v>ci-c-oper-16</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>107</v>
@@ -5640,24 +5839,24 @@
       </c>
       <c r="N36" s="9" t="str" cm="1">
         <f t="array" ref="N36">SECTION_NAME(B36)</f>
-        <v>ci-c-oper-18</v>
+        <v>ci-c-oper-17</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>107</v>
@@ -5671,30 +5870,30 @@
       </c>
       <c r="N37" s="9" t="str" cm="1">
         <f t="array" ref="N37">SECTION_NAME(B37)</f>
-        <v>ci-c-oper-19</v>
+        <v>ci-c-oper-18</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G38" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="9" t="str" cm="1">
         <f t="array" ref="M38">PAGE_NAME(B38)</f>
@@ -5702,117 +5901,129 @@
       </c>
       <c r="N38" s="9" t="str" cm="1">
         <f t="array" ref="N38">SECTION_NAME(B38)</f>
-        <v>ci-c-oper-20</v>
+        <v>ci-c-oper-19</v>
       </c>
       <c r="P38" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G39" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="9" t="str" cm="1">
         <f t="array" ref="M39">PAGE_NAME(B39)</f>
-        <v>StructureDefinition-dtr-qpackage-input-parameters</v>
+        <v>OperationDefinition-questionnaire-package</v>
       </c>
       <c r="N39" s="9" t="str" cm="1">
         <f t="array" ref="N39">SECTION_NAME(B39)</f>
-        <v>ci-c-prof-1</v>
+        <v>ci-c-oper-20</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>741</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>202</v>
+        <v>196</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G40" s="8" t="b">
         <v>0</v>
       </c>
       <c r="M40" s="9" t="str" cm="1">
         <f t="array" ref="M40">PAGE_NAME(B40)</f>
-        <v>StructureDefinition-dtr-supported-Payers</v>
+        <v>StructureDefinition-dtr-qpackage-input-parameters</v>
       </c>
       <c r="N40" s="9" t="str" cm="1">
         <f t="array" ref="N40">SECTION_NAME(B40)</f>
-        <v>ci-c-prof-2</v>
+        <v>ci-c-prof-1</v>
       </c>
       <c r="P40" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G41" s="8" t="b">
         <v>0</v>
       </c>
       <c r="M41" s="9" t="str" cm="1">
         <f t="array" ref="M41">PAGE_NAME(B41)</f>
-        <v>security</v>
+        <v>StructureDefinition-dtr-supported-Payers</v>
       </c>
       <c r="N41" s="9" t="str" cm="1">
         <f t="array" ref="N41">SECTION_NAME(B41)</f>
-        <v>ci-c-sec-1</v>
+        <v>ci-c-prof-2</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R41" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="V41" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>84</v>
@@ -5826,27 +6037,30 @@
       </c>
       <c r="N42" s="9" t="str" cm="1">
         <f t="array" ref="N42">SECTION_NAME(B42)</f>
-        <v>ci-c-sec-2</v>
+        <v>ci-c-sec-1</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R42" s="13" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G43" s="8" t="b">
         <v>0</v>
@@ -5857,24 +6071,24 @@
       </c>
       <c r="N43" s="9" t="str" cm="1">
         <f t="array" ref="N43">SECTION_NAME(B43)</f>
-        <v>ci-c-sec-3</v>
+        <v>ci-c-sec-2</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>107</v>
@@ -5888,27 +6102,27 @@
       </c>
       <c r="N44" s="9" t="str" cm="1">
         <f t="array" ref="N44">SECTION_NAME(B44)</f>
-        <v>ci-c-sec-4</v>
+        <v>ci-c-sec-3</v>
       </c>
       <c r="P44" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>217</v>
+        <v>42</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G45" s="8" t="b">
         <v>0</v>
@@ -5919,24 +6133,24 @@
       </c>
       <c r="N45" s="9" t="str" cm="1">
         <f t="array" ref="N45">SECTION_NAME(B45)</f>
-        <v>ci-c-sec-5</v>
+        <v>ci-c-sec-4</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>91</v>
@@ -5950,21 +6164,24 @@
       </c>
       <c r="N46" s="9" t="str" cm="1">
         <f t="array" ref="N46">SECTION_NAME(B46)</f>
-        <v>ci-c-sec-6</v>
+        <v>ci-c-sec-5</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R46" s="13" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>29</v>
@@ -5981,24 +6198,24 @@
       </c>
       <c r="N47" s="9" t="str" cm="1">
         <f t="array" ref="N47">SECTION_NAME(B47)</f>
-        <v>ci-c-sec-7</v>
+        <v>ci-c-sec-6</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>91</v>
@@ -6012,27 +6229,27 @@
       </c>
       <c r="N48" s="9" t="str" cm="1">
         <f t="array" ref="N48">SECTION_NAME(B48)</f>
-        <v>ci-c-sec-8</v>
+        <v>ci-c-sec-7</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G49" s="8" t="b">
         <v>0</v>
@@ -6043,30 +6260,30 @@
       </c>
       <c r="N49" s="9" t="str" cm="1">
         <f t="array" ref="N49">SECTION_NAME(B49)</f>
-        <v>ci-c-sec-9</v>
+        <v>ci-c-sec-8</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G50" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="9" t="str" cm="1">
         <f t="array" ref="M50">PAGE_NAME(B50)</f>
@@ -6074,58 +6291,58 @@
       </c>
       <c r="N50" s="9" t="str" cm="1">
         <f t="array" ref="N50">SECTION_NAME(B50)</f>
-        <v>ci-c-sec-10</v>
+        <v>ci-c-sec-9</v>
       </c>
       <c r="P50" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G51" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="9" t="str" cm="1">
         <f t="array" ref="M51">PAGE_NAME(B51)</f>
-        <v>specification</v>
+        <v>security</v>
       </c>
       <c r="N51" s="9" t="str" cm="1">
         <f t="array" ref="N51">SECTION_NAME(B51)</f>
-        <v>ci-c-spec-1</v>
+        <v>ci-c-sec-10</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G52" s="8" t="b">
         <v>0</v>
@@ -6136,21 +6353,21 @@
       </c>
       <c r="N52" s="9" t="str" cm="1">
         <f t="array" ref="N52">SECTION_NAME(B52)</f>
-        <v>ci-c-spec-2</v>
+        <v>ci-c-spec-1</v>
       </c>
       <c r="P52" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>30</v>
@@ -6159,7 +6376,7 @@
         <v>91</v>
       </c>
       <c r="G53" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="9" t="str" cm="1">
         <f t="array" ref="M53">PAGE_NAME(B53)</f>
@@ -6167,30 +6384,30 @@
       </c>
       <c r="N53" s="9" t="str" cm="1">
         <f t="array" ref="N53">SECTION_NAME(B53)</f>
-        <v>ci-c-spec-3</v>
+        <v>ci-c-spec-2</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G54" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="9" t="str" cm="1">
         <f t="array" ref="M54">PAGE_NAME(B54)</f>
@@ -6198,27 +6415,27 @@
       </c>
       <c r="N54" s="9" t="str" cm="1">
         <f t="array" ref="N54">SECTION_NAME(B54)</f>
-        <v>ci-c-spec-4</v>
+        <v>ci-c-spec-3</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G55" s="8" t="b">
         <v>0</v>
@@ -6229,24 +6446,27 @@
       </c>
       <c r="N55" s="9" t="str" cm="1">
         <f t="array" ref="N55">SECTION_NAME(B55)</f>
-        <v>ci-c-spec-5</v>
+        <v>ci-c-spec-4</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+      <c r="R55" s="13" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>107</v>
@@ -6260,27 +6480,27 @@
       </c>
       <c r="N56" s="9" t="str" cm="1">
         <f t="array" ref="N56">SECTION_NAME(B56)</f>
-        <v>ci-c-spec-6</v>
+        <v>ci-c-spec-5</v>
       </c>
       <c r="P56" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G57" s="8" t="b">
         <v>0</v>
@@ -6291,24 +6511,24 @@
       </c>
       <c r="N57" s="9" t="str" cm="1">
         <f t="array" ref="N57">SECTION_NAME(B57)</f>
-        <v>ci-c-spec-7</v>
+        <v>ci-c-spec-6</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>84</v>
@@ -6322,24 +6542,27 @@
       </c>
       <c r="N58" s="9" t="str" cm="1">
         <f t="array" ref="N58">SECTION_NAME(B58)</f>
-        <v>ci-c-spec-8</v>
+        <v>ci-c-spec-7</v>
       </c>
       <c r="P58" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+      <c r="R58" s="13" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>258</v>
+        <v>29</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>84</v>
@@ -6353,27 +6576,27 @@
       </c>
       <c r="N59" s="9" t="str" cm="1">
         <f t="array" ref="N59">SECTION_NAME(B59)</f>
-        <v>ci-c-spec-9</v>
+        <v>ci-c-spec-8</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>30</v>
+        <v>256</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G60" s="8" t="b">
         <v>0</v>
@@ -6384,27 +6607,27 @@
       </c>
       <c r="N60" s="9" t="str" cm="1">
         <f t="array" ref="N60">SECTION_NAME(B60)</f>
-        <v>ci-c-spec-10</v>
+        <v>ci-c-spec-9</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G61" s="8" t="b">
         <v>0</v>
@@ -6415,27 +6638,27 @@
       </c>
       <c r="N61" s="9" t="str" cm="1">
         <f t="array" ref="N61">SECTION_NAME(B61)</f>
-        <v>ci-c-spec-11</v>
+        <v>ci-c-spec-10</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>268</v>
+        <v>26</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G62" s="8" t="b">
         <v>0</v>
@@ -6446,24 +6669,27 @@
       </c>
       <c r="N62" s="9" t="str" cm="1">
         <f t="array" ref="N62">SECTION_NAME(B62)</f>
-        <v>ci-c-spec-12</v>
+        <v>ci-c-spec-11</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+      <c r="R62" s="13" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>107</v>
@@ -6477,27 +6703,27 @@
       </c>
       <c r="N63" s="9" t="str" cm="1">
         <f t="array" ref="N63">SECTION_NAME(B63)</f>
-        <v>ci-c-spec-13</v>
+        <v>ci-c-spec-12</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>273</v>
+        <v>267</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>268</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G64" s="8" t="b">
         <v>0</v>
@@ -6508,27 +6734,27 @@
       </c>
       <c r="N64" s="9" t="str" cm="1">
         <f t="array" ref="N64">SECTION_NAME(B64)</f>
-        <v>ci-c-spec-14</v>
+        <v>ci-c-spec-13</v>
       </c>
       <c r="P64" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G65" s="8" t="b">
         <v>0</v>
@@ -6539,27 +6765,30 @@
       </c>
       <c r="N65" s="9" t="str" cm="1">
         <f t="array" ref="N65">SECTION_NAME(B65)</f>
-        <v>ci-c-spec-15</v>
+        <v>ci-c-spec-14</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R65" s="13" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G66" s="8" t="b">
         <v>0</v>
@@ -6570,27 +6799,27 @@
       </c>
       <c r="N66" s="9" t="str" cm="1">
         <f t="array" ref="N66">SECTION_NAME(B66)</f>
-        <v>ci-c-spec-16</v>
+        <v>ci-c-spec-15</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G67" s="8" t="b">
         <v>0</v>
@@ -6601,21 +6830,24 @@
       </c>
       <c r="N67" s="9" t="str" cm="1">
         <f t="array" ref="N67">SECTION_NAME(B67)</f>
-        <v>ci-c-spec-17</v>
+        <v>ci-c-spec-16</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R67" s="13" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>26</v>
@@ -6624,7 +6856,7 @@
         <v>107</v>
       </c>
       <c r="G68" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="9" t="str" cm="1">
         <f t="array" ref="M68">PAGE_NAME(B68)</f>
@@ -6632,30 +6864,30 @@
       </c>
       <c r="N68" s="9" t="str" cm="1">
         <f t="array" ref="N68">SECTION_NAME(B68)</f>
-        <v>ci-c-spec-18</v>
+        <v>ci-c-spec-17</v>
       </c>
       <c r="P68" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G69" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="9" t="str" cm="1">
         <f t="array" ref="M69">PAGE_NAME(B69)</f>
@@ -6663,24 +6895,24 @@
       </c>
       <c r="N69" s="9" t="str" cm="1">
         <f t="array" ref="N69">SECTION_NAME(B69)</f>
-        <v>ci-c-spec-19</v>
+        <v>ci-c-spec-18</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>91</v>
@@ -6694,27 +6926,30 @@
       </c>
       <c r="N70" s="9" t="str" cm="1">
         <f t="array" ref="N70">SECTION_NAME(B70)</f>
-        <v>ci-c-spec-20</v>
+        <v>ci-c-spec-19</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R70" s="13" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G71" s="8" t="b">
         <v>0</v>
@@ -6725,30 +6960,33 @@
       </c>
       <c r="N71" s="9" t="str" cm="1">
         <f t="array" ref="N71">SECTION_NAME(B71)</f>
-        <v>ci-c-spec-21</v>
+        <v>ci-c-spec-20</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R71" s="13" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G72" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="9" t="str" cm="1">
         <f t="array" ref="M72">PAGE_NAME(B72)</f>
@@ -6756,21 +6994,21 @@
       </c>
       <c r="N72" s="9" t="str" cm="1">
         <f t="array" ref="N72">SECTION_NAME(B72)</f>
-        <v>ci-c-spec-22</v>
+        <v>ci-c-spec-21</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>26</v>
@@ -6787,21 +7025,21 @@
       </c>
       <c r="N73" s="9" t="str" cm="1">
         <f t="array" ref="N73">SECTION_NAME(B73)</f>
-        <v>ci-c-spec-23</v>
+        <v>ci-c-spec-22</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>26</v>
@@ -6818,21 +7056,21 @@
       </c>
       <c r="N74" s="9" t="str" cm="1">
         <f t="array" ref="N74">SECTION_NAME(B74)</f>
-        <v>ci-c-spec-24</v>
+        <v>ci-c-spec-23</v>
       </c>
       <c r="P74" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>26</v>
@@ -6841,7 +7079,7 @@
         <v>107</v>
       </c>
       <c r="G75" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="9" t="str" cm="1">
         <f t="array" ref="M75">PAGE_NAME(B75)</f>
@@ -6849,24 +7087,24 @@
       </c>
       <c r="N75" s="9" t="str" cm="1">
         <f t="array" ref="N75">SECTION_NAME(B75)</f>
-        <v>ci-c-spec-25</v>
+        <v>ci-c-spec-24</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>304</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>107</v>
@@ -6880,21 +7118,21 @@
       </c>
       <c r="N76" s="9" t="str" cm="1">
         <f t="array" ref="N76">SECTION_NAME(B76)</f>
-        <v>ci-c-spec-26</v>
+        <v>ci-c-spec-25</v>
       </c>
       <c r="P76" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>30</v>
@@ -6911,21 +7149,21 @@
       </c>
       <c r="N77" s="9" t="str" cm="1">
         <f t="array" ref="N77">SECTION_NAME(B77)</f>
-        <v>ci-c-spec-27</v>
+        <v>ci-c-spec-26</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>30</v>
@@ -6942,21 +7180,21 @@
       </c>
       <c r="N78" s="9" t="str" cm="1">
         <f t="array" ref="N78">SECTION_NAME(B78)</f>
-        <v>ci-c-spec-28</v>
+        <v>ci-c-spec-27</v>
       </c>
       <c r="P78" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>30</v>
@@ -6973,21 +7211,21 @@
       </c>
       <c r="N79" s="9" t="str" cm="1">
         <f t="array" ref="N79">SECTION_NAME(B79)</f>
-        <v>ci-c-spec-29</v>
+        <v>ci-c-spec-28</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="187" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>30</v>
@@ -7004,21 +7242,21 @@
       </c>
       <c r="N80" s="9" t="str" cm="1">
         <f t="array" ref="N80">SECTION_NAME(B80)</f>
-        <v>ci-c-spec-30</v>
+        <v>ci-c-spec-29</v>
       </c>
       <c r="P80" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="187" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>30</v>
@@ -7035,30 +7273,30 @@
       </c>
       <c r="N81" s="9" t="str" cm="1">
         <f t="array" ref="N81">SECTION_NAME(B81)</f>
-        <v>ci-c-spec-31</v>
+        <v>ci-c-spec-30</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G82" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="9" t="str" cm="1">
         <f t="array" ref="M82">PAGE_NAME(B82)</f>
@@ -7066,24 +7304,24 @@
       </c>
       <c r="N82" s="9" t="str" cm="1">
         <f t="array" ref="N82">SECTION_NAME(B82)</f>
-        <v>ci-c-spec-32</v>
+        <v>ci-c-spec-31</v>
       </c>
       <c r="P82" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>107</v>
@@ -7097,24 +7335,24 @@
       </c>
       <c r="N83" s="9" t="str" cm="1">
         <f t="array" ref="N83">SECTION_NAME(B83)</f>
-        <v>ci-c-spec-33</v>
+        <v>ci-c-spec-32</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>107</v>
@@ -7128,27 +7366,27 @@
       </c>
       <c r="N84" s="9" t="str" cm="1">
         <f t="array" ref="N84">SECTION_NAME(B84)</f>
-        <v>ci-c-spec-34</v>
+        <v>ci-c-spec-33</v>
       </c>
       <c r="P84" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A85" s="7" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G85" s="8" t="b">
         <v>1</v>
@@ -7159,27 +7397,27 @@
       </c>
       <c r="N85" s="9" t="str" cm="1">
         <f t="array" ref="N85">SECTION_NAME(B85)</f>
-        <v>ci-c-spec-35</v>
+        <v>ci-c-spec-34</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G86" s="8" t="b">
         <v>1</v>
@@ -7190,27 +7428,30 @@
       </c>
       <c r="N86" s="9" t="str" cm="1">
         <f t="array" ref="N86">SECTION_NAME(B86)</f>
-        <v>ci-c-spec-36</v>
+        <v>ci-c-spec-35</v>
       </c>
       <c r="P86" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R86" s="13" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G87" s="8" t="b">
         <v>1</v>
@@ -7221,30 +7462,30 @@
       </c>
       <c r="N87" s="9" t="str" cm="1">
         <f t="array" ref="N87">SECTION_NAME(B87)</f>
-        <v>ci-c-spec-37</v>
+        <v>ci-c-spec-36</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G88" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="9" t="str" cm="1">
         <f t="array" ref="M88">PAGE_NAME(B88)</f>
@@ -7252,21 +7493,21 @@
       </c>
       <c r="N88" s="9" t="str" cm="1">
         <f t="array" ref="N88">SECTION_NAME(B88)</f>
-        <v>ci-c-spec-38</v>
+        <v>ci-c-spec-37</v>
       </c>
       <c r="P88" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>26</v>
@@ -7275,7 +7516,7 @@
         <v>107</v>
       </c>
       <c r="G89" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="9" t="str" cm="1">
         <f t="array" ref="M89">PAGE_NAME(B89)</f>
@@ -7283,30 +7524,30 @@
       </c>
       <c r="N89" s="9" t="str" cm="1">
         <f t="array" ref="N89">SECTION_NAME(B89)</f>
-        <v>ci-c-spec-39</v>
+        <v>ci-c-spec-38</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G90" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="9" t="str" cm="1">
         <f t="array" ref="M90">PAGE_NAME(B90)</f>
@@ -7314,30 +7555,30 @@
       </c>
       <c r="N90" s="9" t="str" cm="1">
         <f t="array" ref="N90">SECTION_NAME(B90)</f>
-        <v>ci-c-spec-40</v>
+        <v>ci-c-spec-39</v>
       </c>
       <c r="P90" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G91" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="9" t="str" cm="1">
         <f t="array" ref="M91">PAGE_NAME(B91)</f>
@@ -7345,30 +7586,30 @@
       </c>
       <c r="N91" s="9" t="str" cm="1">
         <f t="array" ref="N91">SECTION_NAME(B91)</f>
-        <v>ci-c-spec-41</v>
+        <v>ci-c-spec-40</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G92" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="9" t="str" cm="1">
         <f t="array" ref="M92">PAGE_NAME(B92)</f>
@@ -7376,24 +7617,24 @@
       </c>
       <c r="N92" s="9" t="str" cm="1">
         <f t="array" ref="N92">SECTION_NAME(B92)</f>
-        <v>ci-c-spec-42</v>
+        <v>ci-c-spec-41</v>
       </c>
       <c r="P92" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>107</v>
@@ -7407,30 +7648,30 @@
       </c>
       <c r="N93" s="9" t="str" cm="1">
         <f t="array" ref="N93">SECTION_NAME(B93)</f>
-        <v>ci-c-spec-43</v>
+        <v>ci-c-spec-42</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G94" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="9" t="str" cm="1">
         <f t="array" ref="M94">PAGE_NAME(B94)</f>
@@ -7438,27 +7679,27 @@
       </c>
       <c r="N94" s="9" t="str" cm="1">
         <f t="array" ref="N94">SECTION_NAME(B94)</f>
-        <v>ci-c-spec-44</v>
+        <v>ci-c-spec-43</v>
       </c>
       <c r="P94" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A95" s="7" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G95" s="8" t="b">
         <v>1</v>
@@ -7469,27 +7710,30 @@
       </c>
       <c r="N95" s="9" t="str" cm="1">
         <f t="array" ref="N95">SECTION_NAME(B95)</f>
-        <v>ci-c-spec-45</v>
+        <v>ci-c-spec-44</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R95" s="13" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A96" s="7" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>369</v>
+        <v>32</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G96" s="8" t="b">
         <v>1</v>
@@ -7500,21 +7744,21 @@
       </c>
       <c r="N96" s="9" t="str" cm="1">
         <f t="array" ref="N96">SECTION_NAME(B96)</f>
-        <v>ci-c-spec-46</v>
+        <v>ci-c-spec-45</v>
       </c>
       <c r="P96" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>26</v>
@@ -7523,7 +7767,7 @@
         <v>91</v>
       </c>
       <c r="G97" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="9" t="str" cm="1">
         <f t="array" ref="M97">PAGE_NAME(B97)</f>
@@ -7531,24 +7775,27 @@
       </c>
       <c r="N97" s="9" t="str" cm="1">
         <f t="array" ref="N97">SECTION_NAME(B97)</f>
-        <v>ci-c-spec-47</v>
+        <v>ci-c-spec-46</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R97" s="13" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>91</v>
@@ -7562,30 +7809,33 @@
       </c>
       <c r="N98" s="9" t="str" cm="1">
         <f t="array" ref="N98">SECTION_NAME(B98)</f>
-        <v>ci-c-spec-48</v>
+        <v>ci-c-spec-47</v>
       </c>
       <c r="P98" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="R98" s="13" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A99" s="7" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G99" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" s="9" t="str" cm="1">
         <f t="array" ref="M99">PAGE_NAME(B99)</f>
@@ -7593,30 +7843,30 @@
       </c>
       <c r="N99" s="9" t="str" cm="1">
         <f t="array" ref="N99">SECTION_NAME(B99)</f>
-        <v>ci-c-spec-49</v>
+        <v>ci-c-spec-48</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G100" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="9" t="str" cm="1">
         <f t="array" ref="M100">PAGE_NAME(B100)</f>
@@ -7624,30 +7874,33 @@
       </c>
       <c r="N100" s="9" t="str" cm="1">
         <f t="array" ref="N100">SECTION_NAME(B100)</f>
-        <v>ci-c-spec-50</v>
+        <v>ci-c-spec-49</v>
       </c>
       <c r="P100" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+      <c r="R100" s="13" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>35</v>
+        <v>379</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G101" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" s="9" t="str" cm="1">
         <f t="array" ref="M101">PAGE_NAME(B101)</f>
@@ -7655,30 +7908,30 @@
       </c>
       <c r="N101" s="9" t="str" cm="1">
         <f t="array" ref="N101">SECTION_NAME(B101)</f>
-        <v>ci-c-spec-51</v>
+        <v>ci-c-spec-50</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>386</v>
+        <v>35</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E102" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G102" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="9" t="str" cm="1">
         <f t="array" ref="M102">PAGE_NAME(B102)</f>
@@ -7686,24 +7939,24 @@
       </c>
       <c r="N102" s="9" t="str" cm="1">
         <f t="array" ref="N102">SECTION_NAME(B102)</f>
-        <v>ci-c-spec-52</v>
+        <v>ci-c-spec-51</v>
       </c>
       <c r="P102" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E103" s="8" t="s">
         <v>107</v>
@@ -7717,24 +7970,24 @@
       </c>
       <c r="N103" s="9" t="str" cm="1">
         <f t="array" ref="N103">SECTION_NAME(B103)</f>
-        <v>ci-c-spec-53</v>
+        <v>ci-c-spec-52</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>33</v>
+        <v>387</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E104" s="8" t="s">
         <v>107</v>
@@ -7748,24 +8001,24 @@
       </c>
       <c r="N104" s="9" t="str" cm="1">
         <f t="array" ref="N104">SECTION_NAME(B104)</f>
-        <v>ci-c-spec-54</v>
+        <v>ci-c-spec-53</v>
       </c>
       <c r="P104" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>394</v>
+        <v>33</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>107</v>
@@ -7779,21 +8032,21 @@
       </c>
       <c r="N105" s="9" t="str" cm="1">
         <f t="array" ref="N105">SECTION_NAME(B105)</f>
-        <v>ci-c-spec-55</v>
+        <v>ci-c-spec-54</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>34</v>
+        <v>392</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>29</v>
@@ -7810,27 +8063,27 @@
       </c>
       <c r="N106" s="9" t="str" cm="1">
         <f t="array" ref="N106">SECTION_NAME(B106)</f>
-        <v>ci-c-spec-56</v>
+        <v>ci-c-spec-55</v>
       </c>
       <c r="P106" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>399</v>
+        <v>34</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G107" s="8" t="b">
         <v>0</v>
@@ -7841,27 +8094,27 @@
       </c>
       <c r="N107" s="9" t="str" cm="1">
         <f t="array" ref="N107">SECTION_NAME(B107)</f>
-        <v>ci-c-spec-57</v>
+        <v>ci-c-spec-56</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G108" s="8" t="b">
         <v>0</v>
@@ -7872,27 +8125,27 @@
       </c>
       <c r="N108" s="9" t="str" cm="1">
         <f t="array" ref="N108">SECTION_NAME(B108)</f>
-        <v>ci-c-spec-58</v>
+        <v>ci-c-spec-57</v>
       </c>
       <c r="P108" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G109" s="8" t="b">
         <v>0</v>
@@ -7903,21 +8156,21 @@
       </c>
       <c r="N109" s="9" t="str" cm="1">
         <f t="array" ref="N109">SECTION_NAME(B109)</f>
-        <v>ci-c-spec-59</v>
+        <v>ci-c-spec-58</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A110" s="7" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>26</v>
@@ -7934,27 +8187,27 @@
       </c>
       <c r="N110" s="9" t="str" cm="1">
         <f t="array" ref="N110">SECTION_NAME(B110)</f>
-        <v>ci-c-spec-60</v>
+        <v>ci-c-spec-59</v>
       </c>
       <c r="P110" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G111" s="8" t="b">
         <v>0</v>
@@ -7965,27 +8218,27 @@
       </c>
       <c r="N111" s="9" t="str" cm="1">
         <f t="array" ref="N111">SECTION_NAME(B111)</f>
-        <v>ci-c-spec-61</v>
+        <v>ci-c-spec-60</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="238" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A112" s="7" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G112" s="8" t="b">
         <v>0</v>
@@ -7996,24 +8249,24 @@
       </c>
       <c r="N112" s="9" t="str" cm="1">
         <f t="array" ref="N112">SECTION_NAME(B112)</f>
-        <v>ci-c-spec-62</v>
+        <v>ci-c-spec-61</v>
       </c>
       <c r="P112" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="238" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E113" s="8" t="s">
         <v>91</v>
@@ -8027,24 +8280,24 @@
       </c>
       <c r="N113" s="9" t="str" cm="1">
         <f t="array" ref="N113">SECTION_NAME(B113)</f>
-        <v>ci-c-spec-63</v>
+        <v>ci-c-spec-62</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>91</v>
@@ -8058,21 +8311,21 @@
       </c>
       <c r="N114" s="9" t="str" cm="1">
         <f t="array" ref="N114">SECTION_NAME(B114)</f>
-        <v>ci-c-spec-64</v>
+        <v>ci-c-spec-63</v>
       </c>
       <c r="P114" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>26</v>
@@ -8081,7 +8334,7 @@
         <v>91</v>
       </c>
       <c r="G115" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" s="9" t="str" cm="1">
         <f t="array" ref="M115">PAGE_NAME(B115)</f>
@@ -8089,21 +8342,21 @@
       </c>
       <c r="N115" s="9" t="str" cm="1">
         <f t="array" ref="N115">SECTION_NAME(B115)</f>
-        <v>ci-c-spec-65</v>
+        <v>ci-c-spec-64</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>26</v>
@@ -8112,7 +8365,7 @@
         <v>91</v>
       </c>
       <c r="G116" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="9" t="str" cm="1">
         <f t="array" ref="M116">PAGE_NAME(B116)</f>
@@ -8120,21 +8373,21 @@
       </c>
       <c r="N116" s="9" t="str" cm="1">
         <f t="array" ref="N116">SECTION_NAME(B116)</f>
-        <v>ci-c-spec-66</v>
+        <v>ci-c-spec-65</v>
       </c>
       <c r="P116" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A117" s="7" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>731</v>
+        <v>424</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>26</v>
@@ -8143,7 +8396,7 @@
         <v>91</v>
       </c>
       <c r="G117" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="9" t="str" cm="1">
         <f t="array" ref="M117">PAGE_NAME(B117)</f>
@@ -8151,21 +8404,21 @@
       </c>
       <c r="N117" s="9" t="str" cm="1">
         <f t="array" ref="N117">SECTION_NAME(B117)</f>
-        <v>ci-c-spec-67</v>
+        <v>ci-c-spec-66</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A118" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>431</v>
+        <v>728</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>26</v>
@@ -8182,30 +8435,30 @@
       </c>
       <c r="N118" s="9" t="str" cm="1">
         <f t="array" ref="N118">SECTION_NAME(B118)</f>
-        <v>ci-c-spec-68</v>
+        <v>ci-c-spec-67</v>
       </c>
       <c r="P118" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G119" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="9" t="str" cm="1">
         <f t="array" ref="M119">PAGE_NAME(B119)</f>
@@ -8213,24 +8466,24 @@
       </c>
       <c r="N119" s="9" t="str" cm="1">
         <f t="array" ref="N119">SECTION_NAME(B119)</f>
-        <v>ci-c-spec-69</v>
+        <v>ci-c-spec-68</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A120" s="7" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>91</v>
@@ -8244,30 +8497,30 @@
       </c>
       <c r="N120" s="9" t="str" cm="1">
         <f t="array" ref="N120">SECTION_NAME(B120)</f>
-        <v>ci-c-spec-70</v>
+        <v>ci-c-spec-69</v>
       </c>
       <c r="P120" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E121" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G121" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="9" t="str" cm="1">
         <f t="array" ref="M121">PAGE_NAME(B121)</f>
@@ -8275,24 +8528,24 @@
       </c>
       <c r="N121" s="9" t="str" cm="1">
         <f t="array" ref="N121">SECTION_NAME(B121)</f>
-        <v>ci-c-spec-71</v>
+        <v>ci-c-spec-70</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A122" s="7" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="E122" s="8" t="s">
         <v>91</v>
@@ -8306,24 +8559,24 @@
       </c>
       <c r="N122" s="9" t="str" cm="1">
         <f t="array" ref="N122">SECTION_NAME(B122)</f>
-        <v>ci-c-spec-72</v>
+        <v>ci-c-spec-71</v>
       </c>
       <c r="P122" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A123" s="7" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E123" s="8" t="s">
         <v>91</v>
@@ -8337,21 +8590,21 @@
       </c>
       <c r="N123" s="9" t="str" cm="1">
         <f t="array" ref="N123">SECTION_NAME(B123)</f>
-        <v>ci-c-spec-73</v>
+        <v>ci-c-spec-72</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>26</v>
@@ -8368,24 +8621,24 @@
       </c>
       <c r="N124" s="9" t="str" cm="1">
         <f t="array" ref="N124">SECTION_NAME(B124)</f>
-        <v>ci-c-spec-74</v>
+        <v>ci-c-spec-73</v>
       </c>
       <c r="P124" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E125" s="8" t="s">
         <v>91</v>
@@ -8399,24 +8652,24 @@
       </c>
       <c r="N125" s="9" t="str" cm="1">
         <f t="array" ref="N125">SECTION_NAME(B125)</f>
-        <v>ci-c-spec-75</v>
+        <v>ci-c-spec-74</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>91</v>
@@ -8430,24 +8683,24 @@
       </c>
       <c r="N126" s="9" t="str" cm="1">
         <f t="array" ref="N126">SECTION_NAME(B126)</f>
-        <v>ci-c-spec-76</v>
+        <v>ci-c-spec-75</v>
       </c>
       <c r="P126" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>91</v>
@@ -8461,30 +8714,30 @@
       </c>
       <c r="N127" s="9" t="str" cm="1">
         <f t="array" ref="N127">SECTION_NAME(B127)</f>
-        <v>ci-c-spec-77</v>
+        <v>ci-c-spec-76</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A128" s="7" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G128" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="9" t="str" cm="1">
         <f t="array" ref="M128">PAGE_NAME(B128)</f>
@@ -8492,21 +8745,21 @@
       </c>
       <c r="N128" s="9" t="str" cm="1">
         <f t="array" ref="N128">SECTION_NAME(B128)</f>
-        <v>ci-c-spec-78</v>
+        <v>ci-c-spec-77</v>
       </c>
       <c r="P128" s="10" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A129" s="7" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>26</v>
@@ -8515,7 +8768,7 @@
         <v>91</v>
       </c>
       <c r="G129" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" s="9" t="str" cm="1">
         <f t="array" ref="M129">PAGE_NAME(B129)</f>
@@ -8523,24 +8776,24 @@
       </c>
       <c r="N129" s="9" t="str" cm="1">
         <f t="array" ref="N129">SECTION_NAME(B129)</f>
-        <v>ci-c-spec-79</v>
+        <v>ci-c-spec-78</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A130" s="7" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E130" s="8" t="s">
         <v>91</v>
@@ -8554,24 +8807,24 @@
       </c>
       <c r="N130" s="9" t="str" cm="1">
         <f t="array" ref="N130">SECTION_NAME(B130)</f>
-        <v>ci-c-spec-80</v>
+        <v>ci-c-spec-79</v>
       </c>
       <c r="P130" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A131" s="7" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E131" s="8" t="s">
         <v>91</v>
@@ -8585,30 +8838,30 @@
       </c>
       <c r="N131" s="9" t="str" cm="1">
         <f t="array" ref="N131">SECTION_NAME(B131)</f>
-        <v>ci-c-spec-81</v>
+        <v>ci-c-spec-80</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A132" s="7" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E132" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G132" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="9" t="str" cm="1">
         <f t="array" ref="M132">PAGE_NAME(B132)</f>
@@ -8616,27 +8869,27 @@
       </c>
       <c r="N132" s="9" t="str" cm="1">
         <f t="array" ref="N132">SECTION_NAME(B132)</f>
-        <v>ci-c-spec-82</v>
+        <v>ci-c-spec-81</v>
       </c>
       <c r="P132" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A133" s="7" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G133" s="8" t="b">
         <v>0</v>
@@ -8647,27 +8900,27 @@
       </c>
       <c r="N133" s="9" t="str" cm="1">
         <f t="array" ref="N133">SECTION_NAME(B133)</f>
-        <v>ci-c-spec-83</v>
+        <v>ci-c-spec-82</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A134" s="7" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G134" s="8" t="b">
         <v>0</v>
@@ -8678,27 +8931,27 @@
       </c>
       <c r="N134" s="9" t="str" cm="1">
         <f t="array" ref="N134">SECTION_NAME(B134)</f>
-        <v>ci-c-spec-84</v>
+        <v>ci-c-spec-83</v>
       </c>
       <c r="P134" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A135" s="7" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G135" s="8" t="b">
         <v>0</v>
@@ -8709,24 +8962,24 @@
       </c>
       <c r="N135" s="9" t="str" cm="1">
         <f t="array" ref="N135">SECTION_NAME(B135)</f>
-        <v>ci-c-spec-85</v>
+        <v>ci-c-spec-84</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A136" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E136" s="8" t="s">
         <v>107</v>
@@ -8740,24 +8993,24 @@
       </c>
       <c r="N136" s="9" t="str" cm="1">
         <f t="array" ref="N136">SECTION_NAME(B136)</f>
-        <v>ci-c-spec-86</v>
+        <v>ci-c-spec-85</v>
       </c>
       <c r="P136" s="10" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="137" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A137" s="7" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E137" s="8" t="s">
         <v>107</v>
@@ -8771,24 +9024,24 @@
       </c>
       <c r="N137" s="9" t="str" cm="1">
         <f t="array" ref="N137">SECTION_NAME(B137)</f>
-        <v>ci-c-spec-87</v>
+        <v>ci-c-spec-86</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A138" s="7" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>258</v>
+        <v>26</v>
       </c>
       <c r="E138" s="8" t="s">
         <v>107</v>
@@ -8802,27 +9055,27 @@
       </c>
       <c r="N138" s="9" t="str" cm="1">
         <f t="array" ref="N138">SECTION_NAME(B138)</f>
-        <v>ci-c-spec-88</v>
+        <v>ci-c-spec-87</v>
       </c>
       <c r="P138" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A139" s="7" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>30</v>
+        <v>256</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G139" s="8" t="b">
         <v>0</v>
@@ -8833,27 +9086,27 @@
       </c>
       <c r="N139" s="9" t="str" cm="1">
         <f t="array" ref="N139">SECTION_NAME(B139)</f>
-        <v>ci-c-spec-89</v>
+        <v>ci-c-spec-88</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G140" s="8" t="b">
         <v>0</v>
@@ -8864,21 +9117,21 @@
       </c>
       <c r="N140" s="9" t="str" cm="1">
         <f t="array" ref="N140">SECTION_NAME(B140)</f>
-        <v>ci-c-spec-90</v>
+        <v>ci-c-spec-89</v>
       </c>
       <c r="P140" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A141" s="7" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>29</v>
@@ -8895,24 +9148,24 @@
       </c>
       <c r="N141" s="9" t="str" cm="1">
         <f t="array" ref="N141">SECTION_NAME(B141)</f>
-        <v>ci-c-spec-91</v>
+        <v>ci-c-spec-90</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E142" s="8" t="s">
         <v>107</v>
@@ -8926,21 +9179,21 @@
       </c>
       <c r="N142" s="9" t="str" cm="1">
         <f t="array" ref="N142">SECTION_NAME(B142)</f>
-        <v>ci-c-spec-92</v>
+        <v>ci-c-spec-91</v>
       </c>
       <c r="P142" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>26</v>
@@ -8957,21 +9210,21 @@
       </c>
       <c r="N143" s="9" t="str" cm="1">
         <f t="array" ref="N143">SECTION_NAME(B143)</f>
-        <v>ci-c-spec-93</v>
+        <v>ci-c-spec-92</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A144" s="7" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>26</v>
@@ -8988,21 +9241,21 @@
       </c>
       <c r="N144" s="9" t="str" cm="1">
         <f t="array" ref="N144">SECTION_NAME(B144)</f>
-        <v>ci-c-spec-94</v>
+        <v>ci-c-spec-93</v>
       </c>
       <c r="P144" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A145" s="7" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>26</v>
@@ -9019,21 +9272,21 @@
       </c>
       <c r="N145" s="9" t="str" cm="1">
         <f t="array" ref="N145">SECTION_NAME(B145)</f>
-        <v>ci-c-spec-95</v>
+        <v>ci-c-spec-94</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A146" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>26</v>
@@ -9050,21 +9303,21 @@
       </c>
       <c r="N146" s="9" t="str" cm="1">
         <f t="array" ref="N146">SECTION_NAME(B146)</f>
-        <v>ci-c-spec-96</v>
+        <v>ci-c-spec-95</v>
       </c>
       <c r="P146" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" ht="170" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>26</v>
@@ -9073,7 +9326,7 @@
         <v>107</v>
       </c>
       <c r="G147" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="9" t="str" cm="1">
         <f t="array" ref="M147">PAGE_NAME(B147)</f>
@@ -9081,30 +9334,30 @@
       </c>
       <c r="N147" s="9" t="str" cm="1">
         <f t="array" ref="N147">SECTION_NAME(B147)</f>
-        <v>ci-c-spec-97</v>
+        <v>ci-c-spec-96</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>268</v>
+        <v>26</v>
       </c>
       <c r="E148" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G148" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" s="9" t="str" cm="1">
         <f t="array" ref="M148">PAGE_NAME(B148)</f>
@@ -9112,24 +9365,24 @@
       </c>
       <c r="N148" s="9" t="str" cm="1">
         <f t="array" ref="N148">SECTION_NAME(B148)</f>
-        <v>ci-c-spec-98</v>
+        <v>ci-c-spec-97</v>
       </c>
       <c r="P148" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A149" s="7" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>26</v>
+        <v>266</v>
       </c>
       <c r="E149" s="8" t="s">
         <v>107</v>
@@ -9143,27 +9396,27 @@
       </c>
       <c r="N149" s="9" t="str" cm="1">
         <f t="array" ref="N149">SECTION_NAME(B149)</f>
-        <v>ci-c-spec-99</v>
+        <v>ci-c-spec-98</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G150" s="8" t="b">
         <v>0</v>
@@ -9174,30 +9427,30 @@
       </c>
       <c r="N150" s="9" t="str" cm="1">
         <f t="array" ref="N150">SECTION_NAME(B150)</f>
-        <v>ci-c-spec-100</v>
+        <v>ci-c-spec-99</v>
       </c>
       <c r="P150" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E151" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G151" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" s="9" t="str" cm="1">
         <f t="array" ref="M151">PAGE_NAME(B151)</f>
@@ -9205,21 +9458,21 @@
       </c>
       <c r="N151" s="9" t="str" cm="1">
         <f t="array" ref="N151">SECTION_NAME(B151)</f>
-        <v>ci-c-spec-101</v>
+        <v>ci-c-spec-100</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A152" s="7" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>26</v>
@@ -9228,7 +9481,7 @@
         <v>91</v>
       </c>
       <c r="G152" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="9" t="str" cm="1">
         <f t="array" ref="M152">PAGE_NAME(B152)</f>
@@ -9236,21 +9489,21 @@
       </c>
       <c r="N152" s="9" t="str" cm="1">
         <f t="array" ref="N152">SECTION_NAME(B152)</f>
-        <v>ci-c-spec-102</v>
+        <v>ci-c-spec-101</v>
       </c>
       <c r="P152" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A153" s="7" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>26</v>
@@ -9259,7 +9512,7 @@
         <v>91</v>
       </c>
       <c r="G153" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" s="9" t="str" cm="1">
         <f t="array" ref="M153">PAGE_NAME(B153)</f>
@@ -9267,21 +9520,21 @@
       </c>
       <c r="N153" s="9" t="str" cm="1">
         <f t="array" ref="N153">SECTION_NAME(B153)</f>
-        <v>ci-c-spec-103</v>
+        <v>ci-c-spec-102</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>36</v>
+        <v>534</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>26</v>
@@ -9290,7 +9543,7 @@
         <v>91</v>
       </c>
       <c r="G154" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="9" t="str" cm="1">
         <f t="array" ref="M154">PAGE_NAME(B154)</f>
@@ -9298,21 +9551,21 @@
       </c>
       <c r="N154" s="9" t="str" cm="1">
         <f t="array" ref="N154">SECTION_NAME(B154)</f>
-        <v>ci-c-spec-104</v>
+        <v>ci-c-spec-103</v>
       </c>
       <c r="P154" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A155" s="7" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>541</v>
+        <v>36</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>26</v>
@@ -9329,27 +9582,27 @@
       </c>
       <c r="N155" s="9" t="str" cm="1">
         <f t="array" ref="N155">SECTION_NAME(B155)</f>
-        <v>ci-c-spec-105</v>
+        <v>ci-c-spec-104</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G156" s="8" t="b">
         <v>0</v>
@@ -9360,27 +9613,27 @@
       </c>
       <c r="N156" s="9" t="str" cm="1">
         <f t="array" ref="N156">SECTION_NAME(B156)</f>
-        <v>ci-c-spec-106</v>
+        <v>ci-c-spec-105</v>
       </c>
       <c r="P156" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A157" s="7" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D157" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G157" s="8" t="b">
         <v>0</v>
@@ -9391,30 +9644,30 @@
       </c>
       <c r="N157" s="9" t="str" cm="1">
         <f t="array" ref="N157">SECTION_NAME(B157)</f>
-        <v>ci-c-spec-107</v>
+        <v>ci-c-spec-106</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>549</v>
+        <v>543</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>544</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E158" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G158" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="9" t="str" cm="1">
         <f t="array" ref="M158">PAGE_NAME(B158)</f>
@@ -9422,30 +9675,30 @@
       </c>
       <c r="N158" s="9" t="str" cm="1">
         <f t="array" ref="N158">SECTION_NAME(B158)</f>
-        <v>ci-c-spec-108</v>
+        <v>ci-c-spec-107</v>
       </c>
       <c r="P158" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A159" s="7" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E159" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G159" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="9" t="str" cm="1">
         <f t="array" ref="M159">PAGE_NAME(B159)</f>
@@ -9453,30 +9706,30 @@
       </c>
       <c r="N159" s="9" t="str" cm="1">
         <f t="array" ref="N159">SECTION_NAME(B159)</f>
-        <v>ci-c-spec-109</v>
+        <v>ci-c-spec-108</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A160" s="7" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G160" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="9" t="str" cm="1">
         <f t="array" ref="M160">PAGE_NAME(B160)</f>
@@ -9484,30 +9737,30 @@
       </c>
       <c r="N160" s="9" t="str" cm="1">
         <f t="array" ref="N160">SECTION_NAME(B160)</f>
-        <v>ci-c-spec-110</v>
+        <v>ci-c-spec-109</v>
       </c>
       <c r="P160" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A161" s="7" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G161" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="9" t="str" cm="1">
         <f t="array" ref="M161">PAGE_NAME(B161)</f>
@@ -9515,21 +9768,21 @@
       </c>
       <c r="N161" s="9" t="str" cm="1">
         <f t="array" ref="N161">SECTION_NAME(B161)</f>
-        <v>ci-c-spec-111</v>
+        <v>ci-c-spec-110</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="D162" s="7" t="s">
         <v>26</v>
@@ -9546,24 +9799,24 @@
       </c>
       <c r="N162" s="9" t="str" cm="1">
         <f t="array" ref="N162">SECTION_NAME(B162)</f>
-        <v>ci-c-spec-112</v>
+        <v>ci-c-spec-111</v>
       </c>
       <c r="P162" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="163" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E163" s="8" t="s">
         <v>91</v>
@@ -9577,30 +9830,30 @@
       </c>
       <c r="N163" s="9" t="str" cm="1">
         <f t="array" ref="N163">SECTION_NAME(B163)</f>
-        <v>ci-c-spec-113</v>
+        <v>ci-c-spec-112</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E164" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G164" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="9" t="str" cm="1">
         <f t="array" ref="M164">PAGE_NAME(B164)</f>
@@ -9608,30 +9861,30 @@
       </c>
       <c r="N164" s="9" t="str" cm="1">
         <f t="array" ref="N164">SECTION_NAME(B164)</f>
-        <v>ci-c-spec-114</v>
+        <v>ci-c-spec-113</v>
       </c>
       <c r="P164" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G165" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="9" t="str" cm="1">
         <f t="array" ref="M165">PAGE_NAME(B165)</f>
@@ -9639,27 +9892,27 @@
       </c>
       <c r="N165" s="9" t="str" cm="1">
         <f t="array" ref="N165">SECTION_NAME(B165)</f>
-        <v>ci-c-spec-115</v>
+        <v>ci-c-spec-114</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A166" s="7" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G166" s="8" t="b">
         <v>0</v>
@@ -9670,30 +9923,30 @@
       </c>
       <c r="N166" s="9" t="str" cm="1">
         <f t="array" ref="N166">SECTION_NAME(B166)</f>
-        <v>ci-c-spec-116</v>
+        <v>ci-c-spec-115</v>
       </c>
       <c r="P166" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D167" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G167" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" s="9" t="str" cm="1">
         <f t="array" ref="M167">PAGE_NAME(B167)</f>
@@ -9701,30 +9954,30 @@
       </c>
       <c r="N167" s="9" t="str" cm="1">
         <f t="array" ref="N167">SECTION_NAME(B167)</f>
-        <v>ci-c-spec-117</v>
+        <v>ci-c-spec-116</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>38</v>
+        <v>575</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E168" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G168" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" s="9" t="str" cm="1">
         <f t="array" ref="M168">PAGE_NAME(B168)</f>
@@ -9732,24 +9985,24 @@
       </c>
       <c r="N168" s="9" t="str" cm="1">
         <f t="array" ref="N168">SECTION_NAME(B168)</f>
-        <v>ci-c-spec-118</v>
+        <v>ci-c-spec-117</v>
       </c>
       <c r="P168" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A169" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>582</v>
+        <v>38</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E169" s="8" t="s">
         <v>91</v>
@@ -9763,27 +10016,27 @@
       </c>
       <c r="N169" s="9" t="str" cm="1">
         <f t="array" ref="N169">SECTION_NAME(B169)</f>
-        <v>ci-c-spec-119</v>
+        <v>ci-c-spec-118</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="170" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D170" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G170" s="8" t="b">
         <v>0</v>
@@ -9794,30 +10047,30 @@
       </c>
       <c r="N170" s="9" t="str" cm="1">
         <f t="array" ref="N170">SECTION_NAME(B170)</f>
-        <v>ci-c-spec-120</v>
+        <v>ci-c-spec-119</v>
       </c>
       <c r="P170" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A171" s="7" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D171" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G171" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" s="9" t="str" cm="1">
         <f t="array" ref="M171">PAGE_NAME(B171)</f>
@@ -9825,27 +10078,27 @@
       </c>
       <c r="N171" s="9" t="str" cm="1">
         <f t="array" ref="N171">SECTION_NAME(B171)</f>
-        <v>ci-c-spec-121</v>
+        <v>ci-c-spec-120</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>591</v>
+        <v>729</v>
       </c>
       <c r="D172" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G172" s="8" t="b">
         <v>1</v>
@@ -9856,27 +10109,27 @@
       </c>
       <c r="N172" s="9" t="str" cm="1">
         <f t="array" ref="N172">SECTION_NAME(B172)</f>
-        <v>ci-c-spec-122</v>
+        <v>ci-c-spec-121</v>
       </c>
       <c r="P172" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A173" s="7" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D173" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G173" s="8" t="b">
         <v>1</v>
@@ -9887,24 +10140,24 @@
       </c>
       <c r="N173" s="9" t="str" cm="1">
         <f t="array" ref="N173">SECTION_NAME(B173)</f>
-        <v>ci-c-spec-123</v>
+        <v>ci-c-spec-122</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A174" s="7" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E174" s="8" t="s">
         <v>91</v>
@@ -9918,30 +10171,30 @@
       </c>
       <c r="N174" s="9" t="str" cm="1">
         <f t="array" ref="N174">SECTION_NAME(B174)</f>
-        <v>ci-c-spec-124</v>
+        <v>ci-c-spec-123</v>
       </c>
       <c r="P174" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E175" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G175" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175" s="9" t="str" cm="1">
         <f t="array" ref="M175">PAGE_NAME(B175)</f>
@@ -9949,30 +10202,30 @@
       </c>
       <c r="N175" s="9" t="str" cm="1">
         <f t="array" ref="N175">SECTION_NAME(B175)</f>
-        <v>ci-c-spec-125</v>
+        <v>ci-c-spec-124</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E176" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G176" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M176" s="9" t="str" cm="1">
         <f t="array" ref="M176">PAGE_NAME(B176)</f>
@@ -9980,30 +10233,30 @@
       </c>
       <c r="N176" s="9" t="str" cm="1">
         <f t="array" ref="N176">SECTION_NAME(B176)</f>
-        <v>ci-c-spec-126</v>
+        <v>ci-c-spec-125</v>
       </c>
       <c r="P176" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A177" s="7" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E177" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G177" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" s="9" t="str" cm="1">
         <f t="array" ref="M177">PAGE_NAME(B177)</f>
@@ -10011,27 +10264,27 @@
       </c>
       <c r="N177" s="9" t="str" cm="1">
         <f t="array" ref="N177">SECTION_NAME(B177)</f>
-        <v>ci-c-spec-127</v>
+        <v>ci-c-spec-126</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="7" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G178" s="8" t="b">
         <v>0</v>
@@ -10042,30 +10295,30 @@
       </c>
       <c r="N178" s="9" t="str" cm="1">
         <f t="array" ref="N178">SECTION_NAME(B178)</f>
-        <v>ci-c-spec-128</v>
+        <v>ci-c-spec-127</v>
       </c>
       <c r="P178" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A179" s="7" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E179" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G179" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M179" s="9" t="str" cm="1">
         <f t="array" ref="M179">PAGE_NAME(B179)</f>
@@ -10073,24 +10326,24 @@
       </c>
       <c r="N179" s="9" t="str" cm="1">
         <f t="array" ref="N179">SECTION_NAME(B179)</f>
-        <v>ci-c-spec-129</v>
+        <v>ci-c-spec-128</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A180" s="7" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E180" s="8" t="s">
         <v>107</v>
@@ -10104,30 +10357,30 @@
       </c>
       <c r="N180" s="9" t="str" cm="1">
         <f t="array" ref="N180">SECTION_NAME(B180)</f>
-        <v>ci-c-spec-130</v>
+        <v>ci-c-spec-129</v>
       </c>
       <c r="P180" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A181" s="7" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G181" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" s="9" t="str" cm="1">
         <f t="array" ref="M181">PAGE_NAME(B181)</f>
@@ -10135,24 +10388,24 @@
       </c>
       <c r="N181" s="9" t="str" cm="1">
         <f t="array" ref="N181">SECTION_NAME(B181)</f>
-        <v>ci-c-spec-131</v>
+        <v>ci-c-spec-130</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A182" s="7" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E182" s="8" t="s">
         <v>91</v>
@@ -10166,27 +10419,27 @@
       </c>
       <c r="N182" s="9" t="str" cm="1">
         <f t="array" ref="N182">SECTION_NAME(B182)</f>
-        <v>ci-c-spec-132</v>
+        <v>ci-c-spec-131</v>
       </c>
       <c r="P182" s="10" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="183" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A183" s="7" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G183" s="8" t="b">
         <v>0</v>
@@ -10197,21 +10450,21 @@
       </c>
       <c r="N183" s="9" t="str" cm="1">
         <f t="array" ref="N183">SECTION_NAME(B183)</f>
-        <v>ci-c-spec-133</v>
+        <v>ci-c-spec-132</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D184" s="7" t="s">
         <v>29</v>
@@ -10228,27 +10481,27 @@
       </c>
       <c r="N184" s="9" t="str" cm="1">
         <f t="array" ref="N184">SECTION_NAME(B184)</f>
-        <v>ci-c-spec-134</v>
+        <v>ci-c-spec-133</v>
       </c>
       <c r="P184" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="185" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A185" s="7" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G185" s="8" t="b">
         <v>0</v>
@@ -10259,21 +10512,21 @@
       </c>
       <c r="N185" s="9" t="str" cm="1">
         <f t="array" ref="N185">SECTION_NAME(B185)</f>
-        <v>ci-c-spec-135</v>
+        <v>ci-c-spec-134</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A186" s="7" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>39</v>
+        <v>627</v>
       </c>
       <c r="D186" s="7" t="s">
         <v>26</v>
@@ -10290,21 +10543,21 @@
       </c>
       <c r="N186" s="9" t="str" cm="1">
         <f t="array" ref="N186">SECTION_NAME(B186)</f>
-        <v>ci-c-spec-136</v>
+        <v>ci-c-spec-135</v>
       </c>
       <c r="P186" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>635</v>
+        <v>39</v>
       </c>
       <c r="D187" s="7" t="s">
         <v>26</v>
@@ -10313,7 +10566,7 @@
         <v>91</v>
       </c>
       <c r="G187" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M187" s="9" t="str" cm="1">
         <f t="array" ref="M187">PAGE_NAME(B187)</f>
@@ -10321,21 +10574,21 @@
       </c>
       <c r="N187" s="9" t="str" cm="1">
         <f t="array" ref="N187">SECTION_NAME(B187)</f>
-        <v>ci-c-spec-137</v>
+        <v>ci-c-spec-136</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D188" s="7" t="s">
         <v>26</v>
@@ -10344,7 +10597,7 @@
         <v>91</v>
       </c>
       <c r="G188" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" s="9" t="str" cm="1">
         <f t="array" ref="M188">PAGE_NAME(B188)</f>
@@ -10352,27 +10605,27 @@
       </c>
       <c r="N188" s="9" t="str" cm="1">
         <f t="array" ref="N188">SECTION_NAME(B188)</f>
-        <v>ci-c-spec-138</v>
+        <v>ci-c-spec-137</v>
       </c>
       <c r="P188" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="189" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A189" s="7" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="D189" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G189" s="8" t="b">
         <v>0</v>
@@ -10383,21 +10636,21 @@
       </c>
       <c r="N189" s="9" t="str" cm="1">
         <f t="array" ref="N189">SECTION_NAME(B189)</f>
-        <v>ci-c-spec-139</v>
+        <v>ci-c-spec-138</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="190" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A190" s="7" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D190" s="7" t="s">
         <v>26</v>
@@ -10414,21 +10667,21 @@
       </c>
       <c r="N190" s="9" t="str" cm="1">
         <f t="array" ref="N190">SECTION_NAME(B190)</f>
-        <v>ci-c-spec-140</v>
+        <v>ci-c-spec-139</v>
       </c>
       <c r="P190" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="191" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A191" s="7" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="D191" s="7" t="s">
         <v>26</v>
@@ -10445,27 +10698,27 @@
       </c>
       <c r="N191" s="9" t="str" cm="1">
         <f t="array" ref="N191">SECTION_NAME(B191)</f>
-        <v>ci-c-spec-141</v>
+        <v>ci-c-spec-140</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A192" s="7" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>40</v>
+        <v>644</v>
       </c>
       <c r="D192" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G192" s="8" t="b">
         <v>0</v>
@@ -10476,21 +10729,21 @@
       </c>
       <c r="N192" s="9" t="str" cm="1">
         <f t="array" ref="N192">SECTION_NAME(B192)</f>
-        <v>ci-c-spec-142</v>
+        <v>ci-c-spec-141</v>
       </c>
       <c r="P192" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A193" s="7" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D193" s="7" t="s">
         <v>26</v>
@@ -10507,30 +10760,30 @@
       </c>
       <c r="N193" s="9" t="str" cm="1">
         <f t="array" ref="N193">SECTION_NAME(B193)</f>
-        <v>ci-c-spec-143</v>
+        <v>ci-c-spec-142</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>654</v>
+        <v>41</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>655</v>
+        <v>26</v>
       </c>
       <c r="E194" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G194" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M194" s="9" t="str" cm="1">
         <f t="array" ref="M194">PAGE_NAME(B194)</f>
@@ -10538,30 +10791,30 @@
       </c>
       <c r="N194" s="9" t="str" cm="1">
         <f t="array" ref="N194">SECTION_NAME(B194)</f>
-        <v>ci-c-spec-144</v>
+        <v>ci-c-spec-143</v>
       </c>
       <c r="P194" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A195" s="7" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>31</v>
+        <v>652</v>
       </c>
       <c r="E195" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G195" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" s="9" t="str" cm="1">
         <f t="array" ref="M195">PAGE_NAME(B195)</f>
@@ -10569,21 +10822,21 @@
       </c>
       <c r="N195" s="9" t="str" cm="1">
         <f t="array" ref="N195">SECTION_NAME(B195)</f>
-        <v>ci-c-spec-145</v>
+        <v>ci-c-spec-144</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A196" s="7" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>31</v>
@@ -10600,30 +10853,30 @@
       </c>
       <c r="N196" s="9" t="str" cm="1">
         <f t="array" ref="N196">SECTION_NAME(B196)</f>
-        <v>ci-c-spec-146</v>
+        <v>ci-c-spec-145</v>
       </c>
       <c r="P196" s="10" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A197" s="7" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G197" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" s="9" t="str" cm="1">
         <f t="array" ref="M197">PAGE_NAME(B197)</f>
@@ -10631,30 +10884,30 @@
       </c>
       <c r="N197" s="9" t="str" cm="1">
         <f t="array" ref="N197">SECTION_NAME(B197)</f>
-        <v>ci-c-spec-147</v>
+        <v>ci-c-spec-146</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A198" s="7" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E198" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G198" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M198" s="9" t="str" cm="1">
         <f t="array" ref="M198">PAGE_NAME(B198)</f>
@@ -10662,27 +10915,27 @@
       </c>
       <c r="N198" s="9" t="str" cm="1">
         <f t="array" ref="N198">SECTION_NAME(B198)</f>
-        <v>ci-c-spec-148</v>
+        <v>ci-c-spec-147</v>
       </c>
       <c r="P198" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A199" s="7" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D199" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G199" s="8" t="b">
         <v>0</v>
@@ -10693,24 +10946,24 @@
       </c>
       <c r="N199" s="9" t="str" cm="1">
         <f t="array" ref="N199">SECTION_NAME(B199)</f>
-        <v>ci-c-spec-149</v>
+        <v>ci-c-spec-148</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A200" s="7" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E200" s="8" t="s">
         <v>91</v>
@@ -10724,21 +10977,21 @@
       </c>
       <c r="N200" s="9" t="str" cm="1">
         <f t="array" ref="N200">SECTION_NAME(B200)</f>
-        <v>ci-c-spec-150</v>
+        <v>ci-c-spec-149</v>
       </c>
       <c r="P200" s="10" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="201" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A201" s="7" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D201" s="7" t="s">
         <v>26</v>
@@ -10755,21 +11008,21 @@
       </c>
       <c r="N201" s="9" t="str" cm="1">
         <f t="array" ref="N201">SECTION_NAME(B201)</f>
-        <v>ci-c-spec-151</v>
+        <v>ci-c-spec-150</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A202" s="7" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D202" s="7" t="s">
         <v>26</v>
@@ -10778,7 +11031,7 @@
         <v>91</v>
       </c>
       <c r="G202" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M202" s="9" t="str" cm="1">
         <f t="array" ref="M202">PAGE_NAME(B202)</f>
@@ -10786,21 +11039,21 @@
       </c>
       <c r="N202" s="9" t="str" cm="1">
         <f t="array" ref="N202">SECTION_NAME(B202)</f>
-        <v>ci-c-spec-152</v>
+        <v>ci-c-spec-151</v>
       </c>
       <c r="P202" s="10" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D203" s="7" t="s">
         <v>26</v>
@@ -10817,21 +11070,21 @@
       </c>
       <c r="N203" s="9" t="str" cm="1">
         <f t="array" ref="N203">SECTION_NAME(B203)</f>
-        <v>ci-c-spec-153</v>
+        <v>ci-c-spec-152</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D204" s="7" t="s">
         <v>26</v>
@@ -10840,7 +11093,7 @@
         <v>91</v>
       </c>
       <c r="G204" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" s="9" t="str" cm="1">
         <f t="array" ref="M204">PAGE_NAME(B204)</f>
@@ -10848,21 +11101,21 @@
       </c>
       <c r="N204" s="9" t="str" cm="1">
         <f t="array" ref="N204">SECTION_NAME(B204)</f>
-        <v>ci-c-spec-154</v>
+        <v>ci-c-spec-153</v>
       </c>
       <c r="P204" s="10" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:16" ht="204" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="D205" s="7" t="s">
         <v>26</v>
@@ -10871,7 +11124,7 @@
         <v>91</v>
       </c>
       <c r="G205" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" s="9" t="str" cm="1">
         <f t="array" ref="M205">PAGE_NAME(B205)</f>
@@ -10879,21 +11132,21 @@
       </c>
       <c r="N205" s="9" t="str" cm="1">
         <f t="array" ref="N205">SECTION_NAME(B205)</f>
-        <v>ci-c-spec-155</v>
+        <v>ci-c-spec-154</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A206" s="7" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D206" s="7" t="s">
         <v>26</v>
@@ -10902,7 +11155,7 @@
         <v>91</v>
       </c>
       <c r="G206" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M206" s="9" t="str" cm="1">
         <f t="array" ref="M206">PAGE_NAME(B206)</f>
@@ -10910,21 +11163,21 @@
       </c>
       <c r="N206" s="9" t="str" cm="1">
         <f t="array" ref="N206">SECTION_NAME(B206)</f>
-        <v>ci-c-spec-156</v>
+        <v>ci-c-spec-155</v>
       </c>
       <c r="P206" s="10" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D207" s="7" t="s">
         <v>26</v>
@@ -10941,21 +11194,21 @@
       </c>
       <c r="N207" s="9" t="str" cm="1">
         <f t="array" ref="N207">SECTION_NAME(B207)</f>
-        <v>ci-c-spec-157</v>
+        <v>ci-c-spec-156</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A208" s="7" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D208" s="7" t="s">
         <v>26</v>
@@ -10972,30 +11225,30 @@
       </c>
       <c r="N208" s="9" t="str" cm="1">
         <f t="array" ref="N208">SECTION_NAME(B208)</f>
-        <v>ci-c-spec-158</v>
+        <v>ci-c-spec-157</v>
       </c>
       <c r="P208" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" ht="221" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D209" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G209" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M209" s="9" t="str" cm="1">
         <f t="array" ref="M209">PAGE_NAME(B209)</f>
@@ -11003,21 +11256,21 @@
       </c>
       <c r="N209" s="9" t="str" cm="1">
         <f t="array" ref="N209">SECTION_NAME(B209)</f>
-        <v>ci-c-spec-159</v>
+        <v>ci-c-spec-158</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" ht="221" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D210" s="7" t="s">
         <v>26</v>
@@ -11034,30 +11287,30 @@
       </c>
       <c r="N210" s="9" t="str" cm="1">
         <f t="array" ref="N210">SECTION_NAME(B210)</f>
-        <v>ci-c-spec-160</v>
+        <v>ci-c-spec-159</v>
       </c>
       <c r="P210" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E211" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G211" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" s="9" t="str" cm="1">
         <f t="array" ref="M211">PAGE_NAME(B211)</f>
@@ -11065,30 +11318,30 @@
       </c>
       <c r="N211" s="9" t="str" cm="1">
         <f t="array" ref="N211">SECTION_NAME(B211)</f>
-        <v>ci-c-spec-161</v>
+        <v>ci-c-spec-160</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G212" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M212" s="9" t="str" cm="1">
         <f t="array" ref="M212">PAGE_NAME(B212)</f>
@@ -11096,30 +11349,30 @@
       </c>
       <c r="N212" s="9" t="str" cm="1">
         <f t="array" ref="N212">SECTION_NAME(B212)</f>
-        <v>ci-c-spec-162</v>
+        <v>ci-c-spec-161</v>
       </c>
       <c r="P212" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A213" s="7" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>713</v>
+        <v>29</v>
       </c>
       <c r="E213" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G213" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213" s="9" t="str" cm="1">
         <f t="array" ref="M213">PAGE_NAME(B213)</f>
@@ -11127,27 +11380,28 @@
       </c>
       <c r="N213" s="9" t="str" cm="1">
         <f t="array" ref="N213">SECTION_NAME(B213)</f>
-        <v>ci-c-spec-163</v>
+        <v>ci-c-spec-162</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="214" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="S213" s="13"/>
+    </row>
+    <row r="214" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A214" s="7" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>29</v>
+        <v>710</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G214" s="8" t="b">
         <v>0</v>
@@ -11158,30 +11412,31 @@
       </c>
       <c r="N214" s="9" t="str" cm="1">
         <f t="array" ref="N214">SECTION_NAME(B214)</f>
-        <v>ci-c-spec-164</v>
+        <v>ci-c-spec-163</v>
       </c>
       <c r="P214" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="S214" s="13"/>
+    </row>
+    <row r="215" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A215" s="7" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E215" s="8" t="s">
         <v>107</v>
       </c>
       <c r="G215" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M215" s="9" t="str" cm="1">
         <f t="array" ref="M215">PAGE_NAME(B215)</f>
@@ -11189,24 +11444,25 @@
       </c>
       <c r="N215" s="9" t="str" cm="1">
         <f t="array" ref="N215">SECTION_NAME(B215)</f>
-        <v>ci-c-spec-165</v>
+        <v>ci-c-spec-164</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="S215" s="13"/>
+    </row>
+    <row r="216" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A216" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E216" s="8" t="s">
         <v>107</v>
@@ -11220,18 +11476,72 @@
       </c>
       <c r="N216" s="9" t="str" cm="1">
         <f t="array" ref="N216">SECTION_NAME(B216)</f>
+        <v>ci-c-spec-165</v>
+      </c>
+      <c r="P216" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="S216" s="13"/>
+    </row>
+    <row r="217" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A217" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C217" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="D217" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G217" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M217" s="9" t="str" cm="1">
+        <f t="array" ref="M217">PAGE_NAME(B217)</f>
+        <v>specification</v>
+      </c>
+      <c r="N217" s="9" t="str" cm="1">
+        <f t="array" ref="N217">SECTION_NAME(B217)</f>
         <v>ci-c-spec-166</v>
       </c>
-      <c r="P216" s="10" t="s">
-        <v>723</v>
-      </c>
+      <c r="P217" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="S217" s="13"/>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S218" s="13"/>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S219" s="13"/>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S220" s="13"/>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S221" s="13"/>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S222" s="13"/>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S223" s="13"/>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S224" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE216" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
+  <autoFilter ref="A1:AF217" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" location="ci-c-conf-5" xr:uid="{54FDFC2F-0C71-9847-9311-57A99C2A2FC8}"/>
-    <hyperlink ref="B40" r:id="rId2" location="ci-c-prof-2" xr:uid="{7290C952-57E1-8842-B595-0231F7C148ED}"/>
-    <hyperlink ref="B64" r:id="rId3" location="ci-c-spec-14" xr:uid="{00DAE728-E8A3-4041-ABBD-1CA449CC91CF}"/>
+    <hyperlink ref="B26" r:id="rId1" location="ci-c-oper-7" xr:uid="{4023679D-7765-2B42-A707-2B63CD4C2439}"/>
+    <hyperlink ref="B76" r:id="rId2" location="ci-c-spec-25" xr:uid="{C6E51CB5-4ECD-3246-931F-4ABAFB05C0AF}"/>
+    <hyperlink ref="B158" r:id="rId3" location="ci-c-spec-107" xr:uid="{165FFDE3-4610-954A-A59A-28C882B3B7C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -11242,7 +11552,7 @@
           <x14:formula1>
             <xm:f>'Column Data'!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G1 G217:G1048576</xm:sqref>
+          <xm:sqref>G1 G218:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4866B9BF-5615-6646-965F-909D4D65F2A5}">
           <x14:formula1>
@@ -11254,7 +11564,7 @@
           <x14:formula1>
             <xm:f>'Column Data'!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K1048576 I2:I1048576</xm:sqref>
+          <xm:sqref>I2:I1048576 K2:K1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11272,14 +11582,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="40"/>
+      <c r="B1" s="42"/>
     </row>
     <row r="2" spans="1:2" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
@@ -11344,7 +11654,7 @@
       <c r="A13" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="35" t="s">
         <v>80</v>
       </c>
     </row>
@@ -11504,6 +11814,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -11757,7 +12080,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11766,20 +12089,25 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
+    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94A9A0BE-5C9D-4319-9F23-325C29977794}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11799,28 +12127,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
-    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>